--- a/FAZENDA_PROMISSÃO_distancias.xlsx
+++ b/FAZENDA_PROMISSÃO_distancias.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -67,17 +67,6 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00C00000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00C00000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <i val="1"/>
       <color rgb="00808080"/>
       <sz val="9"/>
@@ -102,12 +91,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -128,13 +117,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -149,28 +145,13 @@
     <xf numFmtId="4" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="8" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
@@ -626,23 +607,23 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>T-04</t>
+          <t>T-01</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>222.45</v>
+        <v>217.12</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>5898</v>
+        <v>6055</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>13992</v>
+        <v>11396</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>11110</v>
+        <v>9085</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>4632</v>
+        <v>7665</v>
       </c>
       <c r="G5" s="8">
         <f>D5/1000</f>
@@ -661,23 +642,23 @@
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>T-03</t>
+          <t>T-08</t>
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>215.16</v>
+        <v>128.52</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>5870</v>
+        <v>5847</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>12620</v>
+        <v>10596</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>9699</v>
+        <v>7699</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>5463</v>
+        <v>6977</v>
       </c>
       <c r="G6" s="15">
         <f>D6/1000</f>
@@ -696,23 +677,23 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>T-05</t>
+          <t>T-02</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>176.55</v>
+        <v>216.07</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>7594</v>
+        <v>5881</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>12490</v>
+        <v>9872</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>9017</v>
+        <v>7641</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>3538</v>
+        <v>6496</v>
       </c>
       <c r="G7" s="8">
         <f>D7/1000</f>
@@ -731,23 +712,23 @@
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>T-01</t>
+          <t>T-32A</t>
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>217.12</v>
+        <v>83.98999999999999</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>6055</v>
+        <v>4543</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>12296</v>
+        <v>9487</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>9276</v>
+        <v>7746</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>7665</v>
+        <v>6182</v>
       </c>
       <c r="G8" s="15">
         <f>D8/1000</f>
@@ -764,60 +745,60 @@
       <c r="J8" s="17" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="inlineStr">
-        <is>
-          <t>T-02</t>
-        </is>
-      </c>
-      <c r="B9" s="19" t="n">
-        <v>216.07</v>
-      </c>
-      <c r="C9" s="20" t="n">
-        <v>5881</v>
-      </c>
-      <c r="D9" s="21" t="n">
-        <v>11710</v>
-      </c>
-      <c r="E9" s="21" t="n">
-        <v>9276</v>
-      </c>
-      <c r="F9" s="21" t="n">
-        <v>6496</v>
-      </c>
-      <c r="G9" s="22">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>T-07</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>214</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>5853</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>9170</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>6257</v>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>5666</v>
+      </c>
+      <c r="G9" s="8">
         <f>D9/1000</f>
         <v/>
       </c>
-      <c r="H9" s="22">
+      <c r="H9" s="8">
         <f>E9/1000</f>
         <v/>
       </c>
-      <c r="I9" s="23">
+      <c r="I9" s="9">
         <f>IFERROR(D9/F9,"")</f>
         <v/>
       </c>
-      <c r="J9" s="24" t="inlineStr"/>
+      <c r="J9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>T-06</t>
+          <t>T-27</t>
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>211.14</v>
+        <v>248.35</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>5814</v>
+        <v>7351</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>11110</v>
+        <v>8982</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>8210</v>
+        <v>5326</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>4461</v>
+        <v>4648</v>
       </c>
       <c r="G10" s="15">
         <f>D10/1000</f>
@@ -834,60 +815,60 @@
       <c r="J10" s="17" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="inlineStr">
-        <is>
-          <t>T-08</t>
-        </is>
-      </c>
-      <c r="B11" s="19" t="n">
-        <v>128.52</v>
-      </c>
-      <c r="C11" s="20" t="n">
-        <v>5847</v>
-      </c>
-      <c r="D11" s="21" t="n">
-        <v>10699</v>
-      </c>
-      <c r="E11" s="21" t="n">
-        <v>7781</v>
-      </c>
-      <c r="F11" s="21" t="n">
-        <v>6977</v>
-      </c>
-      <c r="G11" s="22">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>T-32</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>138.68</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>5245</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>8908</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>6335</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>4871</v>
+      </c>
+      <c r="G11" s="8">
         <f>D11/1000</f>
         <v/>
       </c>
-      <c r="H11" s="22">
+      <c r="H11" s="8">
         <f>E11/1000</f>
         <v/>
       </c>
-      <c r="I11" s="23">
+      <c r="I11" s="9">
         <f>IFERROR(D11/F11,"")</f>
         <v/>
       </c>
-      <c r="J11" s="24" t="inlineStr"/>
+      <c r="J11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>T-07</t>
+          <t>T-28</t>
         </is>
       </c>
       <c r="B12" s="12" t="n">
-        <v>214</v>
+        <v>181.92</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>5853</v>
+        <v>6154</v>
       </c>
       <c r="D12" s="14" t="n">
-        <v>10201</v>
+        <v>8892</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>7781</v>
+        <v>6368</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>5666</v>
+        <v>5748</v>
       </c>
       <c r="G12" s="15">
         <f>D12/1000</f>
@@ -906,23 +887,23 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>T-24</t>
+          <t>T-31A</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>313.18</v>
+        <v>132.85</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>7098</v>
+        <v>5047</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>10067</v>
+        <v>8606</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>6529</v>
+        <v>6188</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>2810</v>
+        <v>4795</v>
       </c>
       <c r="G13" s="8">
         <f>D13/1000</f>
@@ -939,60 +920,60 @@
       <c r="J13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>T-11</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n">
-        <v>303.27</v>
-      </c>
-      <c r="C14" s="6" t="n">
-        <v>7420</v>
-      </c>
-      <c r="D14" s="7" t="n">
-        <v>9927</v>
-      </c>
-      <c r="E14" s="7" t="n">
-        <v>6224</v>
-      </c>
-      <c r="F14" s="7" t="n">
-        <v>2827</v>
-      </c>
-      <c r="G14" s="8">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>T-03</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="n">
+        <v>215.16</v>
+      </c>
+      <c r="C14" s="13" t="n">
+        <v>5870</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>8443</v>
+      </c>
+      <c r="E14" s="14" t="n">
+        <v>6310</v>
+      </c>
+      <c r="F14" s="14" t="n">
+        <v>5463</v>
+      </c>
+      <c r="G14" s="15">
         <f>D14/1000</f>
         <v/>
       </c>
-      <c r="H14" s="8">
+      <c r="H14" s="15">
         <f>E14/1000</f>
         <v/>
       </c>
-      <c r="I14" s="9">
+      <c r="I14" s="16">
         <f>IFERROR(D14/F14,"")</f>
         <v/>
       </c>
-      <c r="J14" s="10" t="inlineStr"/>
+      <c r="J14" s="17" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>T-25</t>
+          <t>T-09</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>128.42</v>
+        <v>136.16</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>6551</v>
+        <v>5252</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>8765</v>
+        <v>8347</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>6106</v>
+        <v>5751</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>2542</v>
+        <v>5369</v>
       </c>
       <c r="G15" s="8">
         <f>D15/1000</f>
@@ -1011,23 +992,23 @@
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>T-10</t>
+          <t>T-04</t>
         </is>
       </c>
       <c r="B16" s="12" t="n">
-        <v>225.86</v>
+        <v>222.45</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>6836</v>
+        <v>5898</v>
       </c>
       <c r="D16" s="14" t="n">
-        <v>8707</v>
+        <v>7962</v>
       </c>
       <c r="E16" s="14" t="n">
-        <v>5290</v>
+        <v>5178</v>
       </c>
       <c r="F16" s="14" t="n">
-        <v>3960</v>
+        <v>4632</v>
       </c>
       <c r="G16" s="15">
         <f>D16/1000</f>
@@ -1044,130 +1025,130 @@
       <c r="J16" s="17" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
-        <is>
-          <t>T-09</t>
-        </is>
-      </c>
-      <c r="B17" s="19" t="n">
-        <v>136.16</v>
-      </c>
-      <c r="C17" s="20" t="n">
-        <v>5252</v>
-      </c>
-      <c r="D17" s="21" t="n">
-        <v>8418</v>
-      </c>
-      <c r="E17" s="21" t="n">
-        <v>5803</v>
-      </c>
-      <c r="F17" s="21" t="n">
-        <v>5369</v>
-      </c>
-      <c r="G17" s="22">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>T-13</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>198.71</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>5502</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>7891</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>5271</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>4181</v>
+      </c>
+      <c r="G17" s="8">
         <f>D17/1000</f>
         <v/>
       </c>
-      <c r="H17" s="22">
+      <c r="H17" s="8">
         <f>E17/1000</f>
         <v/>
       </c>
-      <c r="I17" s="23">
+      <c r="I17" s="9">
         <f>IFERROR(D17/F17,"")</f>
         <v/>
       </c>
-      <c r="J17" s="24" t="inlineStr"/>
+      <c r="J17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>T-20</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="n">
-        <v>240.55</v>
-      </c>
-      <c r="C18" s="6" t="n">
-        <v>9293</v>
-      </c>
-      <c r="D18" s="7" t="n">
-        <v>8379</v>
-      </c>
-      <c r="E18" s="7" t="n">
-        <v>3762</v>
-      </c>
-      <c r="F18" s="7" t="n">
-        <v>1215</v>
-      </c>
-      <c r="G18" s="8">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>T-06</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="n">
+        <v>211.14</v>
+      </c>
+      <c r="C18" s="13" t="n">
+        <v>5814</v>
+      </c>
+      <c r="D18" s="14" t="n">
+        <v>7739</v>
+      </c>
+      <c r="E18" s="14" t="n">
+        <v>4840</v>
+      </c>
+      <c r="F18" s="14" t="n">
+        <v>4461</v>
+      </c>
+      <c r="G18" s="15">
         <f>D18/1000</f>
         <v/>
       </c>
-      <c r="H18" s="8">
+      <c r="H18" s="15">
         <f>E18/1000</f>
         <v/>
       </c>
-      <c r="I18" s="9">
+      <c r="I18" s="16">
         <f>IFERROR(D18/F18,"")</f>
         <v/>
       </c>
-      <c r="J18" s="10" t="inlineStr"/>
+      <c r="J18" s="17" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="inlineStr">
-        <is>
-          <t>T-14</t>
-        </is>
-      </c>
-      <c r="B19" s="19" t="n">
-        <v>180.97</v>
-      </c>
-      <c r="C19" s="20" t="n">
-        <v>5840</v>
-      </c>
-      <c r="D19" s="21" t="n">
-        <v>8295</v>
-      </c>
-      <c r="E19" s="21" t="n">
-        <v>5792</v>
-      </c>
-      <c r="F19" s="21" t="n">
-        <v>3349</v>
-      </c>
-      <c r="G19" s="22">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>T-10</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>225.86</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>6836</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>7696</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>4311</v>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>3960</v>
+      </c>
+      <c r="G19" s="8">
         <f>D19/1000</f>
         <v/>
       </c>
-      <c r="H19" s="22">
+      <c r="H19" s="8">
         <f>E19/1000</f>
         <v/>
       </c>
-      <c r="I19" s="23">
+      <c r="I19" s="9">
         <f>IFERROR(D19/F19,"")</f>
         <v/>
       </c>
-      <c r="J19" s="24" t="inlineStr"/>
+      <c r="J19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>T-13</t>
+          <t>T-30A</t>
         </is>
       </c>
       <c r="B20" s="12" t="n">
-        <v>198.71</v>
+        <v>101.07</v>
       </c>
       <c r="C20" s="13" t="n">
-        <v>5502</v>
+        <v>4286</v>
       </c>
       <c r="D20" s="14" t="n">
-        <v>8255</v>
+        <v>7577</v>
       </c>
       <c r="E20" s="14" t="n">
-        <v>5963</v>
+        <v>5461</v>
       </c>
       <c r="F20" s="14" t="n">
-        <v>4181</v>
+        <v>4476</v>
       </c>
       <c r="G20" s="15">
         <f>D20/1000</f>
@@ -1186,23 +1167,23 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>T-23</t>
+          <t>T-31B</t>
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>249.78</v>
+        <v>89.83</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>6425</v>
+        <v>4143</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>8245</v>
+        <v>7361</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>5045</v>
+        <v>5298</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>1605</v>
+        <v>3986</v>
       </c>
       <c r="G21" s="8">
         <f>D21/1000</f>
@@ -1221,23 +1202,23 @@
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>T-19</t>
+          <t>T-24</t>
         </is>
       </c>
       <c r="B22" s="12" t="n">
-        <v>207.35</v>
+        <v>313.18</v>
       </c>
       <c r="C22" s="13" t="n">
-        <v>5781</v>
+        <v>7098</v>
       </c>
       <c r="D22" s="14" t="n">
-        <v>7549</v>
+        <v>7281</v>
       </c>
       <c r="E22" s="14" t="n">
-        <v>5191</v>
+        <v>3853</v>
       </c>
       <c r="F22" s="14" t="n">
-        <v>2643</v>
+        <v>2810</v>
       </c>
       <c r="G22" s="15">
         <f>D22/1000</f>
@@ -1256,23 +1237,23 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>T-22</t>
+          <t>T-29A</t>
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>268.29</v>
+        <v>158.57</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>6666</v>
+        <v>5634</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>7120</v>
+        <v>7141</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>4076</v>
+        <v>4323</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>954</v>
+        <v>3705</v>
       </c>
       <c r="G23" s="8">
         <f>D23/1000</f>
@@ -1291,23 +1272,23 @@
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>T-12</t>
+          <t>T-14</t>
         </is>
       </c>
       <c r="B24" s="12" t="n">
-        <v>196.2</v>
+        <v>180.97</v>
       </c>
       <c r="C24" s="13" t="n">
-        <v>5516</v>
+        <v>5840</v>
       </c>
       <c r="D24" s="14" t="n">
-        <v>7030</v>
+        <v>6914</v>
       </c>
       <c r="E24" s="14" t="n">
-        <v>4281</v>
+        <v>4312</v>
       </c>
       <c r="F24" s="14" t="n">
-        <v>3785</v>
+        <v>3349</v>
       </c>
       <c r="G24" s="15">
         <f>D24/1000</f>
@@ -1324,165 +1305,165 @@
       <c r="J24" s="17" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="inlineStr">
-        <is>
-          <t>T-15</t>
-        </is>
-      </c>
-      <c r="B25" s="19" t="n">
-        <v>189.27</v>
-      </c>
-      <c r="C25" s="20" t="n">
-        <v>5556</v>
-      </c>
-      <c r="D25" s="21" t="n">
-        <v>6946</v>
-      </c>
-      <c r="E25" s="21" t="n">
-        <v>4324</v>
-      </c>
-      <c r="F25" s="21" t="n">
-        <v>2759</v>
-      </c>
-      <c r="G25" s="22">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>T-30B</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>129.79</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>4831</v>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>6690</v>
+      </c>
+      <c r="E25" s="7" t="n">
+        <v>4284</v>
+      </c>
+      <c r="F25" s="7" t="n">
+        <v>3323</v>
+      </c>
+      <c r="G25" s="8">
         <f>D25/1000</f>
         <v/>
       </c>
-      <c r="H25" s="22">
+      <c r="H25" s="8">
         <f>E25/1000</f>
         <v/>
       </c>
-      <c r="I25" s="23">
+      <c r="I25" s="9">
         <f>IFERROR(D25/F25,"")</f>
         <v/>
       </c>
-      <c r="J25" s="24" t="inlineStr"/>
+      <c r="J25" s="10" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>T-18</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="n">
-        <v>265.83</v>
-      </c>
-      <c r="C26" s="6" t="n">
-        <v>6634</v>
-      </c>
-      <c r="D26" s="7" t="n">
-        <v>6307</v>
-      </c>
-      <c r="E26" s="7" t="n">
-        <v>3762</v>
-      </c>
-      <c r="F26" s="7" t="n">
-        <v>1241</v>
-      </c>
-      <c r="G26" s="8">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>T-12</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="n">
+        <v>196.2</v>
+      </c>
+      <c r="C26" s="13" t="n">
+        <v>5516</v>
+      </c>
+      <c r="D26" s="14" t="n">
+        <v>6686</v>
+      </c>
+      <c r="E26" s="14" t="n">
+        <v>4273</v>
+      </c>
+      <c r="F26" s="14" t="n">
+        <v>3785</v>
+      </c>
+      <c r="G26" s="15">
         <f>D26/1000</f>
         <v/>
       </c>
-      <c r="H26" s="8">
+      <c r="H26" s="15">
         <f>E26/1000</f>
         <v/>
       </c>
-      <c r="I26" s="9">
+      <c r="I26" s="16">
         <f>IFERROR(D26/F26,"")</f>
         <v/>
       </c>
-      <c r="J26" s="10" t="inlineStr"/>
+      <c r="J26" s="17" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="inlineStr">
-        <is>
-          <t>T-16</t>
-        </is>
-      </c>
-      <c r="B27" s="19" t="n">
-        <v>113.43</v>
-      </c>
-      <c r="C27" s="20" t="n">
-        <v>4317</v>
-      </c>
-      <c r="D27" s="21" t="n">
-        <v>5266</v>
-      </c>
-      <c r="E27" s="21" t="n">
-        <v>3109</v>
-      </c>
-      <c r="F27" s="21" t="n">
-        <v>2713</v>
-      </c>
-      <c r="G27" s="22">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>T-05</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>176.55</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>7594</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>6461</v>
+      </c>
+      <c r="E27" s="7" t="n">
+        <v>3675</v>
+      </c>
+      <c r="F27" s="7" t="n">
+        <v>3538</v>
+      </c>
+      <c r="G27" s="8">
         <f>D27/1000</f>
         <v/>
       </c>
-      <c r="H27" s="22">
+      <c r="H27" s="8">
         <f>E27/1000</f>
         <v/>
       </c>
-      <c r="I27" s="23">
+      <c r="I27" s="9">
         <f>IFERROR(D27/F27,"")</f>
         <v/>
       </c>
-      <c r="J27" s="24" t="inlineStr"/>
+      <c r="J27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>T-21</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="n">
-        <v>135.82</v>
-      </c>
-      <c r="C28" s="6" t="n">
-        <v>5029</v>
-      </c>
-      <c r="D28" s="7" t="n">
-        <v>5242</v>
-      </c>
-      <c r="E28" s="7" t="n">
-        <v>2743</v>
-      </c>
-      <c r="F28" s="7" t="n">
-        <v>218</v>
-      </c>
-      <c r="G28" s="8">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>T-26A</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="n">
+        <v>127.51</v>
+      </c>
+      <c r="C28" s="13" t="n">
+        <v>5515</v>
+      </c>
+      <c r="D28" s="14" t="n">
+        <v>6456</v>
+      </c>
+      <c r="E28" s="14" t="n">
+        <v>4333</v>
+      </c>
+      <c r="F28" s="14" t="n">
+        <v>2671</v>
+      </c>
+      <c r="G28" s="15">
         <f>D28/1000</f>
         <v/>
       </c>
-      <c r="H28" s="8">
+      <c r="H28" s="15">
         <f>E28/1000</f>
         <v/>
       </c>
-      <c r="I28" s="9">
+      <c r="I28" s="16">
         <f>IFERROR(D28/F28,"")</f>
         <v/>
       </c>
-      <c r="J28" s="10" t="inlineStr"/>
+      <c r="J28" s="17" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>T-17</t>
+          <t>T-11</t>
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>356.7</v>
+        <v>303.27</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>10087</v>
+        <v>7420</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>5080</v>
+        <v>6274</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>44</v>
+        <v>3141</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>44</v>
+        <v>2827</v>
       </c>
       <c r="G29" s="8">
         <f>D29/1000</f>
@@ -1499,709 +1480,555 @@
       <c r="J29" s="10" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>T-29C</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="C30" s="6" t="n">
-        <v>2922</v>
-      </c>
-      <c r="D30" s="7" t="n">
-        <v>1528</v>
-      </c>
-      <c r="E30" s="7" t="n">
-        <v>68</v>
-      </c>
-      <c r="F30" s="7" t="n">
-        <v>61</v>
-      </c>
-      <c r="G30" s="8">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>T-25</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="n">
+        <v>128.42</v>
+      </c>
+      <c r="C30" s="13" t="n">
+        <v>6551</v>
+      </c>
+      <c r="D30" s="14" t="n">
+        <v>5892</v>
+      </c>
+      <c r="E30" s="14" t="n">
+        <v>3042</v>
+      </c>
+      <c r="F30" s="14" t="n">
+        <v>2542</v>
+      </c>
+      <c r="G30" s="15">
         <f>D30/1000</f>
         <v/>
       </c>
-      <c r="H30" s="8">
+      <c r="H30" s="15">
         <f>E30/1000</f>
         <v/>
       </c>
-      <c r="I30" s="9">
+      <c r="I30" s="16">
         <f>IFERROR(D30/F30,"")</f>
         <v/>
       </c>
-      <c r="J30" s="10" t="inlineStr"/>
+      <c r="J30" s="17" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>T-26</t>
+          <t>T-15</t>
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>147.1</v>
+        <v>189.27</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>5457</v>
-      </c>
-      <c r="D31" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
-      </c>
-      <c r="E31" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
+        <v>5556</v>
+      </c>
+      <c r="D31" s="7" t="n">
+        <v>5853</v>
+      </c>
+      <c r="E31" s="7" t="n">
+        <v>3323</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>1631</v>
-      </c>
-      <c r="G31" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H31" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I31" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J31" s="28" t="inlineStr">
-        <is>
-          <t>sem estrada até este talhão</t>
-        </is>
-      </c>
+        <v>2759</v>
+      </c>
+      <c r="G31" s="8">
+        <f>D31/1000</f>
+        <v/>
+      </c>
+      <c r="H31" s="8">
+        <f>E31/1000</f>
+        <v/>
+      </c>
+      <c r="I31" s="9">
+        <f>IFERROR(D31/F31,"")</f>
+        <v/>
+      </c>
+      <c r="J31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>T-26A</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="n">
-        <v>127.51</v>
-      </c>
-      <c r="C32" s="6" t="n">
-        <v>5515</v>
-      </c>
-      <c r="D32" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
-      </c>
-      <c r="E32" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
-      </c>
-      <c r="F32" s="7" t="n">
-        <v>2671</v>
-      </c>
-      <c r="G32" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H32" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I32" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J32" s="28" t="inlineStr">
-        <is>
-          <t>sem estrada até este talhão</t>
-        </is>
-      </c>
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>T-30C</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="C32" s="13" t="n">
+        <v>3095</v>
+      </c>
+      <c r="D32" s="14" t="n">
+        <v>5817</v>
+      </c>
+      <c r="E32" s="14" t="n">
+        <v>4281</v>
+      </c>
+      <c r="F32" s="14" t="n">
+        <v>3321</v>
+      </c>
+      <c r="G32" s="15">
+        <f>D32/1000</f>
+        <v/>
+      </c>
+      <c r="H32" s="15">
+        <f>E32/1000</f>
+        <v/>
+      </c>
+      <c r="I32" s="16">
+        <f>IFERROR(D32/F32,"")</f>
+        <v/>
+      </c>
+      <c r="J32" s="17" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>T-27</t>
+          <t>T-29B</t>
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>248.35</v>
+        <v>115.08</v>
       </c>
       <c r="C33" s="6" t="n">
-        <v>7351</v>
-      </c>
-      <c r="D33" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
-      </c>
-      <c r="E33" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
+        <v>5656</v>
+      </c>
+      <c r="D33" s="7" t="n">
+        <v>5599</v>
+      </c>
+      <c r="E33" s="7" t="n">
+        <v>2881</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>4648</v>
-      </c>
-      <c r="G33" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H33" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I33" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J33" s="28" t="inlineStr">
-        <is>
-          <t>sem estrada até este talhão</t>
-        </is>
-      </c>
+        <v>2262</v>
+      </c>
+      <c r="G33" s="8">
+        <f>D33/1000</f>
+        <v/>
+      </c>
+      <c r="H33" s="8">
+        <f>E33/1000</f>
+        <v/>
+      </c>
+      <c r="I33" s="9">
+        <f>IFERROR(D33/F33,"")</f>
+        <v/>
+      </c>
+      <c r="J33" s="10" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>T-28</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="n">
-        <v>181.92</v>
-      </c>
-      <c r="C34" s="6" t="n">
-        <v>6154</v>
-      </c>
-      <c r="D34" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
-      </c>
-      <c r="E34" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
-      </c>
-      <c r="F34" s="7" t="n">
-        <v>5748</v>
-      </c>
-      <c r="G34" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H34" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I34" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J34" s="28" t="inlineStr">
-        <is>
-          <t>sem estrada até este talhão</t>
-        </is>
-      </c>
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>T-19</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="n">
+        <v>207.35</v>
+      </c>
+      <c r="C34" s="13" t="n">
+        <v>5781</v>
+      </c>
+      <c r="D34" s="14" t="n">
+        <v>5545</v>
+      </c>
+      <c r="E34" s="14" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F34" s="14" t="n">
+        <v>2643</v>
+      </c>
+      <c r="G34" s="15">
+        <f>D34/1000</f>
+        <v/>
+      </c>
+      <c r="H34" s="15">
+        <f>E34/1000</f>
+        <v/>
+      </c>
+      <c r="I34" s="16">
+        <f>IFERROR(D34/F34,"")</f>
+        <v/>
+      </c>
+      <c r="J34" s="17" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>T-29 C</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="C35" s="6" t="n">
-        <v>3375</v>
-      </c>
-      <c r="D35" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
-      </c>
-      <c r="E35" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
-      </c>
-      <c r="F35" s="7" t="n">
-        <v>2251</v>
-      </c>
-      <c r="G35" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H35" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I35" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J35" s="28" t="inlineStr">
-        <is>
-          <t>sem estrada até este talhão</t>
-        </is>
-      </c>
+      <c r="A35" s="18" t="inlineStr">
+        <is>
+          <t>T-23</t>
+        </is>
+      </c>
+      <c r="B35" s="19" t="n">
+        <v>249.78</v>
+      </c>
+      <c r="C35" s="20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="D35" s="21" t="n">
+        <v>5435</v>
+      </c>
+      <c r="E35" s="21" t="n">
+        <v>2381</v>
+      </c>
+      <c r="F35" s="21" t="n">
+        <v>1605</v>
+      </c>
+      <c r="G35" s="22">
+        <f>D35/1000</f>
+        <v/>
+      </c>
+      <c r="H35" s="22">
+        <f>E35/1000</f>
+        <v/>
+      </c>
+      <c r="I35" s="23">
+        <f>IFERROR(D35/F35,"")</f>
+        <v/>
+      </c>
+      <c r="J35" s="24" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>T-29A</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="n">
-        <v>158.57</v>
-      </c>
-      <c r="C36" s="6" t="n">
-        <v>5634</v>
-      </c>
-      <c r="D36" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
-      </c>
-      <c r="E36" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
-      </c>
-      <c r="F36" s="7" t="n">
-        <v>3705</v>
-      </c>
-      <c r="G36" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H36" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I36" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J36" s="28" t="inlineStr">
-        <is>
-          <t>sem estrada até este talhão</t>
-        </is>
-      </c>
+      <c r="A36" s="18" t="inlineStr">
+        <is>
+          <t>T-26</t>
+        </is>
+      </c>
+      <c r="B36" s="19" t="n">
+        <v>147.1</v>
+      </c>
+      <c r="C36" s="20" t="n">
+        <v>5457</v>
+      </c>
+      <c r="D36" s="21" t="n">
+        <v>5247</v>
+      </c>
+      <c r="E36" s="21" t="n">
+        <v>2566</v>
+      </c>
+      <c r="F36" s="21" t="n">
+        <v>1631</v>
+      </c>
+      <c r="G36" s="22">
+        <f>D36/1000</f>
+        <v/>
+      </c>
+      <c r="H36" s="22">
+        <f>E36/1000</f>
+        <v/>
+      </c>
+      <c r="I36" s="23">
+        <f>IFERROR(D36/F36,"")</f>
+        <v/>
+      </c>
+      <c r="J36" s="24" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>T-29B</t>
+          <t>T-16</t>
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>115.08</v>
+        <v>113.43</v>
       </c>
       <c r="C37" s="6" t="n">
-        <v>5656</v>
-      </c>
-      <c r="D37" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
-      </c>
-      <c r="E37" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
+        <v>4317</v>
+      </c>
+      <c r="D37" s="7" t="n">
+        <v>4758</v>
+      </c>
+      <c r="E37" s="7" t="n">
+        <v>3102</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>2262</v>
-      </c>
-      <c r="G37" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H37" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I37" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J37" s="28" t="inlineStr">
-        <is>
-          <t>sem estrada até este talhão</t>
-        </is>
-      </c>
+        <v>2713</v>
+      </c>
+      <c r="G37" s="8">
+        <f>D37/1000</f>
+        <v/>
+      </c>
+      <c r="H37" s="8">
+        <f>E37/1000</f>
+        <v/>
+      </c>
+      <c r="I37" s="9">
+        <f>IFERROR(D37/F37,"")</f>
+        <v/>
+      </c>
+      <c r="J37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>T-30A</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="n">
-        <v>101.07</v>
-      </c>
-      <c r="C38" s="6" t="n">
-        <v>4286</v>
-      </c>
-      <c r="D38" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
-      </c>
-      <c r="E38" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
-      </c>
-      <c r="F38" s="7" t="n">
-        <v>4476</v>
-      </c>
-      <c r="G38" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H38" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I38" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J38" s="28" t="inlineStr">
-        <is>
-          <t>sem estrada até este talhão</t>
-        </is>
-      </c>
+      <c r="A38" s="18" t="inlineStr">
+        <is>
+          <t>T-18</t>
+        </is>
+      </c>
+      <c r="B38" s="19" t="n">
+        <v>265.83</v>
+      </c>
+      <c r="C38" s="20" t="n">
+        <v>6634</v>
+      </c>
+      <c r="D38" s="21" t="n">
+        <v>4751</v>
+      </c>
+      <c r="E38" s="21" t="n">
+        <v>1242</v>
+      </c>
+      <c r="F38" s="21" t="n">
+        <v>1241</v>
+      </c>
+      <c r="G38" s="22">
+        <f>D38/1000</f>
+        <v/>
+      </c>
+      <c r="H38" s="22">
+        <f>E38/1000</f>
+        <v/>
+      </c>
+      <c r="I38" s="23">
+        <f>IFERROR(D38/F38,"")</f>
+        <v/>
+      </c>
+      <c r="J38" s="24" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>T-30B</t>
+          <t>T-29 C</t>
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>129.79</v>
+        <v>23</v>
       </c>
       <c r="C39" s="6" t="n">
-        <v>4831</v>
-      </c>
-      <c r="D39" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
-      </c>
-      <c r="E39" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
+        <v>3375</v>
+      </c>
+      <c r="D39" s="7" t="n">
+        <v>4544</v>
+      </c>
+      <c r="E39" s="7" t="n">
+        <v>2869</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>3323</v>
-      </c>
-      <c r="G39" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H39" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I39" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J39" s="28" t="inlineStr">
-        <is>
-          <t>sem estrada até este talhão</t>
-        </is>
-      </c>
+        <v>2251</v>
+      </c>
+      <c r="G39" s="8">
+        <f>D39/1000</f>
+        <v/>
+      </c>
+      <c r="H39" s="8">
+        <f>E39/1000</f>
+        <v/>
+      </c>
+      <c r="I39" s="9">
+        <f>IFERROR(D39/F39,"")</f>
+        <v/>
+      </c>
+      <c r="J39" s="10" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>T-30C</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="n">
-        <v>53.2</v>
-      </c>
-      <c r="C40" s="6" t="n">
-        <v>3095</v>
-      </c>
-      <c r="D40" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
-      </c>
-      <c r="E40" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
-      </c>
-      <c r="F40" s="7" t="n">
-        <v>3321</v>
-      </c>
-      <c r="G40" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H40" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I40" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J40" s="28" t="inlineStr">
-        <is>
-          <t>sem estrada até este talhão</t>
-        </is>
-      </c>
+      <c r="A40" s="18" t="inlineStr">
+        <is>
+          <t>T-20</t>
+        </is>
+      </c>
+      <c r="B40" s="19" t="n">
+        <v>240.55</v>
+      </c>
+      <c r="C40" s="20" t="n">
+        <v>9293</v>
+      </c>
+      <c r="D40" s="21" t="n">
+        <v>4474</v>
+      </c>
+      <c r="E40" s="21" t="n">
+        <v>1242</v>
+      </c>
+      <c r="F40" s="21" t="n">
+        <v>1215</v>
+      </c>
+      <c r="G40" s="22">
+        <f>D40/1000</f>
+        <v/>
+      </c>
+      <c r="H40" s="22">
+        <f>E40/1000</f>
+        <v/>
+      </c>
+      <c r="I40" s="23">
+        <f>IFERROR(D40/F40,"")</f>
+        <v/>
+      </c>
+      <c r="J40" s="24" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>T-31A</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="n">
-        <v>132.85</v>
-      </c>
-      <c r="C41" s="6" t="n">
-        <v>5047</v>
-      </c>
-      <c r="D41" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
-      </c>
-      <c r="E41" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
-      </c>
-      <c r="F41" s="7" t="n">
-        <v>4795</v>
-      </c>
-      <c r="G41" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H41" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I41" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J41" s="28" t="inlineStr">
-        <is>
-          <t>sem estrada até este talhão</t>
-        </is>
-      </c>
+      <c r="A41" s="18" t="inlineStr">
+        <is>
+          <t>T-22</t>
+        </is>
+      </c>
+      <c r="B41" s="19" t="n">
+        <v>268.29</v>
+      </c>
+      <c r="C41" s="20" t="n">
+        <v>6666</v>
+      </c>
+      <c r="D41" s="21" t="n">
+        <v>4255</v>
+      </c>
+      <c r="E41" s="21" t="n">
+        <v>1011</v>
+      </c>
+      <c r="F41" s="21" t="n">
+        <v>954</v>
+      </c>
+      <c r="G41" s="22">
+        <f>D41/1000</f>
+        <v/>
+      </c>
+      <c r="H41" s="22">
+        <f>E41/1000</f>
+        <v/>
+      </c>
+      <c r="I41" s="23">
+        <f>IFERROR(D41/F41,"")</f>
+        <v/>
+      </c>
+      <c r="J41" s="24" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>T-31B</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="n">
-        <v>89.83</v>
-      </c>
-      <c r="C42" s="6" t="n">
-        <v>4143</v>
-      </c>
-      <c r="D42" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
-      </c>
-      <c r="E42" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
-      </c>
-      <c r="F42" s="7" t="n">
-        <v>3986</v>
-      </c>
-      <c r="G42" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H42" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I42" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J42" s="28" t="inlineStr">
-        <is>
-          <t>sem estrada até este talhão</t>
-        </is>
-      </c>
+      <c r="A42" s="18" t="inlineStr">
+        <is>
+          <t>T-17</t>
+        </is>
+      </c>
+      <c r="B42" s="19" t="n">
+        <v>356.7</v>
+      </c>
+      <c r="C42" s="20" t="n">
+        <v>10087</v>
+      </c>
+      <c r="D42" s="21" t="n">
+        <v>3811</v>
+      </c>
+      <c r="E42" s="21" t="n">
+        <v>44</v>
+      </c>
+      <c r="F42" s="21" t="n">
+        <v>44</v>
+      </c>
+      <c r="G42" s="22">
+        <f>D42/1000</f>
+        <v/>
+      </c>
+      <c r="H42" s="22">
+        <f>E42/1000</f>
+        <v/>
+      </c>
+      <c r="I42" s="23">
+        <f>IFERROR(D42/F42,"")</f>
+        <v/>
+      </c>
+      <c r="J42" s="24" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>T-32</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="n">
-        <v>138.68</v>
-      </c>
-      <c r="C43" s="6" t="n">
-        <v>5245</v>
-      </c>
-      <c r="D43" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
-      </c>
-      <c r="E43" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
-      </c>
-      <c r="F43" s="7" t="n">
-        <v>4871</v>
-      </c>
-      <c r="G43" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H43" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I43" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J43" s="28" t="inlineStr">
-        <is>
-          <t>sem estrada até este talhão</t>
-        </is>
-      </c>
+      <c r="A43" s="18" t="inlineStr">
+        <is>
+          <t>T-21</t>
+        </is>
+      </c>
+      <c r="B43" s="19" t="n">
+        <v>135.82</v>
+      </c>
+      <c r="C43" s="20" t="n">
+        <v>5029</v>
+      </c>
+      <c r="D43" s="21" t="n">
+        <v>2439</v>
+      </c>
+      <c r="E43" s="21" t="n">
+        <v>222</v>
+      </c>
+      <c r="F43" s="21" t="n">
+        <v>218</v>
+      </c>
+      <c r="G43" s="22">
+        <f>D43/1000</f>
+        <v/>
+      </c>
+      <c r="H43" s="22">
+        <f>E43/1000</f>
+        <v/>
+      </c>
+      <c r="I43" s="23">
+        <f>IFERROR(D43/F43,"")</f>
+        <v/>
+      </c>
+      <c r="J43" s="24" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>T-32A</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="n">
-        <v>83.98999999999999</v>
-      </c>
-      <c r="C44" s="6" t="n">
-        <v>4543</v>
-      </c>
-      <c r="D44" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
-      </c>
-      <c r="E44" s="25" t="inlineStr">
-        <is>
-          <t>sem acesso</t>
-        </is>
-      </c>
-      <c r="F44" s="7" t="n">
-        <v>6182</v>
-      </c>
-      <c r="G44" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H44" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I44" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J44" s="28" t="inlineStr">
-        <is>
-          <t>sem estrada até este talhão</t>
-        </is>
-      </c>
+      <c r="A44" s="18" t="inlineStr">
+        <is>
+          <t>T-29C</t>
+        </is>
+      </c>
+      <c r="B44" s="19" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="C44" s="20" t="n">
+        <v>2922</v>
+      </c>
+      <c r="D44" s="21" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E44" s="21" t="n">
+        <v>62</v>
+      </c>
+      <c r="F44" s="21" t="n">
+        <v>61</v>
+      </c>
+      <c r="G44" s="22">
+        <f>D44/1000</f>
+        <v/>
+      </c>
+      <c r="H44" s="22">
+        <f>E44/1000</f>
+        <v/>
+      </c>
+      <c r="I44" s="23">
+        <f>IFERROR(D44/F44,"")</f>
+        <v/>
+      </c>
+      <c r="J44" s="24" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="29" t="inlineStr">
+      <c r="A46" s="25" t="inlineStr">
         <is>
           <t>TOTAL / MÁXIMO</t>
         </is>
       </c>
-      <c r="B46" s="30">
+      <c r="B46" s="26">
         <f>SUM(B5:B44)</f>
         <v/>
       </c>
-      <c r="D46" s="31">
+      <c r="D46" s="27">
         <f>MAX(IFERROR(D5:D44*1,0))</f>
         <v/>
       </c>
-      <c r="G46" s="32">
+      <c r="G46" s="28">
         <f>IFERROR(MAX(G5:G44),"")</f>
         <v/>
       </c>
-      <c r="I46" s="33">
+      <c r="I46" s="29">
         <f>IFERROR(AVERAGE(I5:I44),"")</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="34" t="inlineStr">
+      <c r="A47" s="30" t="inlineStr">
         <is>
           <t>Fundo amarelo = precisa de conferência: fator ≥ 3,0, ligação suposta, ou talhão sem estrada. Veja a coluna Observação.</t>
         </is>
@@ -2226,127 +2053,127 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="35" t="inlineStr">
+      <c r="A1" s="31" t="inlineStr">
         <is>
           <t>Como estes números foram calculados</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="36" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>Origem</t>
         </is>
       </c>
-      <c r="B3" s="37" t="inlineStr">
+      <c r="B3" s="33" t="inlineStr">
         <is>
           <t>Ponto de sede do projeto do Google Earth (-13.894866, -57.09905).</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="36" t="inlineStr">
+      <c r="A4" s="32" t="inlineStr">
         <is>
           <t>Talhões</t>
         </is>
       </c>
-      <c r="B4" s="37" t="inlineStr">
+      <c r="B4" s="33" t="inlineStr">
         <is>
           <t>40 polígonos da pasta FAZENDA PROMISSÃO.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="36" t="inlineStr">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t>Malha de estradas</t>
         </is>
       </c>
-      <c r="B5" s="37" t="inlineStr">
+      <c r="B5" s="33" t="inlineStr">
         <is>
           <t>Divisas dos talhões (os carreadores correm nas divisas), costuradas onde talhões vizinhos são separados pela faixa do carreador (até 45 m), mais as estradas de dados/estradas_extra.json.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="36" t="inlineStr">
+      <c r="A6" s="32" t="inlineStr">
         <is>
           <t>Dist. máxima</t>
         </is>
       </c>
-      <c r="B6" s="37" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>Menor caminho pela estrada, da sede até o ponto MAIS EXTREMO do perímetro do talhão. Não corta por dentro da lavoura.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="36" t="inlineStr">
+      <c r="A7" s="32" t="inlineStr">
         <is>
           <t>Dist. mínima</t>
         </is>
       </c>
-      <c r="B7" s="37" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>Menor caminho pela estrada, da sede até o ponto de acesso mais próximo.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="36" t="inlineStr">
+      <c r="A8" s="32" t="inlineStr">
         <is>
           <t>Linha reta</t>
         </is>
       </c>
-      <c r="B8" s="37" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>Distância em linha reta da sede até a borda do talhão. Só referência.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="36" t="inlineStr">
+      <c r="A9" s="32" t="inlineStr">
         <is>
           <t>Fator</t>
         </is>
       </c>
-      <c r="B9" s="37" t="inlineStr">
+      <c r="B9" s="33" t="inlineStr">
         <is>
           <t>Dist. máxima ÷ linha reta. Fator alto = rota indireta, ou estrada faltando na malha.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="36" t="inlineStr">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t>Coordenadas</t>
         </is>
       </c>
-      <c r="B10" s="37" t="inlineStr">
+      <c r="B10" s="33" t="inlineStr">
         <is>
           <t>SIRGAS 2000 / UTM 21S (EPSG:31981) para distâncias e áreas.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="36" t="inlineStr">
+      <c r="A11" s="32" t="inlineStr">
         <is>
           <t>Resolução</t>
         </is>
       </c>
-      <c r="B11" s="37" t="inlineStr">
+      <c r="B11" s="33" t="inlineStr">
         <is>
           <t>Malha densificada a cada 25 m — é a precisão do 'ponto mais extremo'.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="36" t="inlineStr">
+      <c r="A12" s="32" t="inlineStr">
         <is>
           <t>Validação</t>
         </is>
       </c>
-      <c r="B12" s="37" t="inlineStr">
+      <c r="B12" s="33" t="inlineStr">
         <is>
           <t>A malha precisa ser conferida por quem roda a fazenda. Use o arquivo _bancada.html.</t>
         </is>

--- a/FAZENDA_PROMISSÃO_distancias.xlsx
+++ b/FAZENDA_PROMISSÃO_distancias.xlsx
@@ -617,10 +617,10 @@
         <v>6055</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>11396</v>
+        <v>11561</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>9085</v>
+        <v>9132</v>
       </c>
       <c r="F5" s="7" t="n">
         <v>7665</v>
@@ -652,10 +652,10 @@
         <v>5847</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>10596</v>
+        <v>10717</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>7699</v>
+        <v>7731</v>
       </c>
       <c r="F6" s="14" t="n">
         <v>6977</v>
@@ -687,10 +687,10 @@
         <v>5881</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>9872</v>
+        <v>9925</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>7641</v>
+        <v>7670</v>
       </c>
       <c r="F7" s="7" t="n">
         <v>6496</v>
@@ -722,10 +722,10 @@
         <v>4543</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>9487</v>
+        <v>9638</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>7746</v>
+        <v>7891</v>
       </c>
       <c r="F8" s="14" t="n">
         <v>6182</v>
@@ -757,10 +757,10 @@
         <v>5853</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>9170</v>
+        <v>9621</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>6257</v>
+        <v>6288</v>
       </c>
       <c r="F9" s="7" t="n">
         <v>5666</v>
@@ -792,10 +792,10 @@
         <v>7351</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>8982</v>
+        <v>9512</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>5326</v>
+        <v>5380</v>
       </c>
       <c r="F10" s="14" t="n">
         <v>4648</v>
@@ -817,23 +817,23 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>T-32</t>
+          <t>T-28</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>138.68</v>
+        <v>181.92</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>5245</v>
+        <v>6154</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>8908</v>
+        <v>9320</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>6335</v>
+        <v>6422</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>4871</v>
+        <v>5748</v>
       </c>
       <c r="G11" s="8">
         <f>D11/1000</f>
@@ -852,23 +852,23 @@
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>T-28</t>
+          <t>T-32</t>
         </is>
       </c>
       <c r="B12" s="12" t="n">
-        <v>181.92</v>
+        <v>138.68</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>6154</v>
+        <v>5245</v>
       </c>
       <c r="D12" s="14" t="n">
-        <v>8892</v>
+        <v>9199</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>6368</v>
+        <v>6391</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>5748</v>
+        <v>4871</v>
       </c>
       <c r="G12" s="15">
         <f>D12/1000</f>
@@ -897,10 +897,10 @@
         <v>5047</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>8606</v>
+        <v>9081</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>6188</v>
+        <v>6245</v>
       </c>
       <c r="F13" s="7" t="n">
         <v>4795</v>
@@ -932,10 +932,10 @@
         <v>5870</v>
       </c>
       <c r="D14" s="14" t="n">
-        <v>8443</v>
+        <v>8843</v>
       </c>
       <c r="E14" s="14" t="n">
-        <v>6310</v>
+        <v>6341</v>
       </c>
       <c r="F14" s="14" t="n">
         <v>5463</v>
@@ -967,10 +967,10 @@
         <v>5252</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>8347</v>
+        <v>8481</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>5751</v>
+        <v>5809</v>
       </c>
       <c r="F15" s="7" t="n">
         <v>5369</v>
@@ -992,23 +992,23 @@
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>T-04</t>
+          <t>T-30A</t>
         </is>
       </c>
       <c r="B16" s="12" t="n">
-        <v>222.45</v>
+        <v>101.07</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>5898</v>
+        <v>4286</v>
       </c>
       <c r="D16" s="14" t="n">
-        <v>7962</v>
+        <v>8408</v>
       </c>
       <c r="E16" s="14" t="n">
-        <v>5178</v>
+        <v>5517</v>
       </c>
       <c r="F16" s="14" t="n">
-        <v>4632</v>
+        <v>4476</v>
       </c>
       <c r="G16" s="15">
         <f>D16/1000</f>
@@ -1027,23 +1027,23 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>T-13</t>
+          <t>T-10</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>198.71</v>
+        <v>225.86</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>5502</v>
+        <v>6836</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>7891</v>
+        <v>8219</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>5271</v>
+        <v>4353</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>4181</v>
+        <v>3960</v>
       </c>
       <c r="G17" s="8">
         <f>D17/1000</f>
@@ -1062,23 +1062,23 @@
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>T-06</t>
+          <t>T-31B</t>
         </is>
       </c>
       <c r="B18" s="12" t="n">
-        <v>211.14</v>
+        <v>89.83</v>
       </c>
       <c r="C18" s="13" t="n">
-        <v>5814</v>
+        <v>4143</v>
       </c>
       <c r="D18" s="14" t="n">
-        <v>7739</v>
+        <v>8040</v>
       </c>
       <c r="E18" s="14" t="n">
-        <v>4840</v>
+        <v>5354</v>
       </c>
       <c r="F18" s="14" t="n">
-        <v>4461</v>
+        <v>3986</v>
       </c>
       <c r="G18" s="15">
         <f>D18/1000</f>
@@ -1097,23 +1097,23 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>T-10</t>
+          <t>T-04</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>225.86</v>
+        <v>222.45</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>6836</v>
+        <v>5898</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>7696</v>
+        <v>8005</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>4311</v>
+        <v>5216</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>3960</v>
+        <v>4632</v>
       </c>
       <c r="G19" s="8">
         <f>D19/1000</f>
@@ -1132,23 +1132,23 @@
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>T-30A</t>
+          <t>T-13</t>
         </is>
       </c>
       <c r="B20" s="12" t="n">
-        <v>101.07</v>
+        <v>198.71</v>
       </c>
       <c r="C20" s="13" t="n">
-        <v>4286</v>
+        <v>5502</v>
       </c>
       <c r="D20" s="14" t="n">
-        <v>7577</v>
+        <v>7994</v>
       </c>
       <c r="E20" s="14" t="n">
-        <v>5461</v>
+        <v>5354</v>
       </c>
       <c r="F20" s="14" t="n">
-        <v>4476</v>
+        <v>4181</v>
       </c>
       <c r="G20" s="15">
         <f>D20/1000</f>
@@ -1167,23 +1167,23 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>T-31B</t>
+          <t>T-06</t>
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>89.83</v>
+        <v>211.14</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>4143</v>
+        <v>5814</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>7361</v>
+        <v>7903</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>5298</v>
+        <v>4871</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>3986</v>
+        <v>4461</v>
       </c>
       <c r="G21" s="8">
         <f>D21/1000</f>
@@ -1212,10 +1212,10 @@
         <v>7098</v>
       </c>
       <c r="D22" s="14" t="n">
-        <v>7281</v>
+        <v>7321</v>
       </c>
       <c r="E22" s="14" t="n">
-        <v>3853</v>
+        <v>3867</v>
       </c>
       <c r="F22" s="14" t="n">
         <v>2810</v>
@@ -1247,10 +1247,10 @@
         <v>5634</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>7141</v>
+        <v>7216</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>4323</v>
+        <v>4377</v>
       </c>
       <c r="F23" s="7" t="n">
         <v>3705</v>
@@ -1272,23 +1272,23 @@
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>T-14</t>
+          <t>T-12</t>
         </is>
       </c>
       <c r="B24" s="12" t="n">
-        <v>180.97</v>
+        <v>196.2</v>
       </c>
       <c r="C24" s="13" t="n">
-        <v>5840</v>
+        <v>5516</v>
       </c>
       <c r="D24" s="14" t="n">
-        <v>6914</v>
+        <v>7209</v>
       </c>
       <c r="E24" s="14" t="n">
-        <v>4312</v>
+        <v>4297</v>
       </c>
       <c r="F24" s="14" t="n">
-        <v>3349</v>
+        <v>3785</v>
       </c>
       <c r="G24" s="15">
         <f>D24/1000</f>
@@ -1307,23 +1307,23 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>T-30B</t>
+          <t>T-25</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>129.79</v>
+        <v>128.42</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>4831</v>
+        <v>6551</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>6690</v>
+        <v>7110</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>4284</v>
+        <v>3069</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>3323</v>
+        <v>2542</v>
       </c>
       <c r="G25" s="8">
         <f>D25/1000</f>
@@ -1342,23 +1342,23 @@
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>T-12</t>
+          <t>T-14</t>
         </is>
       </c>
       <c r="B26" s="12" t="n">
-        <v>196.2</v>
+        <v>180.97</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>5516</v>
+        <v>5840</v>
       </c>
       <c r="D26" s="14" t="n">
-        <v>6686</v>
+        <v>6962</v>
       </c>
       <c r="E26" s="14" t="n">
-        <v>4273</v>
+        <v>4314</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>3785</v>
+        <v>3349</v>
       </c>
       <c r="G26" s="15">
         <f>D26/1000</f>
@@ -1377,23 +1377,23 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>T-05</t>
+          <t>T-30B</t>
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>176.55</v>
+        <v>129.79</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>7594</v>
+        <v>4831</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>6461</v>
+        <v>6886</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>3675</v>
+        <v>4339</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>3538</v>
+        <v>3323</v>
       </c>
       <c r="G27" s="8">
         <f>D27/1000</f>
@@ -1422,10 +1422,10 @@
         <v>5515</v>
       </c>
       <c r="D28" s="14" t="n">
-        <v>6456</v>
+        <v>6825</v>
       </c>
       <c r="E28" s="14" t="n">
-        <v>4333</v>
+        <v>4387</v>
       </c>
       <c r="F28" s="14" t="n">
         <v>2671</v>
@@ -1447,23 +1447,23 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>T-11</t>
+          <t>T-05</t>
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>303.27</v>
+        <v>176.55</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>7420</v>
+        <v>7594</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>6274</v>
+        <v>6818</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>3141</v>
+        <v>3711</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>2827</v>
+        <v>3538</v>
       </c>
       <c r="G29" s="8">
         <f>D29/1000</f>
@@ -1482,23 +1482,23 @@
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>T-25</t>
+          <t>T-11</t>
         </is>
       </c>
       <c r="B30" s="12" t="n">
-        <v>128.42</v>
+        <v>303.27</v>
       </c>
       <c r="C30" s="13" t="n">
-        <v>6551</v>
+        <v>7420</v>
       </c>
       <c r="D30" s="14" t="n">
-        <v>5892</v>
+        <v>6409</v>
       </c>
       <c r="E30" s="14" t="n">
-        <v>3042</v>
+        <v>3180</v>
       </c>
       <c r="F30" s="14" t="n">
-        <v>2542</v>
+        <v>2827</v>
       </c>
       <c r="G30" s="15">
         <f>D30/1000</f>
@@ -1527,7 +1527,7 @@
         <v>5556</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>5853</v>
+        <v>6129</v>
       </c>
       <c r="E31" s="7" t="n">
         <v>3323</v>
@@ -1562,10 +1562,10 @@
         <v>3095</v>
       </c>
       <c r="D32" s="14" t="n">
-        <v>5817</v>
+        <v>6032</v>
       </c>
       <c r="E32" s="14" t="n">
-        <v>4281</v>
+        <v>4337</v>
       </c>
       <c r="F32" s="14" t="n">
         <v>3321</v>
@@ -1585,60 +1585,60 @@
       <c r="J32" s="17" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>T-29B</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="n">
-        <v>115.08</v>
-      </c>
-      <c r="C33" s="6" t="n">
-        <v>5656</v>
-      </c>
-      <c r="D33" s="7" t="n">
-        <v>5599</v>
-      </c>
-      <c r="E33" s="7" t="n">
-        <v>2881</v>
-      </c>
-      <c r="F33" s="7" t="n">
-        <v>2262</v>
-      </c>
-      <c r="G33" s="8">
+      <c r="A33" s="18" t="inlineStr">
+        <is>
+          <t>T-23</t>
+        </is>
+      </c>
+      <c r="B33" s="19" t="n">
+        <v>249.78</v>
+      </c>
+      <c r="C33" s="20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="D33" s="21" t="n">
+        <v>5914</v>
+      </c>
+      <c r="E33" s="21" t="n">
+        <v>2388</v>
+      </c>
+      <c r="F33" s="21" t="n">
+        <v>1605</v>
+      </c>
+      <c r="G33" s="22">
         <f>D33/1000</f>
         <v/>
       </c>
-      <c r="H33" s="8">
+      <c r="H33" s="22">
         <f>E33/1000</f>
         <v/>
       </c>
-      <c r="I33" s="9">
+      <c r="I33" s="23">
         <f>IFERROR(D33/F33,"")</f>
         <v/>
       </c>
-      <c r="J33" s="10" t="inlineStr"/>
+      <c r="J33" s="24" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>T-19</t>
+          <t>T-29B</t>
         </is>
       </c>
       <c r="B34" s="12" t="n">
-        <v>207.35</v>
+        <v>115.08</v>
       </c>
       <c r="C34" s="13" t="n">
-        <v>5781</v>
+        <v>5656</v>
       </c>
       <c r="D34" s="14" t="n">
-        <v>5545</v>
+        <v>5656</v>
       </c>
       <c r="E34" s="14" t="n">
-        <v>2671</v>
+        <v>2939</v>
       </c>
       <c r="F34" s="14" t="n">
-        <v>2643</v>
+        <v>2262</v>
       </c>
       <c r="G34" s="15">
         <f>D34/1000</f>
@@ -1655,39 +1655,39 @@
       <c r="J34" s="17" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="inlineStr">
-        <is>
-          <t>T-23</t>
-        </is>
-      </c>
-      <c r="B35" s="19" t="n">
-        <v>249.78</v>
-      </c>
-      <c r="C35" s="20" t="n">
-        <v>6425</v>
-      </c>
-      <c r="D35" s="21" t="n">
-        <v>5435</v>
-      </c>
-      <c r="E35" s="21" t="n">
-        <v>2381</v>
-      </c>
-      <c r="F35" s="21" t="n">
-        <v>1605</v>
-      </c>
-      <c r="G35" s="22">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>T-19</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>207.35</v>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>5781</v>
+      </c>
+      <c r="D35" s="7" t="n">
+        <v>5583</v>
+      </c>
+      <c r="E35" s="7" t="n">
+        <v>2673</v>
+      </c>
+      <c r="F35" s="7" t="n">
+        <v>2643</v>
+      </c>
+      <c r="G35" s="8">
         <f>D35/1000</f>
         <v/>
       </c>
-      <c r="H35" s="22">
+      <c r="H35" s="8">
         <f>E35/1000</f>
         <v/>
       </c>
-      <c r="I35" s="23">
+      <c r="I35" s="9">
         <f>IFERROR(D35/F35,"")</f>
         <v/>
       </c>
-      <c r="J35" s="24" t="inlineStr"/>
+      <c r="J35" s="10" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="18" t="inlineStr">
@@ -1702,10 +1702,10 @@
         <v>5457</v>
       </c>
       <c r="D36" s="21" t="n">
-        <v>5247</v>
+        <v>5323</v>
       </c>
       <c r="E36" s="21" t="n">
-        <v>2566</v>
+        <v>2605</v>
       </c>
       <c r="F36" s="21" t="n">
         <v>1631</v>
@@ -1725,95 +1725,95 @@
       <c r="J36" s="24" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>T-16</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="n">
-        <v>113.43</v>
-      </c>
-      <c r="C37" s="6" t="n">
-        <v>4317</v>
-      </c>
-      <c r="D37" s="7" t="n">
-        <v>4758</v>
-      </c>
-      <c r="E37" s="7" t="n">
-        <v>3102</v>
-      </c>
-      <c r="F37" s="7" t="n">
-        <v>2713</v>
-      </c>
-      <c r="G37" s="8">
+      <c r="A37" s="18" t="inlineStr">
+        <is>
+          <t>T-18</t>
+        </is>
+      </c>
+      <c r="B37" s="19" t="n">
+        <v>265.83</v>
+      </c>
+      <c r="C37" s="20" t="n">
+        <v>6634</v>
+      </c>
+      <c r="D37" s="21" t="n">
+        <v>4980</v>
+      </c>
+      <c r="E37" s="21" t="n">
+        <v>1256</v>
+      </c>
+      <c r="F37" s="21" t="n">
+        <v>1241</v>
+      </c>
+      <c r="G37" s="22">
         <f>D37/1000</f>
         <v/>
       </c>
-      <c r="H37" s="8">
+      <c r="H37" s="22">
         <f>E37/1000</f>
         <v/>
       </c>
-      <c r="I37" s="9">
+      <c r="I37" s="23">
         <f>IFERROR(D37/F37,"")</f>
         <v/>
       </c>
-      <c r="J37" s="10" t="inlineStr"/>
+      <c r="J37" s="24" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="inlineStr">
-        <is>
-          <t>T-18</t>
-        </is>
-      </c>
-      <c r="B38" s="19" t="n">
-        <v>265.83</v>
-      </c>
-      <c r="C38" s="20" t="n">
-        <v>6634</v>
-      </c>
-      <c r="D38" s="21" t="n">
-        <v>4751</v>
-      </c>
-      <c r="E38" s="21" t="n">
-        <v>1242</v>
-      </c>
-      <c r="F38" s="21" t="n">
-        <v>1241</v>
-      </c>
-      <c r="G38" s="22">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>T-29 C</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="C38" s="13" t="n">
+        <v>3375</v>
+      </c>
+      <c r="D38" s="14" t="n">
+        <v>4934</v>
+      </c>
+      <c r="E38" s="14" t="n">
+        <v>2927</v>
+      </c>
+      <c r="F38" s="14" t="n">
+        <v>2251</v>
+      </c>
+      <c r="G38" s="15">
         <f>D38/1000</f>
         <v/>
       </c>
-      <c r="H38" s="22">
+      <c r="H38" s="15">
         <f>E38/1000</f>
         <v/>
       </c>
-      <c r="I38" s="23">
+      <c r="I38" s="16">
         <f>IFERROR(D38/F38,"")</f>
         <v/>
       </c>
-      <c r="J38" s="24" t="inlineStr"/>
+      <c r="J38" s="17" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>T-29 C</t>
+          <t>T-16</t>
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>23</v>
+        <v>113.43</v>
       </c>
       <c r="C39" s="6" t="n">
-        <v>3375</v>
+        <v>4317</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>4544</v>
+        <v>4781</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>2869</v>
+        <v>3121</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>2251</v>
+        <v>2713</v>
       </c>
       <c r="G39" s="8">
         <f>D39/1000</f>
@@ -1832,23 +1832,23 @@
     <row r="40">
       <c r="A40" s="18" t="inlineStr">
         <is>
-          <t>T-20</t>
+          <t>T-22</t>
         </is>
       </c>
       <c r="B40" s="19" t="n">
-        <v>240.55</v>
+        <v>268.29</v>
       </c>
       <c r="C40" s="20" t="n">
-        <v>9293</v>
+        <v>6666</v>
       </c>
       <c r="D40" s="21" t="n">
-        <v>4474</v>
+        <v>4507</v>
       </c>
       <c r="E40" s="21" t="n">
-        <v>1242</v>
+        <v>1012</v>
       </c>
       <c r="F40" s="21" t="n">
-        <v>1215</v>
+        <v>954</v>
       </c>
       <c r="G40" s="22">
         <f>D40/1000</f>
@@ -1867,23 +1867,23 @@
     <row r="41">
       <c r="A41" s="18" t="inlineStr">
         <is>
-          <t>T-22</t>
+          <t>T-20</t>
         </is>
       </c>
       <c r="B41" s="19" t="n">
-        <v>268.29</v>
+        <v>240.55</v>
       </c>
       <c r="C41" s="20" t="n">
-        <v>6666</v>
+        <v>9293</v>
       </c>
       <c r="D41" s="21" t="n">
-        <v>4255</v>
+        <v>4479</v>
       </c>
       <c r="E41" s="21" t="n">
-        <v>1011</v>
+        <v>1256</v>
       </c>
       <c r="F41" s="21" t="n">
-        <v>954</v>
+        <v>1215</v>
       </c>
       <c r="G41" s="22">
         <f>D41/1000</f>
@@ -1912,7 +1912,7 @@
         <v>10087</v>
       </c>
       <c r="D42" s="21" t="n">
-        <v>3811</v>
+        <v>4081</v>
       </c>
       <c r="E42" s="21" t="n">
         <v>44</v>
@@ -1947,7 +1947,7 @@
         <v>5029</v>
       </c>
       <c r="D43" s="21" t="n">
-        <v>2439</v>
+        <v>2467</v>
       </c>
       <c r="E43" s="21" t="n">
         <v>222</v>
@@ -1982,7 +1982,7 @@
         <v>2922</v>
       </c>
       <c r="D44" s="21" t="n">
-        <v>1500</v>
+        <v>1879</v>
       </c>
       <c r="E44" s="21" t="n">
         <v>62</v>

--- a/FAZENDA_PROMISSÃO_distancias.xlsx
+++ b/FAZENDA_PROMISSÃO_distancias.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhao\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E662922B-E2EE-4F29-B69E-F424C1E49A65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9593145D-7C2C-4F7A-813B-3E4CC34F48F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34755" yWindow="2610" windowWidth="17625" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1884" yWindow="1884" windowWidth="14100" windowHeight="9792" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Distâncias" sheetId="1" r:id="rId1"/>

--- a/FAZENDA_PROMISSÃO_distancias.xlsx
+++ b/FAZENDA_PROMISSÃO_distancias.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9593145D-7C2C-4F7A-813B-3E4CC34F48F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F3A5B14-6954-40D2-9EA3-A8523AB870AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1884" yWindow="1884" windowWidth="14100" windowHeight="9792" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -111,6 +111,15 @@
     <t>T-29A</t>
   </si>
   <si>
+    <t>T-05</t>
+  </si>
+  <si>
+    <t>T-06</t>
+  </si>
+  <si>
+    <t>T-11</t>
+  </si>
+  <si>
     <t>T-30C</t>
   </si>
   <si>
@@ -120,18 +129,12 @@
     <t>T-03</t>
   </si>
   <si>
-    <t>T-06</t>
-  </si>
-  <si>
     <t>T-29B</t>
   </si>
   <si>
     <t>T-04</t>
   </si>
   <si>
-    <t>T-05</t>
-  </si>
-  <si>
     <t>T-12</t>
   </si>
   <si>
@@ -144,22 +147,25 @@
     <t>T-24</t>
   </si>
   <si>
+    <t>T-10</t>
+  </si>
+  <si>
+    <t>T-26A</t>
+  </si>
+  <si>
+    <t>T-26</t>
+  </si>
+  <si>
+    <t>T-09</t>
+  </si>
+  <si>
+    <t>T-20</t>
+  </si>
+  <si>
     <t>T-25</t>
   </si>
   <si>
-    <t>T-26A</t>
-  </si>
-  <si>
-    <t>T-10</t>
-  </si>
-  <si>
-    <t>T-11</t>
-  </si>
-  <si>
-    <t>T-26</t>
-  </si>
-  <si>
-    <t>T-09</t>
+    <t>T-18</t>
   </si>
   <si>
     <t>T-14</t>
@@ -172,12 +178,6 @@
   </si>
   <si>
     <t>T-19</t>
-  </si>
-  <si>
-    <t>T-18</t>
-  </si>
-  <si>
-    <t>T-20</t>
   </si>
   <si>
     <t>T-16</t>
@@ -1012,7 +1012,7 @@
         <v>15117</v>
       </c>
       <c r="E12" s="14">
-        <v>11274</v>
+        <v>12119</v>
       </c>
       <c r="F12" s="14">
         <v>7665</v>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="H12" s="15">
         <f t="shared" si="1"/>
-        <v>11.273999999999999</v>
+        <v>12.119</v>
       </c>
       <c r="I12" s="16">
         <f t="shared" si="2"/>
@@ -1078,7 +1078,7 @@
         <v>14943</v>
       </c>
       <c r="E14" s="14">
-        <v>7812</v>
+        <v>7832</v>
       </c>
       <c r="F14" s="14">
         <v>6977</v>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="H14" s="15">
         <f t="shared" si="1"/>
-        <v>7.8120000000000003</v>
+        <v>7.8319999999999999</v>
       </c>
       <c r="I14" s="16">
         <f t="shared" si="2"/>
@@ -1111,7 +1111,7 @@
         <v>14436</v>
       </c>
       <c r="E15" s="21">
-        <v>7752</v>
+        <v>8917</v>
       </c>
       <c r="F15" s="21">
         <v>6496</v>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="H15" s="22">
         <f t="shared" si="1"/>
-        <v>7.7519999999999998</v>
+        <v>8.9169999999999998</v>
       </c>
       <c r="I15" s="23">
         <f t="shared" si="2"/>
@@ -1144,7 +1144,7 @@
         <v>14436</v>
       </c>
       <c r="E16" s="14">
-        <v>6369</v>
+        <v>7429</v>
       </c>
       <c r="F16" s="14">
         <v>5666</v>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="H16" s="15">
         <f t="shared" si="1"/>
-        <v>6.3689999999999998</v>
+        <v>7.4290000000000003</v>
       </c>
       <c r="I16" s="16">
         <f t="shared" si="2"/>
@@ -1201,155 +1201,155 @@
         <v>25</v>
       </c>
       <c r="B18" s="5">
+        <v>176.55</v>
+      </c>
+      <c r="C18" s="6">
+        <v>7594</v>
+      </c>
+      <c r="D18" s="7">
+        <v>12713</v>
+      </c>
+      <c r="E18" s="7">
+        <v>4778</v>
+      </c>
+      <c r="F18" s="7">
+        <v>3538</v>
+      </c>
+      <c r="G18" s="8">
+        <f t="shared" si="0"/>
+        <v>12.712999999999999</v>
+      </c>
+      <c r="H18" s="8">
+        <f t="shared" si="1"/>
+        <v>4.7779999999999996</v>
+      </c>
+      <c r="I18" s="9">
+        <f t="shared" si="2"/>
+        <v>3.5932730356133407</v>
+      </c>
+      <c r="J18" s="10"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="19">
+        <v>211.14</v>
+      </c>
+      <c r="C19" s="20">
+        <v>5814</v>
+      </c>
+      <c r="D19" s="21">
+        <v>12713</v>
+      </c>
+      <c r="E19" s="21">
+        <v>6012</v>
+      </c>
+      <c r="F19" s="21">
+        <v>4461</v>
+      </c>
+      <c r="G19" s="22">
+        <f t="shared" si="0"/>
+        <v>12.712999999999999</v>
+      </c>
+      <c r="H19" s="22">
+        <f t="shared" si="1"/>
+        <v>6.0119999999999996</v>
+      </c>
+      <c r="I19" s="23">
+        <f t="shared" si="2"/>
+        <v>2.8498094597623851</v>
+      </c>
+      <c r="J19" s="24"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="5">
+        <v>303.27</v>
+      </c>
+      <c r="C20" s="6">
+        <v>7420</v>
+      </c>
+      <c r="D20" s="7">
+        <v>12242</v>
+      </c>
+      <c r="E20" s="7">
+        <v>3207</v>
+      </c>
+      <c r="F20" s="7">
+        <v>2827</v>
+      </c>
+      <c r="G20" s="8">
+        <f t="shared" si="0"/>
+        <v>12.242000000000001</v>
+      </c>
+      <c r="H20" s="8">
+        <f t="shared" si="1"/>
+        <v>3.2069999999999999</v>
+      </c>
+      <c r="I20" s="9">
+        <f t="shared" si="2"/>
+        <v>4.3303855677396532</v>
+      </c>
+      <c r="J20" s="10"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="5">
         <v>53.2</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C21" s="6">
         <v>3095</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D21" s="7">
         <v>12162</v>
       </c>
-      <c r="E18" s="7">
+      <c r="E21" s="7">
         <v>7250</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F21" s="7">
         <v>3321</v>
       </c>
-      <c r="G18" s="8">
+      <c r="G21" s="8">
         <f t="shared" si="0"/>
         <v>12.162000000000001</v>
       </c>
-      <c r="H18" s="8">
+      <c r="H21" s="8">
         <f t="shared" si="1"/>
         <v>7.25</v>
       </c>
-      <c r="I18" s="9">
+      <c r="I21" s="9">
         <f t="shared" si="2"/>
         <v>3.6621499548328815</v>
       </c>
-      <c r="J18" s="10"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="5">
-        <v>23</v>
-      </c>
-      <c r="C19" s="6">
-        <v>3375</v>
-      </c>
-      <c r="D19" s="7">
-        <v>12115</v>
-      </c>
-      <c r="E19" s="7">
-        <v>5852</v>
-      </c>
-      <c r="F19" s="7">
-        <v>2251</v>
-      </c>
-      <c r="G19" s="8">
-        <f t="shared" si="0"/>
-        <v>12.115</v>
-      </c>
-      <c r="H19" s="8">
-        <f t="shared" si="1"/>
-        <v>5.8520000000000003</v>
-      </c>
-      <c r="I19" s="9">
-        <f t="shared" si="2"/>
-        <v>5.3820524211461569</v>
-      </c>
-      <c r="J19" s="10"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="12">
-        <v>215.16</v>
-      </c>
-      <c r="C20" s="13">
-        <v>5870</v>
-      </c>
-      <c r="D20" s="14">
-        <v>11957</v>
-      </c>
-      <c r="E20" s="14">
-        <v>7752</v>
-      </c>
-      <c r="F20" s="14">
-        <v>5463</v>
-      </c>
-      <c r="G20" s="15">
-        <f t="shared" si="0"/>
-        <v>11.957000000000001</v>
-      </c>
-      <c r="H20" s="15">
-        <f t="shared" si="1"/>
-        <v>7.7519999999999998</v>
-      </c>
-      <c r="I20" s="16">
-        <f t="shared" si="2"/>
-        <v>2.18872414424309</v>
-      </c>
-      <c r="J20" s="17"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" s="19">
-        <v>211.14</v>
-      </c>
-      <c r="C21" s="20">
-        <v>5814</v>
-      </c>
-      <c r="D21" s="21">
-        <v>11957</v>
-      </c>
-      <c r="E21" s="21">
-        <v>4952</v>
-      </c>
-      <c r="F21" s="21">
-        <v>4461</v>
-      </c>
-      <c r="G21" s="22">
-        <f t="shared" si="0"/>
-        <v>11.957000000000001</v>
-      </c>
-      <c r="H21" s="22">
-        <f t="shared" si="1"/>
-        <v>4.952</v>
-      </c>
-      <c r="I21" s="23">
-        <f t="shared" si="2"/>
-        <v>2.6803407307778526</v>
-      </c>
-      <c r="J21" s="24"/>
+      <c r="J21" s="10"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>29</v>
       </c>
       <c r="B22" s="5">
-        <v>115.08</v>
+        <v>23</v>
       </c>
       <c r="C22" s="6">
-        <v>5656</v>
+        <v>3375</v>
       </c>
       <c r="D22" s="7">
-        <v>11756</v>
+        <v>12115</v>
       </c>
       <c r="E22" s="7">
         <v>5852</v>
       </c>
       <c r="F22" s="7">
-        <v>2262</v>
+        <v>2251</v>
       </c>
       <c r="G22" s="8">
         <f t="shared" si="0"/>
-        <v>11.756</v>
+        <v>12.115</v>
       </c>
       <c r="H22" s="8">
         <f t="shared" si="1"/>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="I22" s="9">
         <f t="shared" si="2"/>
-        <v>5.1971706454465076</v>
+        <v>5.3820524211461569</v>
       </c>
       <c r="J22" s="10"/>
     </row>
@@ -1366,31 +1366,31 @@
         <v>30</v>
       </c>
       <c r="B23" s="19">
-        <v>222.45</v>
+        <v>215.16</v>
       </c>
       <c r="C23" s="20">
-        <v>5898</v>
+        <v>5870</v>
       </c>
       <c r="D23" s="21">
-        <v>11456</v>
+        <v>11957</v>
       </c>
       <c r="E23" s="21">
-        <v>6283</v>
+        <v>8917</v>
       </c>
       <c r="F23" s="21">
-        <v>4632</v>
+        <v>5463</v>
       </c>
       <c r="G23" s="22">
         <f t="shared" si="0"/>
-        <v>11.456</v>
+        <v>11.957000000000001</v>
       </c>
       <c r="H23" s="22">
         <f t="shared" si="1"/>
-        <v>6.2830000000000004</v>
+        <v>8.9169999999999998</v>
       </c>
       <c r="I23" s="23">
         <f t="shared" si="2"/>
-        <v>2.4732297063903284</v>
+        <v>2.18872414424309</v>
       </c>
       <c r="J23" s="24"/>
     </row>
@@ -1399,151 +1399,151 @@
         <v>31</v>
       </c>
       <c r="B24" s="5">
-        <v>176.55</v>
+        <v>115.08</v>
       </c>
       <c r="C24" s="6">
-        <v>7594</v>
+        <v>5656</v>
       </c>
       <c r="D24" s="7">
+        <v>11756</v>
+      </c>
+      <c r="E24" s="7">
+        <v>5852</v>
+      </c>
+      <c r="F24" s="7">
+        <v>2262</v>
+      </c>
+      <c r="G24" s="8">
+        <f t="shared" si="0"/>
+        <v>11.756</v>
+      </c>
+      <c r="H24" s="8">
+        <f t="shared" si="1"/>
+        <v>5.8520000000000003</v>
+      </c>
+      <c r="I24" s="9">
+        <f t="shared" si="2"/>
+        <v>5.1971706454465076</v>
+      </c>
+      <c r="J24" s="10"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="19">
+        <v>222.45</v>
+      </c>
+      <c r="C25" s="20">
+        <v>5898</v>
+      </c>
+      <c r="D25" s="21">
         <v>11456</v>
       </c>
-      <c r="E24" s="7">
-        <v>3820</v>
-      </c>
-      <c r="F24" s="7">
-        <v>3538</v>
-      </c>
-      <c r="G24" s="8">
+      <c r="E25" s="21">
+        <v>6283</v>
+      </c>
+      <c r="F25" s="21">
+        <v>4632</v>
+      </c>
+      <c r="G25" s="22">
         <f t="shared" si="0"/>
         <v>11.456</v>
       </c>
-      <c r="H24" s="8">
-        <f t="shared" si="1"/>
-        <v>3.82</v>
-      </c>
-      <c r="I24" s="9">
-        <f t="shared" si="2"/>
-        <v>3.2379875635952517</v>
-      </c>
-      <c r="J24" s="10"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" s="5">
-        <v>196.2</v>
-      </c>
-      <c r="C25" s="6">
-        <v>5516</v>
-      </c>
-      <c r="D25" s="7">
-        <v>11418</v>
-      </c>
-      <c r="E25" s="7">
-        <v>4297</v>
-      </c>
-      <c r="F25" s="7">
-        <v>3785</v>
-      </c>
-      <c r="G25" s="8">
-        <f t="shared" si="0"/>
-        <v>11.417999999999999</v>
-      </c>
-      <c r="H25" s="8">
-        <f t="shared" si="1"/>
-        <v>4.2969999999999997</v>
-      </c>
-      <c r="I25" s="9">
-        <f t="shared" si="2"/>
-        <v>3.0166446499339497</v>
-      </c>
-      <c r="J25" s="10"/>
+      <c r="H25" s="22">
+        <f t="shared" si="1"/>
+        <v>6.2830000000000004</v>
+      </c>
+      <c r="I25" s="23">
+        <f t="shared" si="2"/>
+        <v>2.4732297063903284</v>
+      </c>
+      <c r="J25" s="24"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
         <v>33</v>
       </c>
       <c r="B26" s="12">
-        <v>198.71</v>
+        <v>196.2</v>
       </c>
       <c r="C26" s="13">
-        <v>5502</v>
+        <v>5516</v>
       </c>
       <c r="D26" s="14">
         <v>11247</v>
       </c>
       <c r="E26" s="14">
+        <v>4297</v>
+      </c>
+      <c r="F26" s="14">
+        <v>3785</v>
+      </c>
+      <c r="G26" s="15">
+        <f t="shared" si="0"/>
+        <v>11.247</v>
+      </c>
+      <c r="H26" s="15">
+        <f t="shared" si="1"/>
+        <v>4.2969999999999997</v>
+      </c>
+      <c r="I26" s="16">
+        <f t="shared" si="2"/>
+        <v>2.9714663143989433</v>
+      </c>
+      <c r="J26" s="17"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="19">
+        <v>198.71</v>
+      </c>
+      <c r="C27" s="20">
+        <v>5502</v>
+      </c>
+      <c r="D27" s="21">
+        <v>11247</v>
+      </c>
+      <c r="E27" s="21">
         <v>5920</v>
       </c>
-      <c r="F26" s="14">
+      <c r="F27" s="21">
         <v>4181</v>
       </c>
-      <c r="G26" s="15">
+      <c r="G27" s="22">
         <f t="shared" si="0"/>
         <v>11.247</v>
       </c>
-      <c r="H26" s="15">
+      <c r="H27" s="22">
         <f t="shared" si="1"/>
         <v>5.92</v>
       </c>
-      <c r="I26" s="16">
+      <c r="I27" s="23">
         <f t="shared" si="2"/>
         <v>2.6900263094953361</v>
       </c>
-      <c r="J26" s="17"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A27" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" s="5">
-        <v>249.78</v>
-      </c>
-      <c r="C27" s="6">
-        <v>6425</v>
-      </c>
-      <c r="D27" s="7">
-        <v>10250</v>
-      </c>
-      <c r="E27" s="7">
-        <v>2549</v>
-      </c>
-      <c r="F27" s="7">
-        <v>1605</v>
-      </c>
-      <c r="G27" s="8">
-        <f t="shared" si="0"/>
-        <v>10.25</v>
-      </c>
-      <c r="H27" s="8">
-        <f t="shared" si="1"/>
-        <v>2.5489999999999999</v>
-      </c>
-      <c r="I27" s="9">
-        <f t="shared" si="2"/>
-        <v>6.3862928348909653</v>
-      </c>
-      <c r="J27" s="10"/>
+      <c r="J27" s="24"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>35</v>
       </c>
       <c r="B28" s="5">
-        <v>313.18</v>
+        <v>249.78</v>
       </c>
       <c r="C28" s="6">
-        <v>7098</v>
+        <v>6425</v>
       </c>
       <c r="D28" s="7">
         <v>10250</v>
       </c>
       <c r="E28" s="7">
-        <v>4024</v>
+        <v>2549</v>
       </c>
       <c r="F28" s="7">
-        <v>2810</v>
+        <v>1605</v>
       </c>
       <c r="G28" s="8">
         <f t="shared" si="0"/>
@@ -1551,11 +1551,11 @@
       </c>
       <c r="H28" s="8">
         <f t="shared" si="1"/>
-        <v>4.024</v>
+        <v>2.5489999999999999</v>
       </c>
       <c r="I28" s="9">
         <f t="shared" si="2"/>
-        <v>3.6476868327402134</v>
+        <v>6.3862928348909653</v>
       </c>
       <c r="J28" s="10"/>
     </row>
@@ -1564,262 +1564,262 @@
         <v>36</v>
       </c>
       <c r="B29" s="5">
-        <v>128.41999999999999</v>
+        <v>313.18</v>
       </c>
       <c r="C29" s="6">
-        <v>6551</v>
+        <v>7098</v>
       </c>
       <c r="D29" s="7">
-        <v>10091</v>
+        <v>10250</v>
       </c>
       <c r="E29" s="7">
-        <v>4029</v>
+        <v>4024</v>
       </c>
       <c r="F29" s="7">
-        <v>2542</v>
+        <v>2810</v>
       </c>
       <c r="G29" s="8">
         <f t="shared" si="0"/>
-        <v>10.090999999999999</v>
+        <v>10.25</v>
       </c>
       <c r="H29" s="8">
         <f t="shared" si="1"/>
-        <v>4.0289999999999999</v>
+        <v>4.024</v>
       </c>
       <c r="I29" s="9">
         <f t="shared" si="2"/>
-        <v>3.9697088906372935</v>
+        <v>3.6476868327402134</v>
       </c>
       <c r="J29" s="10"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="B30" s="5">
+      <c r="B30" s="12">
+        <v>225.86</v>
+      </c>
+      <c r="C30" s="13">
+        <v>6836</v>
+      </c>
+      <c r="D30" s="14">
+        <v>10206</v>
+      </c>
+      <c r="E30" s="14">
+        <v>4371</v>
+      </c>
+      <c r="F30" s="14">
+        <v>3960</v>
+      </c>
+      <c r="G30" s="15">
+        <f t="shared" si="0"/>
+        <v>10.206</v>
+      </c>
+      <c r="H30" s="15">
+        <f t="shared" si="1"/>
+        <v>4.3710000000000004</v>
+      </c>
+      <c r="I30" s="16">
+        <f t="shared" si="2"/>
+        <v>2.5772727272727272</v>
+      </c>
+      <c r="J30" s="17"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A31" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="5">
         <v>127.51</v>
       </c>
-      <c r="C30" s="6">
+      <c r="C31" s="6">
         <v>5515</v>
       </c>
-      <c r="D30" s="7">
+      <c r="D31" s="7">
         <v>10040</v>
       </c>
-      <c r="E30" s="7">
+      <c r="E31" s="7">
         <v>7341</v>
       </c>
-      <c r="F30" s="7">
+      <c r="F31" s="7">
         <v>2671</v>
       </c>
-      <c r="G30" s="8">
+      <c r="G31" s="8">
         <f t="shared" si="0"/>
         <v>10.039999999999999</v>
       </c>
-      <c r="H30" s="8">
+      <c r="H31" s="8">
         <f t="shared" si="1"/>
         <v>7.3410000000000002</v>
       </c>
-      <c r="I30" s="9">
+      <c r="I31" s="9">
         <f t="shared" si="2"/>
         <v>3.7588918008236614</v>
       </c>
-      <c r="J30" s="10"/>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A31" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="19">
-        <v>225.86</v>
-      </c>
-      <c r="C31" s="20">
-        <v>6836</v>
-      </c>
-      <c r="D31" s="21">
-        <v>9146</v>
-      </c>
-      <c r="E31" s="21">
-        <v>4371</v>
-      </c>
-      <c r="F31" s="21">
-        <v>3960</v>
-      </c>
-      <c r="G31" s="22">
-        <f t="shared" si="0"/>
-        <v>9.1460000000000008</v>
-      </c>
-      <c r="H31" s="22">
-        <f t="shared" si="1"/>
-        <v>4.3710000000000004</v>
-      </c>
-      <c r="I31" s="23">
-        <f t="shared" si="2"/>
-        <v>2.3095959595959594</v>
-      </c>
-      <c r="J31" s="24"/>
+      <c r="J31" s="10"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>39</v>
       </c>
       <c r="B32" s="5">
-        <v>303.27</v>
+        <v>147.1</v>
       </c>
       <c r="C32" s="6">
-        <v>7420</v>
+        <v>5457</v>
       </c>
       <c r="D32" s="7">
-        <v>9146</v>
+        <v>9140</v>
       </c>
       <c r="E32" s="7">
-        <v>3207</v>
+        <v>5521</v>
       </c>
       <c r="F32" s="7">
-        <v>2827</v>
+        <v>1631</v>
       </c>
       <c r="G32" s="8">
         <f t="shared" si="0"/>
-        <v>9.1460000000000008</v>
+        <v>9.14</v>
       </c>
       <c r="H32" s="8">
         <f t="shared" si="1"/>
-        <v>3.2069999999999999</v>
+        <v>5.5209999999999999</v>
       </c>
       <c r="I32" s="9">
         <f t="shared" si="2"/>
-        <v>3.2352316943756634</v>
+        <v>5.6039239730226855</v>
       </c>
       <c r="J32" s="10"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A33" s="4" t="s">
+      <c r="A33" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="B33" s="5">
-        <v>147.1</v>
-      </c>
-      <c r="C33" s="6">
-        <v>5457</v>
-      </c>
-      <c r="D33" s="7">
-        <v>9140</v>
-      </c>
-      <c r="E33" s="7">
-        <v>5521</v>
-      </c>
-      <c r="F33" s="7">
-        <v>1631</v>
-      </c>
-      <c r="G33" s="8">
-        <f t="shared" si="0"/>
-        <v>9.14</v>
-      </c>
-      <c r="H33" s="8">
-        <f t="shared" si="1"/>
-        <v>5.5209999999999999</v>
-      </c>
-      <c r="I33" s="9">
-        <f t="shared" si="2"/>
-        <v>5.6039239730226855</v>
-      </c>
-      <c r="J33" s="10"/>
+      <c r="B33" s="19">
+        <v>136.16</v>
+      </c>
+      <c r="C33" s="20">
+        <v>5252</v>
+      </c>
+      <c r="D33" s="21">
+        <v>9095</v>
+      </c>
+      <c r="E33" s="21">
+        <v>5809</v>
+      </c>
+      <c r="F33" s="21">
+        <v>5369</v>
+      </c>
+      <c r="G33" s="22">
+        <f t="shared" si="0"/>
+        <v>9.0950000000000006</v>
+      </c>
+      <c r="H33" s="22">
+        <f t="shared" si="1"/>
+        <v>5.8090000000000002</v>
+      </c>
+      <c r="I33" s="23">
+        <f t="shared" si="2"/>
+        <v>1.6939839821195752</v>
+      </c>
+      <c r="J33" s="24"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A34" s="11" t="s">
+      <c r="A34" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B34" s="12">
-        <v>136.16</v>
-      </c>
-      <c r="C34" s="13">
-        <v>5252</v>
-      </c>
-      <c r="D34" s="14">
-        <v>9022</v>
-      </c>
-      <c r="E34" s="14">
-        <v>5809</v>
-      </c>
-      <c r="F34" s="14">
-        <v>5369</v>
-      </c>
-      <c r="G34" s="15">
-        <f t="shared" si="0"/>
-        <v>9.0220000000000002</v>
-      </c>
-      <c r="H34" s="15">
-        <f t="shared" si="1"/>
-        <v>5.8090000000000002</v>
-      </c>
-      <c r="I34" s="16">
-        <f t="shared" si="2"/>
-        <v>1.6803874092009685</v>
-      </c>
-      <c r="J34" s="17"/>
+      <c r="B34" s="5">
+        <v>240.55</v>
+      </c>
+      <c r="C34" s="6">
+        <v>9293</v>
+      </c>
+      <c r="D34" s="7">
+        <v>8130</v>
+      </c>
+      <c r="E34" s="7">
+        <v>1256</v>
+      </c>
+      <c r="F34" s="7">
+        <v>1215</v>
+      </c>
+      <c r="G34" s="8">
+        <f t="shared" si="0"/>
+        <v>8.1300000000000008</v>
+      </c>
+      <c r="H34" s="8">
+        <f t="shared" si="1"/>
+        <v>1.256</v>
+      </c>
+      <c r="I34" s="9">
+        <f t="shared" si="2"/>
+        <v>6.6913580246913584</v>
+      </c>
+      <c r="J34" s="10"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A35" s="18" t="s">
+      <c r="A35" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B35" s="19">
-        <v>180.97</v>
-      </c>
-      <c r="C35" s="20">
-        <v>5840</v>
-      </c>
-      <c r="D35" s="21">
-        <v>6962</v>
-      </c>
-      <c r="E35" s="21">
-        <v>4337</v>
-      </c>
-      <c r="F35" s="21">
-        <v>3349</v>
-      </c>
-      <c r="G35" s="22">
-        <f t="shared" si="0"/>
-        <v>6.9619999999999997</v>
-      </c>
-      <c r="H35" s="22">
-        <f t="shared" si="1"/>
-        <v>4.3369999999999997</v>
-      </c>
-      <c r="I35" s="23">
-        <f t="shared" si="2"/>
-        <v>2.0788295013436846</v>
-      </c>
-      <c r="J35" s="24"/>
+      <c r="B35" s="5">
+        <v>128.41999999999999</v>
+      </c>
+      <c r="C35" s="6">
+        <v>6551</v>
+      </c>
+      <c r="D35" s="7">
+        <v>8129</v>
+      </c>
+      <c r="E35" s="7">
+        <v>4029</v>
+      </c>
+      <c r="F35" s="7">
+        <v>2542</v>
+      </c>
+      <c r="G35" s="8">
+        <f t="shared" si="0"/>
+        <v>8.1289999999999996</v>
+      </c>
+      <c r="H35" s="8">
+        <f t="shared" si="1"/>
+        <v>4.0289999999999999</v>
+      </c>
+      <c r="I35" s="9">
+        <f t="shared" si="2"/>
+        <v>3.1978756884343036</v>
+      </c>
+      <c r="J35" s="10"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>43</v>
       </c>
       <c r="B36" s="5">
-        <v>268.29000000000002</v>
+        <v>265.83</v>
       </c>
       <c r="C36" s="6">
-        <v>6666</v>
+        <v>6634</v>
       </c>
       <c r="D36" s="7">
-        <v>6786</v>
+        <v>7087</v>
       </c>
       <c r="E36" s="7">
-        <v>1012</v>
+        <v>1256</v>
       </c>
       <c r="F36" s="7">
-        <v>954</v>
+        <v>1241</v>
       </c>
       <c r="G36" s="8">
         <f t="shared" si="0"/>
-        <v>6.7859999999999996</v>
+        <v>7.0869999999999997</v>
       </c>
       <c r="H36" s="8">
         <f t="shared" si="1"/>
-        <v>1.012</v>
+        <v>1.256</v>
       </c>
       <c r="I36" s="9">
         <f t="shared" si="2"/>
-        <v>7.1132075471698117</v>
+        <v>5.71071716357776</v>
       </c>
       <c r="J36" s="10"/>
     </row>
@@ -1828,132 +1828,132 @@
         <v>44</v>
       </c>
       <c r="B37" s="19">
+        <v>180.97</v>
+      </c>
+      <c r="C37" s="20">
+        <v>5840</v>
+      </c>
+      <c r="D37" s="21">
+        <v>6962</v>
+      </c>
+      <c r="E37" s="21">
+        <v>4337</v>
+      </c>
+      <c r="F37" s="21">
+        <v>3349</v>
+      </c>
+      <c r="G37" s="22">
+        <f t="shared" si="0"/>
+        <v>6.9619999999999997</v>
+      </c>
+      <c r="H37" s="22">
+        <f t="shared" si="1"/>
+        <v>4.3369999999999997</v>
+      </c>
+      <c r="I37" s="23">
+        <f t="shared" si="2"/>
+        <v>2.0788295013436846</v>
+      </c>
+      <c r="J37" s="24"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A38" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" s="5">
+        <v>268.29000000000002</v>
+      </c>
+      <c r="C38" s="6">
+        <v>6666</v>
+      </c>
+      <c r="D38" s="7">
+        <v>6786</v>
+      </c>
+      <c r="E38" s="7">
+        <v>1012</v>
+      </c>
+      <c r="F38" s="7">
+        <v>954</v>
+      </c>
+      <c r="G38" s="8">
+        <f t="shared" si="0"/>
+        <v>6.7859999999999996</v>
+      </c>
+      <c r="H38" s="8">
+        <f t="shared" si="1"/>
+        <v>1.012</v>
+      </c>
+      <c r="I38" s="9">
+        <f t="shared" si="2"/>
+        <v>7.1132075471698117</v>
+      </c>
+      <c r="J38" s="10"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A39" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" s="19">
         <v>189.27</v>
       </c>
-      <c r="C37" s="20">
+      <c r="C39" s="20">
         <v>5556</v>
       </c>
-      <c r="D37" s="21">
+      <c r="D39" s="21">
         <v>6420</v>
       </c>
-      <c r="E37" s="21">
+      <c r="E39" s="21">
         <v>3358</v>
       </c>
-      <c r="F37" s="21">
+      <c r="F39" s="21">
         <v>2759</v>
       </c>
-      <c r="G37" s="22">
+      <c r="G39" s="22">
         <f t="shared" si="0"/>
         <v>6.42</v>
       </c>
-      <c r="H37" s="22">
+      <c r="H39" s="22">
         <f t="shared" si="1"/>
         <v>3.3580000000000001</v>
       </c>
-      <c r="I37" s="23">
+      <c r="I39" s="23">
         <f t="shared" si="2"/>
         <v>2.326930047118521</v>
       </c>
-      <c r="J37" s="24"/>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A38" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="B38" s="12">
+      <c r="J39" s="24"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A40" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40" s="12">
         <v>207.35</v>
       </c>
-      <c r="C38" s="13">
+      <c r="C40" s="13">
         <v>5781</v>
       </c>
-      <c r="D38" s="14">
+      <c r="D40" s="14">
         <v>5718</v>
       </c>
-      <c r="E38" s="14">
+      <c r="E40" s="14">
         <v>2673</v>
       </c>
-      <c r="F38" s="14">
+      <c r="F40" s="14">
         <v>2643</v>
       </c>
-      <c r="G38" s="15">
+      <c r="G40" s="15">
         <f t="shared" si="0"/>
         <v>5.718</v>
       </c>
-      <c r="H38" s="15">
+      <c r="H40" s="15">
         <f t="shared" si="1"/>
         <v>2.673</v>
       </c>
-      <c r="I38" s="16">
+      <c r="I40" s="16">
         <f t="shared" si="2"/>
         <v>2.1634506242905789</v>
       </c>
-      <c r="J38" s="17"/>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A39" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B39" s="5">
-        <v>265.83</v>
-      </c>
-      <c r="C39" s="6">
-        <v>6634</v>
-      </c>
-      <c r="D39" s="7">
-        <v>5234</v>
-      </c>
-      <c r="E39" s="7">
-        <v>1256</v>
-      </c>
-      <c r="F39" s="7">
-        <v>1241</v>
-      </c>
-      <c r="G39" s="8">
-        <f t="shared" si="0"/>
-        <v>5.234</v>
-      </c>
-      <c r="H39" s="8">
-        <f t="shared" si="1"/>
-        <v>1.256</v>
-      </c>
-      <c r="I39" s="9">
-        <f t="shared" si="2"/>
-        <v>4.217566478646253</v>
-      </c>
-      <c r="J39" s="10"/>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A40" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B40" s="5">
-        <v>240.55</v>
-      </c>
-      <c r="C40" s="6">
-        <v>9293</v>
-      </c>
-      <c r="D40" s="7">
-        <v>5163</v>
-      </c>
-      <c r="E40" s="7">
-        <v>1256</v>
-      </c>
-      <c r="F40" s="7">
-        <v>1215</v>
-      </c>
-      <c r="G40" s="8">
-        <f t="shared" si="0"/>
-        <v>5.1630000000000003</v>
-      </c>
-      <c r="H40" s="8">
-        <f t="shared" si="1"/>
-        <v>1.256</v>
-      </c>
-      <c r="I40" s="9">
-        <f t="shared" si="2"/>
-        <v>4.2493827160493831</v>
-      </c>
-      <c r="J40" s="10"/>
+      <c r="J40" s="17"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="18" t="s">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="B46" s="26">
         <f>SUM(B5:B44)</f>
-        <v>7068.94</v>
+        <v>7068.9400000000005</v>
       </c>
       <c r="D46" s="27">
         <f>MAX(D5:D44)</f>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="I46" s="29">
         <f>IFERROR(AVERAGE(I5:I44),"")</f>
-        <v>6.9302081942559486</v>
+        <v>7.0556905910258845</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">

--- a/FAZENDA_PROMISSÃO_distancias.xlsx
+++ b/FAZENDA_PROMISSÃO_distancias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F3A5B14-6954-40D2-9EA3-A8523AB870AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5174EB2-DB4D-4CEE-833A-7208E4F7E6CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1884" yWindow="1884" windowWidth="14100" windowHeight="9792" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Distâncias" sheetId="1" r:id="rId1"/>
@@ -72,115 +72,115 @@
     <t>Observação</t>
   </si>
   <si>
+    <t>T-28</t>
+  </si>
+  <si>
+    <t>T-02</t>
+  </si>
+  <si>
+    <t>T-31A</t>
+  </si>
+  <si>
+    <t>T-32A</t>
+  </si>
+  <si>
+    <t>T-03</t>
+  </si>
+  <si>
+    <t>T-09</t>
+  </si>
+  <si>
+    <t>T-05</t>
+  </si>
+  <si>
+    <t>T-11</t>
+  </si>
+  <si>
+    <t>T-10</t>
+  </si>
+  <si>
+    <t>T-32</t>
+  </si>
+  <si>
+    <t>T-06</t>
+  </si>
+  <si>
+    <t>T-07</t>
+  </si>
+  <si>
     <t>T-27</t>
   </si>
   <si>
-    <t>T-28</t>
+    <t>T-30A</t>
+  </si>
+  <si>
+    <t>T-26A</t>
+  </si>
+  <si>
+    <t>T-29A</t>
   </si>
   <si>
     <t>T-31B</t>
   </si>
   <si>
-    <t>T-31A</t>
+    <t>T-26</t>
+  </si>
+  <si>
+    <t>T-08</t>
   </si>
   <si>
     <t>T-30B</t>
   </si>
   <si>
-    <t>T-30A</t>
-  </si>
-  <si>
-    <t>T-32</t>
+    <t>T-30C</t>
+  </si>
+  <si>
+    <t>T-22</t>
+  </si>
+  <si>
+    <t>T-29B</t>
+  </si>
+  <si>
+    <t>T-29 C</t>
   </si>
   <si>
     <t>T-01</t>
   </si>
   <si>
-    <t>T-32A</t>
-  </si>
-  <si>
-    <t>T-08</t>
-  </si>
-  <si>
-    <t>T-02</t>
-  </si>
-  <si>
-    <t>T-07</t>
-  </si>
-  <si>
-    <t>T-29A</t>
-  </si>
-  <si>
-    <t>T-05</t>
-  </si>
-  <si>
-    <t>T-06</t>
-  </si>
-  <si>
-    <t>T-11</t>
-  </si>
-  <si>
-    <t>T-30C</t>
-  </si>
-  <si>
-    <t>T-29 C</t>
-  </si>
-  <si>
-    <t>T-03</t>
-  </si>
-  <si>
-    <t>T-29B</t>
+    <t>T-23</t>
+  </si>
+  <si>
+    <t>T-24</t>
+  </si>
+  <si>
+    <t>T-13</t>
   </si>
   <si>
     <t>T-04</t>
   </si>
   <si>
+    <t>T-20</t>
+  </si>
+  <si>
+    <t>T-25</t>
+  </si>
+  <si>
+    <t>T-14</t>
+  </si>
+  <si>
+    <t>T-15</t>
+  </si>
+  <si>
     <t>T-12</t>
   </si>
   <si>
-    <t>T-13</t>
-  </si>
-  <si>
-    <t>T-23</t>
-  </si>
-  <si>
-    <t>T-24</t>
-  </si>
-  <si>
-    <t>T-10</t>
-  </si>
-  <si>
-    <t>T-26A</t>
-  </si>
-  <si>
-    <t>T-26</t>
-  </si>
-  <si>
-    <t>T-09</t>
-  </si>
-  <si>
-    <t>T-20</t>
-  </si>
-  <si>
-    <t>T-25</t>
+    <t>T-19</t>
+  </si>
+  <si>
+    <t>T-16</t>
   </si>
   <si>
     <t>T-18</t>
-  </si>
-  <si>
-    <t>T-14</t>
-  </si>
-  <si>
-    <t>T-22</t>
-  </si>
-  <si>
-    <t>T-15</t>
-  </si>
-  <si>
-    <t>T-19</t>
-  </si>
-  <si>
-    <t>T-16</t>
   </si>
   <si>
     <t>T-17</t>
@@ -383,6 +383,13 @@
     <xf numFmtId="4" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -390,13 +397,6 @@
     <xf numFmtId="4" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -772,31 +772,31 @@
         <v>12</v>
       </c>
       <c r="B5" s="5">
-        <v>248.35</v>
+        <v>181.92</v>
       </c>
       <c r="C5" s="6">
-        <v>7351</v>
+        <v>6154</v>
       </c>
       <c r="D5" s="7">
-        <v>17740</v>
+        <v>26947</v>
       </c>
       <c r="E5" s="7">
-        <v>8293</v>
+        <v>24849</v>
       </c>
       <c r="F5" s="7">
-        <v>4648</v>
+        <v>5748</v>
       </c>
       <c r="G5" s="8">
         <f t="shared" ref="G5:G44" si="0">D5/1000</f>
-        <v>17.739999999999998</v>
+        <v>26.946999999999999</v>
       </c>
       <c r="H5" s="8">
         <f t="shared" ref="H5:H44" si="1">E5/1000</f>
-        <v>8.2929999999999993</v>
+        <v>24.849</v>
       </c>
       <c r="I5" s="9">
         <f t="shared" ref="I5:I44" si="2">IFERROR(D5/F5,"")</f>
-        <v>3.8166953528399312</v>
+        <v>4.6880654140570632</v>
       </c>
       <c r="J5" s="10"/>
     </row>
@@ -805,31 +805,31 @@
         <v>13</v>
       </c>
       <c r="B6" s="5">
-        <v>181.92</v>
+        <v>216.07</v>
       </c>
       <c r="C6" s="6">
-        <v>6154</v>
+        <v>5881</v>
       </c>
       <c r="D6" s="7">
-        <v>17335</v>
+        <v>25800</v>
       </c>
       <c r="E6" s="7">
-        <v>9334</v>
+        <v>24267</v>
       </c>
       <c r="F6" s="7">
-        <v>5748</v>
+        <v>6496</v>
       </c>
       <c r="G6" s="8">
         <f t="shared" si="0"/>
-        <v>17.335000000000001</v>
+        <v>25.8</v>
       </c>
       <c r="H6" s="8">
         <f t="shared" si="1"/>
-        <v>9.3339999999999996</v>
+        <v>24.266999999999999</v>
       </c>
       <c r="I6" s="9">
         <f t="shared" si="2"/>
-        <v>3.0158315935977731</v>
+        <v>3.9716748768472905</v>
       </c>
       <c r="J6" s="10"/>
     </row>
@@ -838,31 +838,31 @@
         <v>14</v>
       </c>
       <c r="B7" s="5">
-        <v>89.83</v>
+        <v>132.85</v>
       </c>
       <c r="C7" s="6">
-        <v>4143</v>
+        <v>5047</v>
       </c>
       <c r="D7" s="7">
-        <v>17293</v>
+        <v>24908</v>
       </c>
       <c r="E7" s="7">
-        <v>8295</v>
+        <v>23846</v>
       </c>
       <c r="F7" s="7">
-        <v>3986</v>
+        <v>4795</v>
       </c>
       <c r="G7" s="8">
         <f t="shared" si="0"/>
-        <v>17.292999999999999</v>
+        <v>24.908000000000001</v>
       </c>
       <c r="H7" s="8">
         <f t="shared" si="1"/>
-        <v>8.2949999999999999</v>
+        <v>23.846</v>
       </c>
       <c r="I7" s="9">
         <f t="shared" si="2"/>
-        <v>4.3384345208228803</v>
+        <v>5.1945776850886336</v>
       </c>
       <c r="J7" s="10"/>
     </row>
@@ -871,31 +871,31 @@
         <v>15</v>
       </c>
       <c r="B8" s="5">
-        <v>132.85</v>
+        <v>83.99</v>
       </c>
       <c r="C8" s="6">
-        <v>5047</v>
+        <v>4543</v>
       </c>
       <c r="D8" s="7">
-        <v>17285</v>
+        <v>23900</v>
       </c>
       <c r="E8" s="7">
-        <v>13744</v>
+        <v>21482</v>
       </c>
       <c r="F8" s="7">
-        <v>4795</v>
+        <v>6182</v>
       </c>
       <c r="G8" s="8">
         <f t="shared" si="0"/>
-        <v>17.285</v>
+        <v>23.9</v>
       </c>
       <c r="H8" s="8">
         <f t="shared" si="1"/>
-        <v>13.744</v>
+        <v>21.481999999999999</v>
       </c>
       <c r="I8" s="9">
         <f t="shared" si="2"/>
-        <v>3.6047966631908239</v>
+        <v>3.866062762859916</v>
       </c>
       <c r="J8" s="10"/>
     </row>
@@ -904,31 +904,31 @@
         <v>16</v>
       </c>
       <c r="B9" s="5">
-        <v>129.79</v>
+        <v>215.16</v>
       </c>
       <c r="C9" s="6">
-        <v>4831</v>
+        <v>5870</v>
       </c>
       <c r="D9" s="7">
-        <v>17169</v>
+        <v>22825</v>
       </c>
       <c r="E9" s="7">
-        <v>7252</v>
+        <v>21300</v>
       </c>
       <c r="F9" s="7">
-        <v>3323</v>
+        <v>5463</v>
       </c>
       <c r="G9" s="8">
         <f t="shared" si="0"/>
-        <v>17.169</v>
+        <v>22.824999999999999</v>
       </c>
       <c r="H9" s="8">
         <f t="shared" si="1"/>
-        <v>7.2519999999999998</v>
+        <v>21.3</v>
       </c>
       <c r="I9" s="9">
         <f t="shared" si="2"/>
-        <v>5.1667168221486612</v>
+        <v>4.1781072670693762</v>
       </c>
       <c r="J9" s="10"/>
     </row>
@@ -937,31 +937,31 @@
         <v>17</v>
       </c>
       <c r="B10" s="5">
-        <v>101.07</v>
+        <v>136.16</v>
       </c>
       <c r="C10" s="6">
-        <v>4286</v>
+        <v>5252</v>
       </c>
       <c r="D10" s="7">
-        <v>16690</v>
+        <v>22812</v>
       </c>
       <c r="E10" s="7">
-        <v>10435</v>
+        <v>17958</v>
       </c>
       <c r="F10" s="7">
-        <v>4476</v>
+        <v>5369</v>
       </c>
       <c r="G10" s="8">
         <f t="shared" si="0"/>
-        <v>16.690000000000001</v>
+        <v>22.812000000000001</v>
       </c>
       <c r="H10" s="8">
         <f t="shared" si="1"/>
-        <v>10.435</v>
+        <v>17.957999999999998</v>
       </c>
       <c r="I10" s="9">
         <f t="shared" si="2"/>
-        <v>3.7287756925826629</v>
+        <v>4.2488359098528594</v>
       </c>
       <c r="J10" s="10"/>
     </row>
@@ -970,229 +970,229 @@
         <v>18</v>
       </c>
       <c r="B11" s="5">
+        <v>176.55</v>
+      </c>
+      <c r="C11" s="6">
+        <v>7594</v>
+      </c>
+      <c r="D11" s="7">
+        <v>22477</v>
+      </c>
+      <c r="E11" s="7">
+        <v>21218</v>
+      </c>
+      <c r="F11" s="7">
+        <v>3538</v>
+      </c>
+      <c r="G11" s="8">
+        <f t="shared" si="0"/>
+        <v>22.477</v>
+      </c>
+      <c r="H11" s="8">
+        <f t="shared" si="1"/>
+        <v>21.218</v>
+      </c>
+      <c r="I11" s="9">
+        <f t="shared" si="2"/>
+        <v>6.3530243075183721</v>
+      </c>
+      <c r="J11" s="10"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="5">
+        <v>303.27</v>
+      </c>
+      <c r="C12" s="6">
+        <v>7420</v>
+      </c>
+      <c r="D12" s="7">
+        <v>22477</v>
+      </c>
+      <c r="E12" s="7">
+        <v>19803</v>
+      </c>
+      <c r="F12" s="7">
+        <v>2827</v>
+      </c>
+      <c r="G12" s="8">
+        <f t="shared" si="0"/>
+        <v>22.477</v>
+      </c>
+      <c r="H12" s="8">
+        <f t="shared" si="1"/>
+        <v>19.803000000000001</v>
+      </c>
+      <c r="I12" s="9">
+        <f t="shared" si="2"/>
+        <v>7.9508312698974182</v>
+      </c>
+      <c r="J12" s="10"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="5">
+        <v>225.86</v>
+      </c>
+      <c r="C13" s="6">
+        <v>6836</v>
+      </c>
+      <c r="D13" s="7">
+        <v>21841</v>
+      </c>
+      <c r="E13" s="7">
+        <v>18362</v>
+      </c>
+      <c r="F13" s="7">
+        <v>3960</v>
+      </c>
+      <c r="G13" s="8">
+        <f t="shared" si="0"/>
+        <v>21.841000000000001</v>
+      </c>
+      <c r="H13" s="8">
+        <f t="shared" si="1"/>
+        <v>18.361999999999998</v>
+      </c>
+      <c r="I13" s="9">
+        <f t="shared" si="2"/>
+        <v>5.5154040404040403</v>
+      </c>
+      <c r="J13" s="10"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="5">
         <v>138.68</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C14" s="6">
         <v>5245</v>
       </c>
-      <c r="D11" s="7">
-        <v>15734</v>
-      </c>
-      <c r="E11" s="7">
-        <v>9304</v>
-      </c>
-      <c r="F11" s="7">
+      <c r="D14" s="7">
+        <v>21534</v>
+      </c>
+      <c r="E14" s="7">
+        <v>19410</v>
+      </c>
+      <c r="F14" s="7">
         <v>4871</v>
       </c>
-      <c r="G11" s="8">
-        <f t="shared" si="0"/>
-        <v>15.734</v>
-      </c>
-      <c r="H11" s="8">
-        <f t="shared" si="1"/>
-        <v>9.3040000000000003</v>
-      </c>
-      <c r="I11" s="9">
-        <f t="shared" si="2"/>
-        <v>3.2301375487579551</v>
-      </c>
-      <c r="J11" s="10"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="12">
-        <v>217.12</v>
-      </c>
-      <c r="C12" s="13">
-        <v>6055</v>
-      </c>
-      <c r="D12" s="14">
-        <v>15117</v>
-      </c>
-      <c r="E12" s="14">
-        <v>12119</v>
-      </c>
-      <c r="F12" s="14">
-        <v>7665</v>
-      </c>
-      <c r="G12" s="15">
-        <f t="shared" si="0"/>
-        <v>15.117000000000001</v>
-      </c>
-      <c r="H12" s="15">
-        <f t="shared" si="1"/>
-        <v>12.119</v>
-      </c>
-      <c r="I12" s="16">
-        <f t="shared" si="2"/>
-        <v>1.9722113502935421</v>
-      </c>
-      <c r="J12" s="17"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="19">
-        <v>83.99</v>
-      </c>
-      <c r="C13" s="20">
-        <v>4543</v>
-      </c>
-      <c r="D13" s="21">
-        <v>15090</v>
-      </c>
-      <c r="E13" s="21">
-        <v>11386</v>
-      </c>
-      <c r="F13" s="21">
-        <v>6182</v>
-      </c>
-      <c r="G13" s="22">
-        <f t="shared" si="0"/>
-        <v>15.09</v>
-      </c>
-      <c r="H13" s="22">
-        <f t="shared" si="1"/>
-        <v>11.385999999999999</v>
-      </c>
-      <c r="I13" s="23">
-        <f t="shared" si="2"/>
-        <v>2.4409576188935618</v>
-      </c>
-      <c r="J13" s="24"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="12">
-        <v>128.52000000000001</v>
-      </c>
-      <c r="C14" s="13">
-        <v>5847</v>
-      </c>
-      <c r="D14" s="14">
-        <v>14943</v>
-      </c>
-      <c r="E14" s="14">
-        <v>7832</v>
-      </c>
-      <c r="F14" s="14">
-        <v>6977</v>
-      </c>
-      <c r="G14" s="15">
-        <f t="shared" si="0"/>
-        <v>14.943</v>
-      </c>
-      <c r="H14" s="15">
-        <f t="shared" si="1"/>
-        <v>7.8319999999999999</v>
-      </c>
-      <c r="I14" s="16">
-        <f t="shared" si="2"/>
-        <v>2.141751469112799</v>
-      </c>
-      <c r="J14" s="17"/>
+      <c r="G14" s="8">
+        <f t="shared" si="0"/>
+        <v>21.533999999999999</v>
+      </c>
+      <c r="H14" s="8">
+        <f t="shared" si="1"/>
+        <v>19.41</v>
+      </c>
+      <c r="I14" s="9">
+        <f t="shared" si="2"/>
+        <v>4.4208581400123181</v>
+      </c>
+      <c r="J14" s="10"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="19">
-        <v>216.07</v>
-      </c>
-      <c r="C15" s="20">
-        <v>5881</v>
-      </c>
-      <c r="D15" s="21">
-        <v>14436</v>
-      </c>
-      <c r="E15" s="21">
-        <v>8917</v>
-      </c>
-      <c r="F15" s="21">
-        <v>6496</v>
-      </c>
-      <c r="G15" s="22">
-        <f t="shared" si="0"/>
-        <v>14.436</v>
-      </c>
-      <c r="H15" s="22">
-        <f t="shared" si="1"/>
-        <v>8.9169999999999998</v>
-      </c>
-      <c r="I15" s="23">
-        <f t="shared" si="2"/>
-        <v>2.2222906403940885</v>
-      </c>
-      <c r="J15" s="24"/>
+      <c r="B15" s="5">
+        <v>211.14</v>
+      </c>
+      <c r="C15" s="6">
+        <v>5814</v>
+      </c>
+      <c r="D15" s="7">
+        <v>21354</v>
+      </c>
+      <c r="E15" s="7">
+        <v>19803</v>
+      </c>
+      <c r="F15" s="7">
+        <v>4461</v>
+      </c>
+      <c r="G15" s="8">
+        <f t="shared" si="0"/>
+        <v>21.353999999999999</v>
+      </c>
+      <c r="H15" s="8">
+        <f t="shared" si="1"/>
+        <v>19.803000000000001</v>
+      </c>
+      <c r="I15" s="9">
+        <f t="shared" si="2"/>
+        <v>4.7868190988567587</v>
+      </c>
+      <c r="J15" s="10"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="12">
+      <c r="B16" s="5">
         <v>214</v>
       </c>
-      <c r="C16" s="13">
+      <c r="C16" s="6">
         <v>5853</v>
       </c>
-      <c r="D16" s="14">
-        <v>14436</v>
-      </c>
-      <c r="E16" s="14">
-        <v>7429</v>
-      </c>
-      <c r="F16" s="14">
+      <c r="D16" s="7">
+        <v>21326</v>
+      </c>
+      <c r="E16" s="7">
+        <v>18362</v>
+      </c>
+      <c r="F16" s="7">
         <v>5666</v>
       </c>
-      <c r="G16" s="15">
-        <f t="shared" si="0"/>
-        <v>14.436</v>
-      </c>
-      <c r="H16" s="15">
-        <f t="shared" si="1"/>
-        <v>7.4290000000000003</v>
-      </c>
-      <c r="I16" s="16">
-        <f t="shared" si="2"/>
-        <v>2.5478291563713378</v>
-      </c>
-      <c r="J16" s="17"/>
+      <c r="G16" s="8">
+        <f t="shared" si="0"/>
+        <v>21.326000000000001</v>
+      </c>
+      <c r="H16" s="8">
+        <f t="shared" si="1"/>
+        <v>18.361999999999998</v>
+      </c>
+      <c r="I16" s="9">
+        <f t="shared" si="2"/>
+        <v>3.7638545711260147</v>
+      </c>
+      <c r="J16" s="10"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>24</v>
       </c>
       <c r="B17" s="5">
-        <v>158.57</v>
+        <v>248.35</v>
       </c>
       <c r="C17" s="6">
-        <v>5634</v>
+        <v>7351</v>
       </c>
       <c r="D17" s="7">
-        <v>12738</v>
+        <v>20889</v>
       </c>
       <c r="E17" s="7">
-        <v>7311</v>
+        <v>18393</v>
       </c>
       <c r="F17" s="7">
-        <v>3705</v>
+        <v>4648</v>
       </c>
       <c r="G17" s="8">
         <f t="shared" si="0"/>
-        <v>12.738</v>
+        <v>20.888999999999999</v>
       </c>
       <c r="H17" s="8">
         <f t="shared" si="1"/>
-        <v>7.3109999999999999</v>
+        <v>18.393000000000001</v>
       </c>
       <c r="I17" s="9">
         <f t="shared" si="2"/>
-        <v>3.4380566801619432</v>
+        <v>4.4941910499139412</v>
       </c>
       <c r="J17" s="10"/>
     </row>
@@ -1201,97 +1201,97 @@
         <v>25</v>
       </c>
       <c r="B18" s="5">
-        <v>176.55</v>
+        <v>101.07</v>
       </c>
       <c r="C18" s="6">
-        <v>7594</v>
+        <v>4286</v>
       </c>
       <c r="D18" s="7">
-        <v>12713</v>
+        <v>20556</v>
       </c>
       <c r="E18" s="7">
-        <v>4778</v>
+        <v>20519</v>
       </c>
       <c r="F18" s="7">
-        <v>3538</v>
+        <v>4476</v>
       </c>
       <c r="G18" s="8">
         <f t="shared" si="0"/>
-        <v>12.712999999999999</v>
+        <v>20.556000000000001</v>
       </c>
       <c r="H18" s="8">
         <f t="shared" si="1"/>
-        <v>4.7779999999999996</v>
+        <v>20.518999999999998</v>
       </c>
       <c r="I18" s="9">
         <f t="shared" si="2"/>
-        <v>3.5932730356133407</v>
+        <v>4.5924932975871311</v>
       </c>
       <c r="J18" s="10"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="18" t="s">
+      <c r="A19" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="19">
-        <v>211.14</v>
-      </c>
-      <c r="C19" s="20">
-        <v>5814</v>
-      </c>
-      <c r="D19" s="21">
-        <v>12713</v>
-      </c>
-      <c r="E19" s="21">
-        <v>6012</v>
-      </c>
-      <c r="F19" s="21">
-        <v>4461</v>
-      </c>
-      <c r="G19" s="22">
-        <f t="shared" si="0"/>
-        <v>12.712999999999999</v>
-      </c>
-      <c r="H19" s="22">
-        <f t="shared" si="1"/>
-        <v>6.0119999999999996</v>
-      </c>
-      <c r="I19" s="23">
-        <f t="shared" si="2"/>
-        <v>2.8498094597623851</v>
-      </c>
-      <c r="J19" s="24"/>
+      <c r="B19" s="5">
+        <v>127.51</v>
+      </c>
+      <c r="C19" s="6">
+        <v>5515</v>
+      </c>
+      <c r="D19" s="7">
+        <v>19795</v>
+      </c>
+      <c r="E19" s="7">
+        <v>17710</v>
+      </c>
+      <c r="F19" s="7">
+        <v>2671</v>
+      </c>
+      <c r="G19" s="8">
+        <f t="shared" si="0"/>
+        <v>19.795000000000002</v>
+      </c>
+      <c r="H19" s="8">
+        <f t="shared" si="1"/>
+        <v>17.71</v>
+      </c>
+      <c r="I19" s="9">
+        <f t="shared" si="2"/>
+        <v>7.4110819917633846</v>
+      </c>
+      <c r="J19" s="10"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>27</v>
       </c>
       <c r="B20" s="5">
-        <v>303.27</v>
+        <v>158.57</v>
       </c>
       <c r="C20" s="6">
-        <v>7420</v>
+        <v>5634</v>
       </c>
       <c r="D20" s="7">
-        <v>12242</v>
+        <v>19482</v>
       </c>
       <c r="E20" s="7">
-        <v>3207</v>
+        <v>17403</v>
       </c>
       <c r="F20" s="7">
-        <v>2827</v>
+        <v>3705</v>
       </c>
       <c r="G20" s="8">
         <f t="shared" si="0"/>
-        <v>12.242000000000001</v>
+        <v>19.481999999999999</v>
       </c>
       <c r="H20" s="8">
         <f t="shared" si="1"/>
-        <v>3.2069999999999999</v>
+        <v>17.402999999999999</v>
       </c>
       <c r="I20" s="9">
         <f t="shared" si="2"/>
-        <v>4.3303855677396532</v>
+        <v>5.2582995951417004</v>
       </c>
       <c r="J20" s="10"/>
     </row>
@@ -1300,31 +1300,31 @@
         <v>28</v>
       </c>
       <c r="B21" s="5">
-        <v>53.2</v>
+        <v>89.83</v>
       </c>
       <c r="C21" s="6">
-        <v>3095</v>
+        <v>4143</v>
       </c>
       <c r="D21" s="7">
-        <v>12162</v>
+        <v>19468</v>
       </c>
       <c r="E21" s="7">
-        <v>7250</v>
+        <v>18376</v>
       </c>
       <c r="F21" s="7">
-        <v>3321</v>
+        <v>3986</v>
       </c>
       <c r="G21" s="8">
         <f t="shared" si="0"/>
-        <v>12.162000000000001</v>
+        <v>19.468</v>
       </c>
       <c r="H21" s="8">
         <f t="shared" si="1"/>
-        <v>7.25</v>
+        <v>18.376000000000001</v>
       </c>
       <c r="I21" s="9">
         <f t="shared" si="2"/>
-        <v>3.6621499548328815</v>
+        <v>4.8840943301555448</v>
       </c>
       <c r="J21" s="10"/>
     </row>
@@ -1333,396 +1333,396 @@
         <v>29</v>
       </c>
       <c r="B22" s="5">
-        <v>23</v>
+        <v>147.1</v>
       </c>
       <c r="C22" s="6">
-        <v>3375</v>
+        <v>5457</v>
       </c>
       <c r="D22" s="7">
-        <v>12115</v>
+        <v>19279</v>
       </c>
       <c r="E22" s="7">
-        <v>5852</v>
+        <v>15615</v>
       </c>
       <c r="F22" s="7">
-        <v>2251</v>
+        <v>1631</v>
       </c>
       <c r="G22" s="8">
         <f t="shared" si="0"/>
-        <v>12.115</v>
+        <v>19.279</v>
       </c>
       <c r="H22" s="8">
         <f t="shared" si="1"/>
-        <v>5.8520000000000003</v>
+        <v>15.615</v>
       </c>
       <c r="I22" s="9">
         <f t="shared" si="2"/>
-        <v>5.3820524211461569</v>
+        <v>11.820355610055181</v>
       </c>
       <c r="J22" s="10"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A23" s="18" t="s">
+      <c r="A23" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B23" s="19">
-        <v>215.16</v>
-      </c>
-      <c r="C23" s="20">
-        <v>5870</v>
-      </c>
-      <c r="D23" s="21">
-        <v>11957</v>
-      </c>
-      <c r="E23" s="21">
-        <v>8917</v>
-      </c>
-      <c r="F23" s="21">
-        <v>5463</v>
-      </c>
-      <c r="G23" s="22">
-        <f t="shared" si="0"/>
-        <v>11.957000000000001</v>
-      </c>
-      <c r="H23" s="22">
-        <f t="shared" si="1"/>
-        <v>8.9169999999999998</v>
-      </c>
-      <c r="I23" s="23">
-        <f t="shared" si="2"/>
-        <v>2.18872414424309</v>
-      </c>
-      <c r="J23" s="24"/>
+      <c r="B23" s="12">
+        <v>128.52000000000001</v>
+      </c>
+      <c r="C23" s="13">
+        <v>5847</v>
+      </c>
+      <c r="D23" s="14">
+        <v>18414</v>
+      </c>
+      <c r="E23" s="14">
+        <v>15328</v>
+      </c>
+      <c r="F23" s="14">
+        <v>6977</v>
+      </c>
+      <c r="G23" s="15">
+        <f t="shared" si="0"/>
+        <v>18.414000000000001</v>
+      </c>
+      <c r="H23" s="15">
+        <f t="shared" si="1"/>
+        <v>15.327999999999999</v>
+      </c>
+      <c r="I23" s="16">
+        <f t="shared" si="2"/>
+        <v>2.6392432277483158</v>
+      </c>
+      <c r="J23" s="17"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>31</v>
       </c>
       <c r="B24" s="5">
+        <v>129.79</v>
+      </c>
+      <c r="C24" s="6">
+        <v>4831</v>
+      </c>
+      <c r="D24" s="7">
+        <v>18408</v>
+      </c>
+      <c r="E24" s="7">
+        <v>17363</v>
+      </c>
+      <c r="F24" s="7">
+        <v>3323</v>
+      </c>
+      <c r="G24" s="8">
+        <f t="shared" si="0"/>
+        <v>18.408000000000001</v>
+      </c>
+      <c r="H24" s="8">
+        <f t="shared" si="1"/>
+        <v>17.363</v>
+      </c>
+      <c r="I24" s="9">
+        <f t="shared" si="2"/>
+        <v>5.5395726752934094</v>
+      </c>
+      <c r="J24" s="10"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="5">
+        <v>53.2</v>
+      </c>
+      <c r="C25" s="6">
+        <v>3095</v>
+      </c>
+      <c r="D25" s="7">
+        <v>18408</v>
+      </c>
+      <c r="E25" s="7">
+        <v>17333</v>
+      </c>
+      <c r="F25" s="7">
+        <v>3321</v>
+      </c>
+      <c r="G25" s="8">
+        <f t="shared" si="0"/>
+        <v>18.408000000000001</v>
+      </c>
+      <c r="H25" s="8">
+        <f t="shared" si="1"/>
+        <v>17.332999999999998</v>
+      </c>
+      <c r="I25" s="9">
+        <f t="shared" si="2"/>
+        <v>5.5429087624209572</v>
+      </c>
+      <c r="J25" s="10"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A26" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="5">
+        <v>268.29000000000002</v>
+      </c>
+      <c r="C26" s="6">
+        <v>6666</v>
+      </c>
+      <c r="D26" s="7">
+        <v>17728</v>
+      </c>
+      <c r="E26" s="7">
+        <v>12669</v>
+      </c>
+      <c r="F26" s="7">
+        <v>954</v>
+      </c>
+      <c r="G26" s="8">
+        <f t="shared" si="0"/>
+        <v>17.728000000000002</v>
+      </c>
+      <c r="H26" s="8">
+        <f t="shared" si="1"/>
+        <v>12.669</v>
+      </c>
+      <c r="I26" s="9">
+        <f t="shared" si="2"/>
+        <v>18.582809224318659</v>
+      </c>
+      <c r="J26" s="10"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="5">
         <v>115.08</v>
       </c>
-      <c r="C24" s="6">
+      <c r="C27" s="6">
         <v>5656</v>
       </c>
-      <c r="D24" s="7">
-        <v>11756</v>
-      </c>
-      <c r="E24" s="7">
-        <v>5852</v>
-      </c>
-      <c r="F24" s="7">
+      <c r="D27" s="7">
+        <v>17453</v>
+      </c>
+      <c r="E27" s="7">
+        <v>15971</v>
+      </c>
+      <c r="F27" s="7">
         <v>2262</v>
       </c>
-      <c r="G24" s="8">
-        <f t="shared" si="0"/>
-        <v>11.756</v>
-      </c>
-      <c r="H24" s="8">
-        <f t="shared" si="1"/>
-        <v>5.8520000000000003</v>
-      </c>
-      <c r="I24" s="9">
-        <f t="shared" si="2"/>
-        <v>5.1971706454465076</v>
-      </c>
-      <c r="J24" s="10"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" s="19">
-        <v>222.45</v>
-      </c>
-      <c r="C25" s="20">
-        <v>5898</v>
-      </c>
-      <c r="D25" s="21">
-        <v>11456</v>
-      </c>
-      <c r="E25" s="21">
-        <v>6283</v>
-      </c>
-      <c r="F25" s="21">
-        <v>4632</v>
-      </c>
-      <c r="G25" s="22">
-        <f t="shared" si="0"/>
-        <v>11.456</v>
-      </c>
-      <c r="H25" s="22">
-        <f t="shared" si="1"/>
-        <v>6.2830000000000004</v>
-      </c>
-      <c r="I25" s="23">
-        <f t="shared" si="2"/>
-        <v>2.4732297063903284</v>
-      </c>
-      <c r="J25" s="24"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A26" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" s="12">
-        <v>196.2</v>
-      </c>
-      <c r="C26" s="13">
-        <v>5516</v>
-      </c>
-      <c r="D26" s="14">
-        <v>11247</v>
-      </c>
-      <c r="E26" s="14">
-        <v>4297</v>
-      </c>
-      <c r="F26" s="14">
-        <v>3785</v>
-      </c>
-      <c r="G26" s="15">
-        <f t="shared" si="0"/>
-        <v>11.247</v>
-      </c>
-      <c r="H26" s="15">
-        <f t="shared" si="1"/>
-        <v>4.2969999999999997</v>
-      </c>
-      <c r="I26" s="16">
-        <f t="shared" si="2"/>
-        <v>2.9714663143989433</v>
-      </c>
-      <c r="J26" s="17"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A27" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" s="19">
-        <v>198.71</v>
-      </c>
-      <c r="C27" s="20">
-        <v>5502</v>
-      </c>
-      <c r="D27" s="21">
-        <v>11247</v>
-      </c>
-      <c r="E27" s="21">
-        <v>5920</v>
-      </c>
-      <c r="F27" s="21">
-        <v>4181</v>
-      </c>
-      <c r="G27" s="22">
-        <f t="shared" si="0"/>
-        <v>11.247</v>
-      </c>
-      <c r="H27" s="22">
-        <f t="shared" si="1"/>
-        <v>5.92</v>
-      </c>
-      <c r="I27" s="23">
-        <f t="shared" si="2"/>
-        <v>2.6900263094953361</v>
-      </c>
-      <c r="J27" s="24"/>
+      <c r="G27" s="8">
+        <f t="shared" si="0"/>
+        <v>17.452999999999999</v>
+      </c>
+      <c r="H27" s="8">
+        <f t="shared" si="1"/>
+        <v>15.971</v>
+      </c>
+      <c r="I27" s="9">
+        <f t="shared" si="2"/>
+        <v>7.7157382847038019</v>
+      </c>
+      <c r="J27" s="10"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>35</v>
       </c>
       <c r="B28" s="5">
+        <v>23</v>
+      </c>
+      <c r="C28" s="6">
+        <v>3375</v>
+      </c>
+      <c r="D28" s="7">
+        <v>17363</v>
+      </c>
+      <c r="E28" s="7">
+        <v>15928</v>
+      </c>
+      <c r="F28" s="7">
+        <v>2251</v>
+      </c>
+      <c r="G28" s="8">
+        <f t="shared" si="0"/>
+        <v>17.363</v>
+      </c>
+      <c r="H28" s="8">
+        <f t="shared" si="1"/>
+        <v>15.928000000000001</v>
+      </c>
+      <c r="I28" s="9">
+        <f t="shared" si="2"/>
+        <v>7.7134606841403821</v>
+      </c>
+      <c r="J28" s="10"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A29" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="12">
+        <v>217.12</v>
+      </c>
+      <c r="C29" s="13">
+        <v>6055</v>
+      </c>
+      <c r="D29" s="14">
+        <v>15384</v>
+      </c>
+      <c r="E29" s="14">
+        <v>12085</v>
+      </c>
+      <c r="F29" s="14">
+        <v>7665</v>
+      </c>
+      <c r="G29" s="15">
+        <f t="shared" si="0"/>
+        <v>15.384</v>
+      </c>
+      <c r="H29" s="15">
+        <f t="shared" si="1"/>
+        <v>12.085000000000001</v>
+      </c>
+      <c r="I29" s="16">
+        <f t="shared" si="2"/>
+        <v>2.0070450097847359</v>
+      </c>
+      <c r="J29" s="17"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A30" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="5">
         <v>249.78</v>
       </c>
-      <c r="C28" s="6">
+      <c r="C30" s="6">
         <v>6425</v>
       </c>
-      <c r="D28" s="7">
-        <v>10250</v>
-      </c>
-      <c r="E28" s="7">
-        <v>2549</v>
-      </c>
-      <c r="F28" s="7">
+      <c r="D30" s="7">
+        <v>12684</v>
+      </c>
+      <c r="E30" s="7">
+        <v>9393</v>
+      </c>
+      <c r="F30" s="7">
         <v>1605</v>
       </c>
-      <c r="G28" s="8">
-        <f t="shared" si="0"/>
-        <v>10.25</v>
-      </c>
-      <c r="H28" s="8">
-        <f t="shared" si="1"/>
-        <v>2.5489999999999999</v>
-      </c>
-      <c r="I28" s="9">
-        <f t="shared" si="2"/>
-        <v>6.3862928348909653</v>
-      </c>
-      <c r="J28" s="10"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A29" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" s="5">
-        <v>313.18</v>
-      </c>
-      <c r="C29" s="6">
-        <v>7098</v>
-      </c>
-      <c r="D29" s="7">
-        <v>10250</v>
-      </c>
-      <c r="E29" s="7">
-        <v>4024</v>
-      </c>
-      <c r="F29" s="7">
-        <v>2810</v>
-      </c>
-      <c r="G29" s="8">
-        <f t="shared" si="0"/>
-        <v>10.25</v>
-      </c>
-      <c r="H29" s="8">
-        <f t="shared" si="1"/>
-        <v>4.024</v>
-      </c>
-      <c r="I29" s="9">
-        <f t="shared" si="2"/>
-        <v>3.6476868327402134</v>
-      </c>
-      <c r="J29" s="10"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A30" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="12">
-        <v>225.86</v>
-      </c>
-      <c r="C30" s="13">
-        <v>6836</v>
-      </c>
-      <c r="D30" s="14">
-        <v>10206</v>
-      </c>
-      <c r="E30" s="14">
-        <v>4371</v>
-      </c>
-      <c r="F30" s="14">
-        <v>3960</v>
-      </c>
-      <c r="G30" s="15">
-        <f t="shared" si="0"/>
-        <v>10.206</v>
-      </c>
-      <c r="H30" s="15">
-        <f t="shared" si="1"/>
-        <v>4.3710000000000004</v>
-      </c>
-      <c r="I30" s="16">
-        <f t="shared" si="2"/>
-        <v>2.5772727272727272</v>
-      </c>
-      <c r="J30" s="17"/>
+      <c r="G30" s="8">
+        <f t="shared" si="0"/>
+        <v>12.683999999999999</v>
+      </c>
+      <c r="H30" s="8">
+        <f t="shared" si="1"/>
+        <v>9.3930000000000007</v>
+      </c>
+      <c r="I30" s="9">
+        <f t="shared" si="2"/>
+        <v>7.9028037383177567</v>
+      </c>
+      <c r="J30" s="10"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>38</v>
       </c>
       <c r="B31" s="5">
-        <v>127.51</v>
+        <v>313.18</v>
       </c>
       <c r="C31" s="6">
-        <v>5515</v>
+        <v>7098</v>
       </c>
       <c r="D31" s="7">
-        <v>10040</v>
+        <v>9423</v>
       </c>
       <c r="E31" s="7">
-        <v>7341</v>
+        <v>3998</v>
       </c>
       <c r="F31" s="7">
-        <v>2671</v>
+        <v>2810</v>
       </c>
       <c r="G31" s="8">
         <f t="shared" si="0"/>
-        <v>10.039999999999999</v>
+        <v>9.423</v>
       </c>
       <c r="H31" s="8">
         <f t="shared" si="1"/>
-        <v>7.3410000000000002</v>
+        <v>3.9980000000000002</v>
       </c>
       <c r="I31" s="9">
         <f t="shared" si="2"/>
-        <v>3.7588918008236614</v>
+        <v>3.3533807829181494</v>
       </c>
       <c r="J31" s="10"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="B32" s="5">
-        <v>147.1</v>
-      </c>
-      <c r="C32" s="6">
-        <v>5457</v>
-      </c>
-      <c r="D32" s="7">
-        <v>9140</v>
-      </c>
-      <c r="E32" s="7">
-        <v>5521</v>
-      </c>
-      <c r="F32" s="7">
-        <v>1631</v>
-      </c>
-      <c r="G32" s="8">
-        <f t="shared" si="0"/>
-        <v>9.14</v>
-      </c>
-      <c r="H32" s="8">
-        <f t="shared" si="1"/>
-        <v>5.5209999999999999</v>
-      </c>
-      <c r="I32" s="9">
-        <f t="shared" si="2"/>
-        <v>5.6039239730226855</v>
-      </c>
-      <c r="J32" s="10"/>
+      <c r="B32" s="19">
+        <v>198.71</v>
+      </c>
+      <c r="C32" s="20">
+        <v>5502</v>
+      </c>
+      <c r="D32" s="21">
+        <v>9372</v>
+      </c>
+      <c r="E32" s="21">
+        <v>5868</v>
+      </c>
+      <c r="F32" s="21">
+        <v>4181</v>
+      </c>
+      <c r="G32" s="22">
+        <f t="shared" si="0"/>
+        <v>9.3719999999999999</v>
+      </c>
+      <c r="H32" s="22">
+        <f t="shared" si="1"/>
+        <v>5.8680000000000003</v>
+      </c>
+      <c r="I32" s="23">
+        <f t="shared" si="2"/>
+        <v>2.2415690026309494</v>
+      </c>
+      <c r="J32" s="24"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A33" s="18" t="s">
+      <c r="A33" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B33" s="19">
-        <v>136.16</v>
-      </c>
-      <c r="C33" s="20">
-        <v>5252</v>
-      </c>
-      <c r="D33" s="21">
-        <v>9095</v>
-      </c>
-      <c r="E33" s="21">
-        <v>5809</v>
-      </c>
-      <c r="F33" s="21">
-        <v>5369</v>
-      </c>
-      <c r="G33" s="22">
-        <f t="shared" si="0"/>
-        <v>9.0950000000000006</v>
-      </c>
-      <c r="H33" s="22">
-        <f t="shared" si="1"/>
-        <v>5.8090000000000002</v>
-      </c>
-      <c r="I33" s="23">
-        <f t="shared" si="2"/>
-        <v>1.6939839821195752</v>
-      </c>
-      <c r="J33" s="24"/>
+      <c r="B33" s="12">
+        <v>222.45</v>
+      </c>
+      <c r="C33" s="13">
+        <v>5898</v>
+      </c>
+      <c r="D33" s="14">
+        <v>9262</v>
+      </c>
+      <c r="E33" s="14">
+        <v>6251</v>
+      </c>
+      <c r="F33" s="14">
+        <v>4632</v>
+      </c>
+      <c r="G33" s="15">
+        <f t="shared" si="0"/>
+        <v>9.2620000000000005</v>
+      </c>
+      <c r="H33" s="15">
+        <f t="shared" si="1"/>
+        <v>6.2510000000000003</v>
+      </c>
+      <c r="I33" s="16">
+        <f t="shared" si="2"/>
+        <v>1.9995682210708117</v>
+      </c>
+      <c r="J33" s="17"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
@@ -1735,258 +1735,258 @@
         <v>9293</v>
       </c>
       <c r="D34" s="7">
-        <v>8130</v>
+        <v>8086</v>
       </c>
       <c r="E34" s="7">
-        <v>1256</v>
+        <v>1210</v>
       </c>
       <c r="F34" s="7">
         <v>1215</v>
       </c>
       <c r="G34" s="8">
         <f t="shared" si="0"/>
-        <v>8.1300000000000008</v>
+        <v>8.0860000000000003</v>
       </c>
       <c r="H34" s="8">
         <f t="shared" si="1"/>
-        <v>1.256</v>
+        <v>1.21</v>
       </c>
       <c r="I34" s="9">
         <f t="shared" si="2"/>
-        <v>6.6913580246913584</v>
+        <v>6.655144032921811</v>
       </c>
       <c r="J34" s="10"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="B35" s="5">
+      <c r="B35" s="12">
         <v>128.41999999999999</v>
       </c>
-      <c r="C35" s="6">
+      <c r="C35" s="13">
         <v>6551</v>
       </c>
-      <c r="D35" s="7">
-        <v>8129</v>
-      </c>
-      <c r="E35" s="7">
-        <v>4029</v>
-      </c>
-      <c r="F35" s="7">
+      <c r="D35" s="14">
+        <v>7330</v>
+      </c>
+      <c r="E35" s="14">
+        <v>3998</v>
+      </c>
+      <c r="F35" s="14">
         <v>2542</v>
       </c>
-      <c r="G35" s="8">
-        <f t="shared" si="0"/>
-        <v>8.1289999999999996</v>
-      </c>
-      <c r="H35" s="8">
-        <f t="shared" si="1"/>
-        <v>4.0289999999999999</v>
-      </c>
-      <c r="I35" s="9">
-        <f t="shared" si="2"/>
-        <v>3.1978756884343036</v>
-      </c>
-      <c r="J35" s="10"/>
+      <c r="G35" s="15">
+        <f t="shared" si="0"/>
+        <v>7.33</v>
+      </c>
+      <c r="H35" s="15">
+        <f t="shared" si="1"/>
+        <v>3.9980000000000002</v>
+      </c>
+      <c r="I35" s="16">
+        <f t="shared" si="2"/>
+        <v>2.8835562549173881</v>
+      </c>
+      <c r="J35" s="17"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="5">
+      <c r="B36" s="19">
+        <v>180.97</v>
+      </c>
+      <c r="C36" s="20">
+        <v>5840</v>
+      </c>
+      <c r="D36" s="21">
+        <v>6948</v>
+      </c>
+      <c r="E36" s="21">
+        <v>4279</v>
+      </c>
+      <c r="F36" s="21">
+        <v>3349</v>
+      </c>
+      <c r="G36" s="22">
+        <f t="shared" si="0"/>
+        <v>6.9480000000000004</v>
+      </c>
+      <c r="H36" s="22">
+        <f t="shared" si="1"/>
+        <v>4.2789999999999999</v>
+      </c>
+      <c r="I36" s="23">
+        <f t="shared" si="2"/>
+        <v>2.0746491489997014</v>
+      </c>
+      <c r="J36" s="24"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A37" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="12">
+        <v>189.27</v>
+      </c>
+      <c r="C37" s="13">
+        <v>5556</v>
+      </c>
+      <c r="D37" s="14">
+        <v>6198</v>
+      </c>
+      <c r="E37" s="14">
+        <v>4279</v>
+      </c>
+      <c r="F37" s="14">
+        <v>2759</v>
+      </c>
+      <c r="G37" s="15">
+        <f t="shared" si="0"/>
+        <v>6.1980000000000004</v>
+      </c>
+      <c r="H37" s="15">
+        <f t="shared" si="1"/>
+        <v>4.2789999999999999</v>
+      </c>
+      <c r="I37" s="16">
+        <f t="shared" si="2"/>
+        <v>2.2464661109097501</v>
+      </c>
+      <c r="J37" s="17"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A38" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" s="19">
+        <v>196.2</v>
+      </c>
+      <c r="C38" s="20">
+        <v>5516</v>
+      </c>
+      <c r="D38" s="21">
+        <v>6006</v>
+      </c>
+      <c r="E38" s="21">
+        <v>4262</v>
+      </c>
+      <c r="F38" s="21">
+        <v>3785</v>
+      </c>
+      <c r="G38" s="22">
+        <f t="shared" si="0"/>
+        <v>6.0060000000000002</v>
+      </c>
+      <c r="H38" s="22">
+        <f t="shared" si="1"/>
+        <v>4.2619999999999996</v>
+      </c>
+      <c r="I38" s="23">
+        <f t="shared" si="2"/>
+        <v>1.5867899603698812</v>
+      </c>
+      <c r="J38" s="24"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A39" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" s="12">
+        <v>207.35</v>
+      </c>
+      <c r="C39" s="13">
+        <v>5781</v>
+      </c>
+      <c r="D39" s="14">
+        <v>5956</v>
+      </c>
+      <c r="E39" s="14">
+        <v>2635</v>
+      </c>
+      <c r="F39" s="14">
+        <v>2643</v>
+      </c>
+      <c r="G39" s="15">
+        <f t="shared" si="0"/>
+        <v>5.9560000000000004</v>
+      </c>
+      <c r="H39" s="15">
+        <f t="shared" si="1"/>
+        <v>2.6349999999999998</v>
+      </c>
+      <c r="I39" s="16">
+        <f t="shared" si="2"/>
+        <v>2.2534998108210367</v>
+      </c>
+      <c r="J39" s="17"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A40" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40" s="19">
+        <v>113.43</v>
+      </c>
+      <c r="C40" s="20">
+        <v>4317</v>
+      </c>
+      <c r="D40" s="21">
+        <v>5143</v>
+      </c>
+      <c r="E40" s="21">
+        <v>3094</v>
+      </c>
+      <c r="F40" s="21">
+        <v>2713</v>
+      </c>
+      <c r="G40" s="22">
+        <f t="shared" si="0"/>
+        <v>5.1429999999999998</v>
+      </c>
+      <c r="H40" s="22">
+        <f t="shared" si="1"/>
+        <v>3.0939999999999999</v>
+      </c>
+      <c r="I40" s="23">
+        <f t="shared" si="2"/>
+        <v>1.8956874308883156</v>
+      </c>
+      <c r="J40" s="24"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A41" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41" s="5">
         <v>265.83</v>
       </c>
-      <c r="C36" s="6">
+      <c r="C41" s="6">
         <v>6634</v>
       </c>
-      <c r="D36" s="7">
-        <v>7087</v>
-      </c>
-      <c r="E36" s="7">
-        <v>1256</v>
-      </c>
-      <c r="F36" s="7">
+      <c r="D41" s="7">
+        <v>5049</v>
+      </c>
+      <c r="E41" s="7">
+        <v>1210</v>
+      </c>
+      <c r="F41" s="7">
         <v>1241</v>
       </c>
-      <c r="G36" s="8">
-        <f t="shared" si="0"/>
-        <v>7.0869999999999997</v>
-      </c>
-      <c r="H36" s="8">
-        <f t="shared" si="1"/>
-        <v>1.256</v>
-      </c>
-      <c r="I36" s="9">
-        <f t="shared" si="2"/>
-        <v>5.71071716357776</v>
-      </c>
-      <c r="J36" s="10"/>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A37" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="B37" s="19">
-        <v>180.97</v>
-      </c>
-      <c r="C37" s="20">
-        <v>5840</v>
-      </c>
-      <c r="D37" s="21">
-        <v>6962</v>
-      </c>
-      <c r="E37" s="21">
-        <v>4337</v>
-      </c>
-      <c r="F37" s="21">
-        <v>3349</v>
-      </c>
-      <c r="G37" s="22">
-        <f t="shared" si="0"/>
-        <v>6.9619999999999997</v>
-      </c>
-      <c r="H37" s="22">
-        <f t="shared" si="1"/>
-        <v>4.3369999999999997</v>
-      </c>
-      <c r="I37" s="23">
-        <f t="shared" si="2"/>
-        <v>2.0788295013436846</v>
-      </c>
-      <c r="J37" s="24"/>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A38" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B38" s="5">
-        <v>268.29000000000002</v>
-      </c>
-      <c r="C38" s="6">
-        <v>6666</v>
-      </c>
-      <c r="D38" s="7">
-        <v>6786</v>
-      </c>
-      <c r="E38" s="7">
-        <v>1012</v>
-      </c>
-      <c r="F38" s="7">
-        <v>954</v>
-      </c>
-      <c r="G38" s="8">
-        <f t="shared" si="0"/>
-        <v>6.7859999999999996</v>
-      </c>
-      <c r="H38" s="8">
-        <f t="shared" si="1"/>
-        <v>1.012</v>
-      </c>
-      <c r="I38" s="9">
-        <f t="shared" si="2"/>
-        <v>7.1132075471698117</v>
-      </c>
-      <c r="J38" s="10"/>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A39" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="B39" s="19">
-        <v>189.27</v>
-      </c>
-      <c r="C39" s="20">
-        <v>5556</v>
-      </c>
-      <c r="D39" s="21">
-        <v>6420</v>
-      </c>
-      <c r="E39" s="21">
-        <v>3358</v>
-      </c>
-      <c r="F39" s="21">
-        <v>2759</v>
-      </c>
-      <c r="G39" s="22">
-        <f t="shared" si="0"/>
-        <v>6.42</v>
-      </c>
-      <c r="H39" s="22">
-        <f t="shared" si="1"/>
-        <v>3.3580000000000001</v>
-      </c>
-      <c r="I39" s="23">
-        <f t="shared" si="2"/>
-        <v>2.326930047118521</v>
-      </c>
-      <c r="J39" s="24"/>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A40" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="B40" s="12">
-        <v>207.35</v>
-      </c>
-      <c r="C40" s="13">
-        <v>5781</v>
-      </c>
-      <c r="D40" s="14">
-        <v>5718</v>
-      </c>
-      <c r="E40" s="14">
-        <v>2673</v>
-      </c>
-      <c r="F40" s="14">
-        <v>2643</v>
-      </c>
-      <c r="G40" s="15">
-        <f t="shared" si="0"/>
-        <v>5.718</v>
-      </c>
-      <c r="H40" s="15">
-        <f t="shared" si="1"/>
-        <v>2.673</v>
-      </c>
-      <c r="I40" s="16">
-        <f t="shared" si="2"/>
-        <v>2.1634506242905789</v>
-      </c>
-      <c r="J40" s="17"/>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A41" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="B41" s="19">
-        <v>113.43</v>
-      </c>
-      <c r="C41" s="20">
-        <v>4317</v>
-      </c>
-      <c r="D41" s="21">
-        <v>5128</v>
-      </c>
-      <c r="E41" s="21">
-        <v>3121</v>
-      </c>
-      <c r="F41" s="21">
-        <v>2713</v>
-      </c>
-      <c r="G41" s="22">
-        <f t="shared" si="0"/>
-        <v>5.1280000000000001</v>
-      </c>
-      <c r="H41" s="22">
-        <f t="shared" si="1"/>
-        <v>3.121</v>
-      </c>
-      <c r="I41" s="23">
-        <f t="shared" si="2"/>
-        <v>1.8901584961297457</v>
-      </c>
-      <c r="J41" s="24"/>
+      <c r="G41" s="8">
+        <f t="shared" si="0"/>
+        <v>5.0490000000000004</v>
+      </c>
+      <c r="H41" s="8">
+        <f t="shared" si="1"/>
+        <v>1.21</v>
+      </c>
+      <c r="I41" s="9">
+        <f t="shared" si="2"/>
+        <v>4.0684931506849313</v>
+      </c>
+      <c r="J41" s="10"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
@@ -1999,25 +1999,25 @@
         <v>10087</v>
       </c>
       <c r="D42" s="7">
-        <v>4233</v>
+        <v>4373</v>
       </c>
       <c r="E42" s="7">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F42" s="7">
         <v>44</v>
       </c>
       <c r="G42" s="8">
         <f t="shared" si="0"/>
-        <v>4.2329999999999997</v>
+        <v>4.3730000000000002</v>
       </c>
       <c r="H42" s="8">
         <f t="shared" si="1"/>
-        <v>4.3999999999999997E-2</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="I42" s="9">
         <f t="shared" si="2"/>
-        <v>96.204545454545453</v>
+        <v>99.38636363636364</v>
       </c>
       <c r="J42" s="10"/>
     </row>
@@ -2032,25 +2032,25 @@
         <v>5029</v>
       </c>
       <c r="D43" s="7">
-        <v>4124</v>
+        <v>2564</v>
       </c>
       <c r="E43" s="7">
-        <v>222</v>
+        <v>182</v>
       </c>
       <c r="F43" s="7">
         <v>218</v>
       </c>
       <c r="G43" s="8">
         <f t="shared" si="0"/>
-        <v>4.1239999999999997</v>
+        <v>2.5640000000000001</v>
       </c>
       <c r="H43" s="8">
         <f t="shared" si="1"/>
-        <v>0.222</v>
+        <v>0.182</v>
       </c>
       <c r="I43" s="9">
         <f t="shared" si="2"/>
-        <v>18.917431192660551</v>
+        <v>11.761467889908257</v>
       </c>
       <c r="J43" s="10"/>
     </row>
@@ -2065,25 +2065,25 @@
         <v>2922</v>
       </c>
       <c r="D44" s="7">
-        <v>2151</v>
+        <v>1350</v>
       </c>
       <c r="E44" s="7">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="F44" s="7">
         <v>61</v>
       </c>
       <c r="G44" s="8">
         <f t="shared" si="0"/>
-        <v>2.1509999999999998</v>
+        <v>1.35</v>
       </c>
       <c r="H44" s="8">
         <f t="shared" si="1"/>
-        <v>6.2E-2</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="I44" s="9">
         <f t="shared" si="2"/>
-        <v>35.26229508196721</v>
+        <v>22.131147540983605</v>
       </c>
       <c r="J44" s="10"/>
     </row>
@@ -2097,15 +2097,15 @@
       </c>
       <c r="D46" s="27">
         <f>MAX(D5:D44)</f>
-        <v>17740</v>
+        <v>26947</v>
       </c>
       <c r="G46" s="28">
         <f>IFERROR(MAX(G5:G44),"")</f>
-        <v>17.739999999999998</v>
+        <v>26.946999999999999</v>
       </c>
       <c r="I46" s="29">
         <f>IFERROR(AVERAGE(I5:I44),"")</f>
-        <v>7.0556905910258845</v>
+        <v>7.9894998949830791</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">

--- a/FAZENDA_PROMISSÃO_distancias.xlsx
+++ b/FAZENDA_PROMISSÃO_distancias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5174EB2-DB4D-4CEE-833A-7208E4F7E6CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7815F4DF-98F1-49A6-8EB3-1A43519E6DFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -72,121 +72,121 @@
     <t>Observação</t>
   </si>
   <si>
+    <t>T-01</t>
+  </si>
+  <si>
+    <t>T-30B</t>
+  </si>
+  <si>
+    <t>T-32A</t>
+  </si>
+  <si>
     <t>T-28</t>
   </si>
   <si>
+    <t>T-31A</t>
+  </si>
+  <si>
     <t>T-02</t>
   </si>
   <si>
-    <t>T-31A</t>
-  </si>
-  <si>
-    <t>T-32A</t>
+    <t>T-27</t>
+  </si>
+  <si>
+    <t>T-30A</t>
+  </si>
+  <si>
+    <t>T-32</t>
+  </si>
+  <si>
+    <t>T-08</t>
+  </si>
+  <si>
+    <t>T-29A</t>
   </si>
   <si>
     <t>T-03</t>
   </si>
   <si>
+    <t>T-31B</t>
+  </si>
+  <si>
+    <t>T-29B</t>
+  </si>
+  <si>
+    <t>T-10</t>
+  </si>
+  <si>
+    <t>T-11</t>
+  </si>
+  <si>
+    <t>T-07</t>
+  </si>
+  <si>
+    <t>T-26A</t>
+  </si>
+  <si>
+    <t>T-04</t>
+  </si>
+  <si>
+    <t>T-06</t>
+  </si>
+  <si>
+    <t>T-05</t>
+  </si>
+  <si>
     <t>T-09</t>
   </si>
   <si>
-    <t>T-05</t>
-  </si>
-  <si>
-    <t>T-11</t>
-  </si>
-  <si>
-    <t>T-10</t>
-  </si>
-  <si>
-    <t>T-32</t>
-  </si>
-  <si>
-    <t>T-06</t>
-  </si>
-  <si>
-    <t>T-07</t>
-  </si>
-  <si>
-    <t>T-27</t>
-  </si>
-  <si>
-    <t>T-30A</t>
-  </si>
-  <si>
-    <t>T-26A</t>
-  </si>
-  <si>
-    <t>T-29A</t>
-  </si>
-  <si>
-    <t>T-31B</t>
+    <t>T-30C</t>
   </si>
   <si>
     <t>T-26</t>
   </si>
   <si>
-    <t>T-08</t>
-  </si>
-  <si>
-    <t>T-30B</t>
-  </si>
-  <si>
-    <t>T-30C</t>
+    <t>T-13</t>
+  </si>
+  <si>
+    <t>T-12</t>
+  </si>
+  <si>
+    <t>T-24</t>
+  </si>
+  <si>
+    <t>T-25</t>
+  </si>
+  <si>
+    <t>T-29 C</t>
+  </si>
+  <si>
+    <t>T-14</t>
+  </si>
+  <si>
+    <t>T-15</t>
+  </si>
+  <si>
+    <t>T-19</t>
   </si>
   <si>
     <t>T-22</t>
   </si>
   <si>
-    <t>T-29B</t>
-  </si>
-  <si>
-    <t>T-29 C</t>
-  </si>
-  <si>
-    <t>T-01</t>
-  </si>
-  <si>
     <t>T-23</t>
   </si>
   <si>
-    <t>T-24</t>
-  </si>
-  <si>
-    <t>T-13</t>
-  </si>
-  <si>
-    <t>T-04</t>
+    <t>T-16</t>
+  </si>
+  <si>
+    <t>T-18</t>
   </si>
   <si>
     <t>T-20</t>
   </si>
   <si>
-    <t>T-25</t>
-  </si>
-  <si>
-    <t>T-14</t>
-  </si>
-  <si>
-    <t>T-15</t>
-  </si>
-  <si>
-    <t>T-12</t>
-  </si>
-  <si>
-    <t>T-19</t>
-  </si>
-  <si>
-    <t>T-16</t>
-  </si>
-  <si>
-    <t>T-18</t>
+    <t>T-21</t>
   </si>
   <si>
     <t>T-17</t>
-  </si>
-  <si>
-    <t>T-21</t>
   </si>
   <si>
     <t>T-29C</t>
@@ -376,6 +376,13 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -383,13 +390,6 @@
     <xf numFmtId="4" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -772,858 +772,858 @@
         <v>12</v>
       </c>
       <c r="B5" s="5">
-        <v>181.92</v>
+        <v>217.12</v>
       </c>
       <c r="C5" s="6">
-        <v>6154</v>
+        <v>6055</v>
       </c>
       <c r="D5" s="7">
-        <v>26947</v>
+        <v>12960</v>
       </c>
       <c r="E5" s="7">
-        <v>24849</v>
+        <v>10338</v>
       </c>
       <c r="F5" s="7">
-        <v>5748</v>
+        <v>7665</v>
       </c>
       <c r="G5" s="8">
         <f t="shared" ref="G5:G44" si="0">D5/1000</f>
-        <v>26.946999999999999</v>
+        <v>12.96</v>
       </c>
       <c r="H5" s="8">
         <f t="shared" ref="H5:H44" si="1">E5/1000</f>
-        <v>24.849</v>
+        <v>10.337999999999999</v>
       </c>
       <c r="I5" s="9">
         <f t="shared" ref="I5:I44" si="2">IFERROR(D5/F5,"")</f>
-        <v>4.6880654140570632</v>
+        <v>1.6908023483365948</v>
       </c>
       <c r="J5" s="10"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="5">
-        <v>216.07</v>
-      </c>
-      <c r="C6" s="6">
-        <v>5881</v>
-      </c>
-      <c r="D6" s="7">
-        <v>25800</v>
-      </c>
-      <c r="E6" s="7">
-        <v>24267</v>
-      </c>
-      <c r="F6" s="7">
-        <v>6496</v>
-      </c>
-      <c r="G6" s="8">
-        <f t="shared" si="0"/>
-        <v>25.8</v>
-      </c>
-      <c r="H6" s="8">
-        <f t="shared" si="1"/>
-        <v>24.266999999999999</v>
-      </c>
-      <c r="I6" s="9">
-        <f t="shared" si="2"/>
-        <v>3.9716748768472905</v>
-      </c>
-      <c r="J6" s="10"/>
+      <c r="B6" s="12">
+        <v>129.79</v>
+      </c>
+      <c r="C6" s="13">
+        <v>4831</v>
+      </c>
+      <c r="D6" s="14">
+        <v>12959</v>
+      </c>
+      <c r="E6" s="14">
+        <v>11538</v>
+      </c>
+      <c r="F6" s="14">
+        <v>3323</v>
+      </c>
+      <c r="G6" s="15">
+        <f t="shared" si="0"/>
+        <v>12.959</v>
+      </c>
+      <c r="H6" s="15">
+        <f t="shared" si="1"/>
+        <v>11.538</v>
+      </c>
+      <c r="I6" s="16">
+        <f t="shared" si="2"/>
+        <v>3.8997893469756244</v>
+      </c>
+      <c r="J6" s="17"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="5">
-        <v>132.85</v>
+        <v>83.99</v>
       </c>
       <c r="C7" s="6">
-        <v>5047</v>
+        <v>4543</v>
       </c>
       <c r="D7" s="7">
-        <v>24908</v>
+        <v>12518</v>
       </c>
       <c r="E7" s="7">
-        <v>23846</v>
+        <v>10768</v>
       </c>
       <c r="F7" s="7">
-        <v>4795</v>
+        <v>6182</v>
       </c>
       <c r="G7" s="8">
         <f t="shared" si="0"/>
-        <v>24.908000000000001</v>
+        <v>12.518000000000001</v>
       </c>
       <c r="H7" s="8">
         <f t="shared" si="1"/>
-        <v>23.846</v>
+        <v>10.768000000000001</v>
       </c>
       <c r="I7" s="9">
         <f t="shared" si="2"/>
-        <v>5.1945776850886336</v>
+        <v>2.0249110320284696</v>
       </c>
       <c r="J7" s="10"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="5">
-        <v>83.99</v>
-      </c>
-      <c r="C8" s="6">
-        <v>4543</v>
-      </c>
-      <c r="D8" s="7">
-        <v>23900</v>
-      </c>
-      <c r="E8" s="7">
-        <v>21482</v>
-      </c>
-      <c r="F8" s="7">
-        <v>6182</v>
-      </c>
-      <c r="G8" s="8">
-        <f t="shared" si="0"/>
-        <v>23.9</v>
-      </c>
-      <c r="H8" s="8">
-        <f t="shared" si="1"/>
-        <v>21.481999999999999</v>
-      </c>
-      <c r="I8" s="9">
-        <f t="shared" si="2"/>
-        <v>3.866062762859916</v>
-      </c>
-      <c r="J8" s="10"/>
+      <c r="B8" s="19">
+        <v>181.92</v>
+      </c>
+      <c r="C8" s="20">
+        <v>6154</v>
+      </c>
+      <c r="D8" s="21">
+        <v>12214</v>
+      </c>
+      <c r="E8" s="21">
+        <v>9304</v>
+      </c>
+      <c r="F8" s="21">
+        <v>5748</v>
+      </c>
+      <c r="G8" s="22">
+        <f t="shared" si="0"/>
+        <v>12.214</v>
+      </c>
+      <c r="H8" s="22">
+        <f t="shared" si="1"/>
+        <v>9.3040000000000003</v>
+      </c>
+      <c r="I8" s="23">
+        <f t="shared" si="2"/>
+        <v>2.1249130132219904</v>
+      </c>
+      <c r="J8" s="24"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B9" s="5">
-        <v>215.16</v>
+        <v>132.85</v>
       </c>
       <c r="C9" s="6">
-        <v>5870</v>
+        <v>5047</v>
       </c>
       <c r="D9" s="7">
-        <v>22825</v>
+        <v>12191</v>
       </c>
       <c r="E9" s="7">
-        <v>21300</v>
+        <v>10345</v>
       </c>
       <c r="F9" s="7">
-        <v>5463</v>
+        <v>4795</v>
       </c>
       <c r="G9" s="8">
         <f t="shared" si="0"/>
-        <v>22.824999999999999</v>
+        <v>12.191000000000001</v>
       </c>
       <c r="H9" s="8">
         <f t="shared" si="1"/>
-        <v>21.3</v>
+        <v>10.345000000000001</v>
       </c>
       <c r="I9" s="9">
         <f t="shared" si="2"/>
-        <v>4.1781072670693762</v>
+        <v>2.5424400417101145</v>
       </c>
       <c r="J9" s="10"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="5">
-        <v>136.16</v>
-      </c>
-      <c r="C10" s="6">
-        <v>5252</v>
-      </c>
-      <c r="D10" s="7">
-        <v>22812</v>
-      </c>
-      <c r="E10" s="7">
-        <v>17958</v>
-      </c>
-      <c r="F10" s="7">
-        <v>5369</v>
-      </c>
-      <c r="G10" s="8">
-        <f t="shared" si="0"/>
-        <v>22.812000000000001</v>
-      </c>
-      <c r="H10" s="8">
-        <f t="shared" si="1"/>
-        <v>17.957999999999998</v>
-      </c>
-      <c r="I10" s="9">
-        <f t="shared" si="2"/>
-        <v>4.2488359098528594</v>
-      </c>
-      <c r="J10" s="10"/>
+      <c r="B10" s="19">
+        <v>216.07</v>
+      </c>
+      <c r="C10" s="20">
+        <v>5881</v>
+      </c>
+      <c r="D10" s="21">
+        <v>11900</v>
+      </c>
+      <c r="E10" s="21">
+        <v>8902</v>
+      </c>
+      <c r="F10" s="21">
+        <v>6496</v>
+      </c>
+      <c r="G10" s="22">
+        <f t="shared" si="0"/>
+        <v>11.9</v>
+      </c>
+      <c r="H10" s="22">
+        <f t="shared" si="1"/>
+        <v>8.9019999999999992</v>
+      </c>
+      <c r="I10" s="23">
+        <f t="shared" si="2"/>
+        <v>1.8318965517241379</v>
+      </c>
+      <c r="J10" s="24"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="5">
-        <v>176.55</v>
+        <v>248.35</v>
       </c>
       <c r="C11" s="6">
-        <v>7594</v>
+        <v>7351</v>
       </c>
       <c r="D11" s="7">
-        <v>22477</v>
+        <v>11757</v>
       </c>
       <c r="E11" s="7">
-        <v>21218</v>
+        <v>8266</v>
       </c>
       <c r="F11" s="7">
-        <v>3538</v>
+        <v>4648</v>
       </c>
       <c r="G11" s="8">
         <f t="shared" si="0"/>
-        <v>22.477</v>
+        <v>11.757</v>
       </c>
       <c r="H11" s="8">
         <f t="shared" si="1"/>
-        <v>21.218</v>
+        <v>8.266</v>
       </c>
       <c r="I11" s="9">
         <f t="shared" si="2"/>
-        <v>6.3530243075183721</v>
+        <v>2.5294750430292599</v>
       </c>
       <c r="J11" s="10"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="5">
-        <v>303.27</v>
-      </c>
-      <c r="C12" s="6">
-        <v>7420</v>
-      </c>
-      <c r="D12" s="7">
-        <v>22477</v>
-      </c>
-      <c r="E12" s="7">
-        <v>19803</v>
-      </c>
-      <c r="F12" s="7">
-        <v>2827</v>
-      </c>
-      <c r="G12" s="8">
-        <f t="shared" si="0"/>
-        <v>22.477</v>
-      </c>
-      <c r="H12" s="8">
-        <f t="shared" si="1"/>
-        <v>19.803000000000001</v>
-      </c>
-      <c r="I12" s="9">
-        <f t="shared" si="2"/>
-        <v>7.9508312698974182</v>
-      </c>
-      <c r="J12" s="10"/>
+      <c r="B12" s="19">
+        <v>101.07</v>
+      </c>
+      <c r="C12" s="20">
+        <v>4286</v>
+      </c>
+      <c r="D12" s="21">
+        <v>11588</v>
+      </c>
+      <c r="E12" s="21">
+        <v>8542</v>
+      </c>
+      <c r="F12" s="21">
+        <v>4476</v>
+      </c>
+      <c r="G12" s="22">
+        <f t="shared" si="0"/>
+        <v>11.587999999999999</v>
+      </c>
+      <c r="H12" s="22">
+        <f t="shared" si="1"/>
+        <v>8.5419999999999998</v>
+      </c>
+      <c r="I12" s="23">
+        <f t="shared" si="2"/>
+        <v>2.5889186773905273</v>
+      </c>
+      <c r="J12" s="24"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B13" s="5">
-        <v>225.86</v>
+        <v>138.68</v>
       </c>
       <c r="C13" s="6">
-        <v>6836</v>
+        <v>5245</v>
       </c>
       <c r="D13" s="7">
-        <v>21841</v>
+        <v>11407</v>
       </c>
       <c r="E13" s="7">
-        <v>18362</v>
+        <v>9282</v>
       </c>
       <c r="F13" s="7">
-        <v>3960</v>
+        <v>4871</v>
       </c>
       <c r="G13" s="8">
         <f t="shared" si="0"/>
-        <v>21.841000000000001</v>
+        <v>11.407</v>
       </c>
       <c r="H13" s="8">
         <f t="shared" si="1"/>
-        <v>18.361999999999998</v>
+        <v>9.282</v>
       </c>
       <c r="I13" s="9">
         <f t="shared" si="2"/>
-        <v>5.5154040404040403</v>
+        <v>2.3418189283514677</v>
       </c>
       <c r="J13" s="10"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="5">
-        <v>138.68</v>
-      </c>
-      <c r="C14" s="6">
-        <v>5245</v>
-      </c>
-      <c r="D14" s="7">
-        <v>21534</v>
-      </c>
-      <c r="E14" s="7">
-        <v>19410</v>
-      </c>
-      <c r="F14" s="7">
-        <v>4871</v>
-      </c>
-      <c r="G14" s="8">
-        <f t="shared" si="0"/>
-        <v>21.533999999999999</v>
-      </c>
-      <c r="H14" s="8">
-        <f t="shared" si="1"/>
-        <v>19.41</v>
-      </c>
-      <c r="I14" s="9">
-        <f t="shared" si="2"/>
-        <v>4.4208581400123181</v>
-      </c>
-      <c r="J14" s="10"/>
+      <c r="B14" s="19">
+        <v>128.52000000000001</v>
+      </c>
+      <c r="C14" s="20">
+        <v>5847</v>
+      </c>
+      <c r="D14" s="21">
+        <v>11236</v>
+      </c>
+      <c r="E14" s="21">
+        <v>7756</v>
+      </c>
+      <c r="F14" s="21">
+        <v>6977</v>
+      </c>
+      <c r="G14" s="22">
+        <f t="shared" si="0"/>
+        <v>11.236000000000001</v>
+      </c>
+      <c r="H14" s="22">
+        <f t="shared" si="1"/>
+        <v>7.7560000000000002</v>
+      </c>
+      <c r="I14" s="23">
+        <f t="shared" si="2"/>
+        <v>1.6104342840762504</v>
+      </c>
+      <c r="J14" s="24"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>22</v>
       </c>
       <c r="B15" s="5">
-        <v>211.14</v>
+        <v>158.57</v>
       </c>
       <c r="C15" s="6">
-        <v>5814</v>
+        <v>5634</v>
       </c>
       <c r="D15" s="7">
-        <v>21354</v>
+        <v>10904</v>
       </c>
       <c r="E15" s="7">
-        <v>19803</v>
+        <v>7276</v>
       </c>
       <c r="F15" s="7">
-        <v>4461</v>
+        <v>3705</v>
       </c>
       <c r="G15" s="8">
         <f t="shared" si="0"/>
-        <v>21.353999999999999</v>
+        <v>10.904</v>
       </c>
       <c r="H15" s="8">
         <f t="shared" si="1"/>
-        <v>19.803000000000001</v>
+        <v>7.2759999999999998</v>
       </c>
       <c r="I15" s="9">
         <f t="shared" si="2"/>
-        <v>4.7868190988567587</v>
+        <v>2.9430499325236168</v>
       </c>
       <c r="J15" s="10"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="5">
-        <v>214</v>
-      </c>
-      <c r="C16" s="6">
-        <v>5853</v>
-      </c>
-      <c r="D16" s="7">
-        <v>21326</v>
-      </c>
-      <c r="E16" s="7">
-        <v>18362</v>
-      </c>
-      <c r="F16" s="7">
-        <v>5666</v>
-      </c>
-      <c r="G16" s="8">
-        <f t="shared" si="0"/>
-        <v>21.326000000000001</v>
-      </c>
-      <c r="H16" s="8">
-        <f t="shared" si="1"/>
-        <v>18.361999999999998</v>
-      </c>
-      <c r="I16" s="9">
-        <f t="shared" si="2"/>
-        <v>3.7638545711260147</v>
-      </c>
-      <c r="J16" s="10"/>
+      <c r="B16" s="19">
+        <v>215.16</v>
+      </c>
+      <c r="C16" s="20">
+        <v>5870</v>
+      </c>
+      <c r="D16" s="21">
+        <v>10437</v>
+      </c>
+      <c r="E16" s="21">
+        <v>7458</v>
+      </c>
+      <c r="F16" s="21">
+        <v>5463</v>
+      </c>
+      <c r="G16" s="22">
+        <f t="shared" si="0"/>
+        <v>10.436999999999999</v>
+      </c>
+      <c r="H16" s="22">
+        <f t="shared" si="1"/>
+        <v>7.4580000000000002</v>
+      </c>
+      <c r="I16" s="23">
+        <f t="shared" si="2"/>
+        <v>1.9104887424492036</v>
+      </c>
+      <c r="J16" s="24"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>24</v>
       </c>
       <c r="B17" s="5">
-        <v>248.35</v>
+        <v>89.83</v>
       </c>
       <c r="C17" s="6">
-        <v>7351</v>
+        <v>4143</v>
       </c>
       <c r="D17" s="7">
-        <v>20889</v>
+        <v>10403</v>
       </c>
       <c r="E17" s="7">
-        <v>18393</v>
+        <v>8249</v>
       </c>
       <c r="F17" s="7">
-        <v>4648</v>
+        <v>3986</v>
       </c>
       <c r="G17" s="8">
         <f t="shared" si="0"/>
-        <v>20.888999999999999</v>
+        <v>10.403</v>
       </c>
       <c r="H17" s="8">
         <f t="shared" si="1"/>
-        <v>18.393000000000001</v>
+        <v>8.2490000000000006</v>
       </c>
       <c r="I17" s="9">
         <f t="shared" si="2"/>
-        <v>4.4941910499139412</v>
+        <v>2.6098845960863022</v>
       </c>
       <c r="J17" s="10"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="5">
-        <v>101.07</v>
-      </c>
-      <c r="C18" s="6">
-        <v>4286</v>
-      </c>
-      <c r="D18" s="7">
-        <v>20556</v>
-      </c>
-      <c r="E18" s="7">
-        <v>20519</v>
-      </c>
-      <c r="F18" s="7">
-        <v>4476</v>
-      </c>
-      <c r="G18" s="8">
-        <f t="shared" si="0"/>
-        <v>20.556000000000001</v>
-      </c>
-      <c r="H18" s="8">
-        <f t="shared" si="1"/>
-        <v>20.518999999999998</v>
-      </c>
-      <c r="I18" s="9">
-        <f t="shared" si="2"/>
-        <v>4.5924932975871311</v>
-      </c>
-      <c r="J18" s="10"/>
+      <c r="B18" s="12">
+        <v>115.08</v>
+      </c>
+      <c r="C18" s="13">
+        <v>5656</v>
+      </c>
+      <c r="D18" s="14">
+        <v>9988</v>
+      </c>
+      <c r="E18" s="14">
+        <v>5844</v>
+      </c>
+      <c r="F18" s="14">
+        <v>2262</v>
+      </c>
+      <c r="G18" s="15">
+        <f t="shared" si="0"/>
+        <v>9.9879999999999995</v>
+      </c>
+      <c r="H18" s="15">
+        <f t="shared" si="1"/>
+        <v>5.8440000000000003</v>
+      </c>
+      <c r="I18" s="16">
+        <f t="shared" si="2"/>
+        <v>4.4155614500442084</v>
+      </c>
+      <c r="J18" s="17"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>26</v>
       </c>
       <c r="B19" s="5">
-        <v>127.51</v>
+        <v>225.86</v>
       </c>
       <c r="C19" s="6">
-        <v>5515</v>
+        <v>6836</v>
       </c>
       <c r="D19" s="7">
-        <v>19795</v>
+        <v>9444</v>
       </c>
       <c r="E19" s="7">
-        <v>17710</v>
+        <v>4349</v>
       </c>
       <c r="F19" s="7">
-        <v>2671</v>
+        <v>3960</v>
       </c>
       <c r="G19" s="8">
         <f t="shared" si="0"/>
-        <v>19.795000000000002</v>
+        <v>9.4440000000000008</v>
       </c>
       <c r="H19" s="8">
         <f t="shared" si="1"/>
-        <v>17.71</v>
+        <v>4.3490000000000002</v>
       </c>
       <c r="I19" s="9">
         <f t="shared" si="2"/>
-        <v>7.4110819917633846</v>
+        <v>2.3848484848484848</v>
       </c>
       <c r="J19" s="10"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="B20" s="5">
-        <v>158.57</v>
-      </c>
-      <c r="C20" s="6">
-        <v>5634</v>
-      </c>
-      <c r="D20" s="7">
-        <v>19482</v>
-      </c>
-      <c r="E20" s="7">
-        <v>17403</v>
-      </c>
-      <c r="F20" s="7">
-        <v>3705</v>
-      </c>
-      <c r="G20" s="8">
-        <f t="shared" si="0"/>
-        <v>19.481999999999999</v>
-      </c>
-      <c r="H20" s="8">
-        <f t="shared" si="1"/>
-        <v>17.402999999999999</v>
-      </c>
-      <c r="I20" s="9">
-        <f t="shared" si="2"/>
-        <v>5.2582995951417004</v>
-      </c>
-      <c r="J20" s="10"/>
+      <c r="B20" s="12">
+        <v>303.27</v>
+      </c>
+      <c r="C20" s="13">
+        <v>7420</v>
+      </c>
+      <c r="D20" s="14">
+        <v>9444</v>
+      </c>
+      <c r="E20" s="14">
+        <v>3158</v>
+      </c>
+      <c r="F20" s="14">
+        <v>2827</v>
+      </c>
+      <c r="G20" s="15">
+        <f t="shared" si="0"/>
+        <v>9.4440000000000008</v>
+      </c>
+      <c r="H20" s="15">
+        <f t="shared" si="1"/>
+        <v>3.1579999999999999</v>
+      </c>
+      <c r="I20" s="16">
+        <f t="shared" si="2"/>
+        <v>3.3406437920056598</v>
+      </c>
+      <c r="J20" s="17"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>28</v>
       </c>
       <c r="B21" s="5">
-        <v>89.83</v>
+        <v>214</v>
       </c>
       <c r="C21" s="6">
-        <v>4143</v>
+        <v>5853</v>
       </c>
       <c r="D21" s="7">
-        <v>19468</v>
+        <v>9307</v>
       </c>
       <c r="E21" s="7">
-        <v>18376</v>
+        <v>7403</v>
       </c>
       <c r="F21" s="7">
-        <v>3986</v>
+        <v>5666</v>
       </c>
       <c r="G21" s="8">
         <f t="shared" si="0"/>
-        <v>19.468</v>
+        <v>9.3070000000000004</v>
       </c>
       <c r="H21" s="8">
         <f t="shared" si="1"/>
-        <v>18.376000000000001</v>
+        <v>7.4029999999999996</v>
       </c>
       <c r="I21" s="9">
         <f t="shared" si="2"/>
-        <v>4.8840943301555448</v>
+        <v>1.6426050123543947</v>
       </c>
       <c r="J21" s="10"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="5">
-        <v>147.1</v>
-      </c>
-      <c r="C22" s="6">
-        <v>5457</v>
-      </c>
-      <c r="D22" s="7">
-        <v>19279</v>
-      </c>
-      <c r="E22" s="7">
-        <v>15615</v>
-      </c>
-      <c r="F22" s="7">
-        <v>1631</v>
-      </c>
-      <c r="G22" s="8">
-        <f t="shared" si="0"/>
-        <v>19.279</v>
-      </c>
-      <c r="H22" s="8">
-        <f t="shared" si="1"/>
-        <v>15.615</v>
-      </c>
-      <c r="I22" s="9">
-        <f t="shared" si="2"/>
-        <v>11.820355610055181</v>
-      </c>
-      <c r="J22" s="10"/>
+      <c r="B22" s="12">
+        <v>127.51</v>
+      </c>
+      <c r="C22" s="13">
+        <v>5515</v>
+      </c>
+      <c r="D22" s="14">
+        <v>9225</v>
+      </c>
+      <c r="E22" s="14">
+        <v>7276</v>
+      </c>
+      <c r="F22" s="14">
+        <v>2671</v>
+      </c>
+      <c r="G22" s="15">
+        <f t="shared" si="0"/>
+        <v>9.2249999999999996</v>
+      </c>
+      <c r="H22" s="15">
+        <f t="shared" si="1"/>
+        <v>7.2759999999999998</v>
+      </c>
+      <c r="I22" s="16">
+        <f t="shared" si="2"/>
+        <v>3.4537626357169597</v>
+      </c>
+      <c r="J22" s="17"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A23" s="11" t="s">
+      <c r="A23" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B23" s="12">
-        <v>128.52000000000001</v>
-      </c>
-      <c r="C23" s="13">
-        <v>5847</v>
-      </c>
-      <c r="D23" s="14">
-        <v>18414</v>
-      </c>
-      <c r="E23" s="14">
-        <v>15328</v>
-      </c>
-      <c r="F23" s="14">
-        <v>6977</v>
-      </c>
-      <c r="G23" s="15">
-        <f t="shared" si="0"/>
-        <v>18.414000000000001</v>
-      </c>
-      <c r="H23" s="15">
-        <f t="shared" si="1"/>
-        <v>15.327999999999999</v>
-      </c>
-      <c r="I23" s="16">
-        <f t="shared" si="2"/>
-        <v>2.6392432277483158</v>
-      </c>
-      <c r="J23" s="17"/>
+      <c r="B23" s="5">
+        <v>222.45</v>
+      </c>
+      <c r="C23" s="6">
+        <v>5898</v>
+      </c>
+      <c r="D23" s="7">
+        <v>9106</v>
+      </c>
+      <c r="E23" s="7">
+        <v>6252</v>
+      </c>
+      <c r="F23" s="7">
+        <v>4632</v>
+      </c>
+      <c r="G23" s="8">
+        <f t="shared" si="0"/>
+        <v>9.1059999999999999</v>
+      </c>
+      <c r="H23" s="8">
+        <f t="shared" si="1"/>
+        <v>6.2519999999999998</v>
+      </c>
+      <c r="I23" s="9">
+        <f t="shared" si="2"/>
+        <v>1.9658894645941278</v>
+      </c>
+      <c r="J23" s="10"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="B24" s="5">
-        <v>129.79</v>
-      </c>
-      <c r="C24" s="6">
-        <v>4831</v>
-      </c>
-      <c r="D24" s="7">
-        <v>18408</v>
-      </c>
-      <c r="E24" s="7">
-        <v>17363</v>
-      </c>
-      <c r="F24" s="7">
-        <v>3323</v>
-      </c>
-      <c r="G24" s="8">
-        <f t="shared" si="0"/>
-        <v>18.408000000000001</v>
-      </c>
-      <c r="H24" s="8">
-        <f t="shared" si="1"/>
-        <v>17.363</v>
-      </c>
-      <c r="I24" s="9">
-        <f t="shared" si="2"/>
-        <v>5.5395726752934094</v>
-      </c>
-      <c r="J24" s="10"/>
+      <c r="B24" s="19">
+        <v>211.14</v>
+      </c>
+      <c r="C24" s="20">
+        <v>5814</v>
+      </c>
+      <c r="D24" s="21">
+        <v>8958</v>
+      </c>
+      <c r="E24" s="21">
+        <v>5988</v>
+      </c>
+      <c r="F24" s="21">
+        <v>4461</v>
+      </c>
+      <c r="G24" s="22">
+        <f t="shared" si="0"/>
+        <v>8.9580000000000002</v>
+      </c>
+      <c r="H24" s="22">
+        <f t="shared" si="1"/>
+        <v>5.9880000000000004</v>
+      </c>
+      <c r="I24" s="23">
+        <f t="shared" si="2"/>
+        <v>2.0080699394754538</v>
+      </c>
+      <c r="J24" s="24"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>32</v>
       </c>
       <c r="B25" s="5">
-        <v>53.2</v>
+        <v>176.55</v>
       </c>
       <c r="C25" s="6">
-        <v>3095</v>
+        <v>7594</v>
       </c>
       <c r="D25" s="7">
-        <v>18408</v>
+        <v>8953</v>
       </c>
       <c r="E25" s="7">
-        <v>17333</v>
+        <v>4746</v>
       </c>
       <c r="F25" s="7">
-        <v>3321</v>
+        <v>3538</v>
       </c>
       <c r="G25" s="8">
         <f t="shared" si="0"/>
-        <v>18.408000000000001</v>
+        <v>8.9529999999999994</v>
       </c>
       <c r="H25" s="8">
         <f t="shared" si="1"/>
-        <v>17.332999999999998</v>
+        <v>4.7460000000000004</v>
       </c>
       <c r="I25" s="9">
         <f t="shared" si="2"/>
-        <v>5.5429087624209572</v>
+        <v>2.5305257207461844</v>
       </c>
       <c r="J25" s="10"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="B26" s="5">
-        <v>268.29000000000002</v>
-      </c>
-      <c r="C26" s="6">
-        <v>6666</v>
-      </c>
-      <c r="D26" s="7">
-        <v>17728</v>
-      </c>
-      <c r="E26" s="7">
-        <v>12669</v>
-      </c>
-      <c r="F26" s="7">
-        <v>954</v>
-      </c>
-      <c r="G26" s="8">
-        <f t="shared" si="0"/>
-        <v>17.728000000000002</v>
-      </c>
-      <c r="H26" s="8">
-        <f t="shared" si="1"/>
-        <v>12.669</v>
-      </c>
-      <c r="I26" s="9">
-        <f t="shared" si="2"/>
-        <v>18.582809224318659</v>
-      </c>
-      <c r="J26" s="10"/>
+      <c r="B26" s="19">
+        <v>136.16</v>
+      </c>
+      <c r="C26" s="20">
+        <v>5252</v>
+      </c>
+      <c r="D26" s="21">
+        <v>8435</v>
+      </c>
+      <c r="E26" s="21">
+        <v>5773</v>
+      </c>
+      <c r="F26" s="21">
+        <v>5369</v>
+      </c>
+      <c r="G26" s="22">
+        <f t="shared" si="0"/>
+        <v>8.4350000000000005</v>
+      </c>
+      <c r="H26" s="22">
+        <f t="shared" si="1"/>
+        <v>5.7729999999999997</v>
+      </c>
+      <c r="I26" s="23">
+        <f t="shared" si="2"/>
+        <v>1.5710560625814862</v>
+      </c>
+      <c r="J26" s="24"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>34</v>
       </c>
       <c r="B27" s="5">
-        <v>115.08</v>
+        <v>53.2</v>
       </c>
       <c r="C27" s="6">
-        <v>5656</v>
+        <v>3095</v>
       </c>
       <c r="D27" s="7">
-        <v>17453</v>
+        <v>8289</v>
       </c>
       <c r="E27" s="7">
-        <v>15971</v>
+        <v>7205</v>
       </c>
       <c r="F27" s="7">
-        <v>2262</v>
+        <v>3321</v>
       </c>
       <c r="G27" s="8">
         <f t="shared" si="0"/>
-        <v>17.452999999999999</v>
+        <v>8.2889999999999997</v>
       </c>
       <c r="H27" s="8">
         <f t="shared" si="1"/>
-        <v>15.971</v>
+        <v>7.2050000000000001</v>
       </c>
       <c r="I27" s="9">
         <f t="shared" si="2"/>
-        <v>7.7157382847038019</v>
+        <v>2.4959349593495936</v>
       </c>
       <c r="J27" s="10"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B28" s="5">
-        <v>23</v>
-      </c>
-      <c r="C28" s="6">
-        <v>3375</v>
-      </c>
-      <c r="D28" s="7">
-        <v>17363</v>
-      </c>
-      <c r="E28" s="7">
-        <v>15928</v>
-      </c>
-      <c r="F28" s="7">
-        <v>2251</v>
-      </c>
-      <c r="G28" s="8">
-        <f t="shared" si="0"/>
-        <v>17.363</v>
-      </c>
-      <c r="H28" s="8">
-        <f t="shared" si="1"/>
-        <v>15.928000000000001</v>
-      </c>
-      <c r="I28" s="9">
-        <f t="shared" si="2"/>
-        <v>7.7134606841403821</v>
-      </c>
-      <c r="J28" s="10"/>
+      <c r="B28" s="12">
+        <v>147.1</v>
+      </c>
+      <c r="C28" s="13">
+        <v>5457</v>
+      </c>
+      <c r="D28" s="14">
+        <v>8224</v>
+      </c>
+      <c r="E28" s="14">
+        <v>5488</v>
+      </c>
+      <c r="F28" s="14">
+        <v>1631</v>
+      </c>
+      <c r="G28" s="15">
+        <f t="shared" si="0"/>
+        <v>8.2240000000000002</v>
+      </c>
+      <c r="H28" s="15">
+        <f t="shared" si="1"/>
+        <v>5.4880000000000004</v>
+      </c>
+      <c r="I28" s="16">
+        <f t="shared" si="2"/>
+        <v>5.0423053341508277</v>
+      </c>
+      <c r="J28" s="17"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A29" s="11" t="s">
+      <c r="A29" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B29" s="12">
-        <v>217.12</v>
-      </c>
-      <c r="C29" s="13">
-        <v>6055</v>
-      </c>
-      <c r="D29" s="14">
-        <v>15384</v>
-      </c>
-      <c r="E29" s="14">
-        <v>12085</v>
-      </c>
-      <c r="F29" s="14">
-        <v>7665</v>
-      </c>
-      <c r="G29" s="15">
-        <f t="shared" si="0"/>
-        <v>15.384</v>
-      </c>
-      <c r="H29" s="15">
-        <f t="shared" si="1"/>
-        <v>12.085000000000001</v>
-      </c>
-      <c r="I29" s="16">
-        <f t="shared" si="2"/>
-        <v>2.0070450097847359</v>
-      </c>
-      <c r="J29" s="17"/>
+      <c r="B29" s="5">
+        <v>198.71</v>
+      </c>
+      <c r="C29" s="6">
+        <v>5502</v>
+      </c>
+      <c r="D29" s="7">
+        <v>8048</v>
+      </c>
+      <c r="E29" s="7">
+        <v>5261</v>
+      </c>
+      <c r="F29" s="7">
+        <v>4181</v>
+      </c>
+      <c r="G29" s="8">
+        <f t="shared" si="0"/>
+        <v>8.048</v>
+      </c>
+      <c r="H29" s="8">
+        <f t="shared" si="1"/>
+        <v>5.2610000000000001</v>
+      </c>
+      <c r="I29" s="9">
+        <f t="shared" si="2"/>
+        <v>1.9248983496771108</v>
+      </c>
+      <c r="J29" s="10"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="B30" s="5">
-        <v>249.78</v>
-      </c>
-      <c r="C30" s="6">
-        <v>6425</v>
-      </c>
-      <c r="D30" s="7">
-        <v>12684</v>
-      </c>
-      <c r="E30" s="7">
-        <v>9393</v>
-      </c>
-      <c r="F30" s="7">
-        <v>1605</v>
-      </c>
-      <c r="G30" s="8">
-        <f t="shared" si="0"/>
-        <v>12.683999999999999</v>
-      </c>
-      <c r="H30" s="8">
-        <f t="shared" si="1"/>
-        <v>9.3930000000000007</v>
-      </c>
-      <c r="I30" s="9">
-        <f t="shared" si="2"/>
-        <v>7.9028037383177567</v>
-      </c>
-      <c r="J30" s="10"/>
+      <c r="B30" s="19">
+        <v>196.2</v>
+      </c>
+      <c r="C30" s="20">
+        <v>5516</v>
+      </c>
+      <c r="D30" s="21">
+        <v>7944</v>
+      </c>
+      <c r="E30" s="21">
+        <v>4263</v>
+      </c>
+      <c r="F30" s="21">
+        <v>3785</v>
+      </c>
+      <c r="G30" s="22">
+        <f t="shared" si="0"/>
+        <v>7.944</v>
+      </c>
+      <c r="H30" s="22">
+        <f t="shared" si="1"/>
+        <v>4.2629999999999999</v>
+      </c>
+      <c r="I30" s="23">
+        <f t="shared" si="2"/>
+        <v>2.0988110964332893</v>
+      </c>
+      <c r="J30" s="24"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
@@ -1636,7 +1636,7 @@
         <v>7098</v>
       </c>
       <c r="D31" s="7">
-        <v>9423</v>
+        <v>7392</v>
       </c>
       <c r="E31" s="7">
         <v>3998</v>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="G31" s="8">
         <f t="shared" si="0"/>
-        <v>9.423</v>
+        <v>7.3920000000000003</v>
       </c>
       <c r="H31" s="8">
         <f t="shared" si="1"/>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="I31" s="9">
         <f t="shared" si="2"/>
-        <v>3.3533807829181494</v>
+        <v>2.6306049822064055</v>
       </c>
       <c r="J31" s="10"/>
     </row>
@@ -1663,31 +1663,31 @@
         <v>39</v>
       </c>
       <c r="B32" s="19">
-        <v>198.71</v>
+        <v>128.41999999999999</v>
       </c>
       <c r="C32" s="20">
-        <v>5502</v>
+        <v>6551</v>
       </c>
       <c r="D32" s="21">
-        <v>9372</v>
+        <v>7330</v>
       </c>
       <c r="E32" s="21">
-        <v>5868</v>
+        <v>3998</v>
       </c>
       <c r="F32" s="21">
-        <v>4181</v>
+        <v>2542</v>
       </c>
       <c r="G32" s="22">
         <f t="shared" si="0"/>
-        <v>9.3719999999999999</v>
+        <v>7.33</v>
       </c>
       <c r="H32" s="22">
         <f t="shared" si="1"/>
-        <v>5.8680000000000003</v>
+        <v>3.9980000000000002</v>
       </c>
       <c r="I32" s="23">
         <f t="shared" si="2"/>
-        <v>2.2415690026309494</v>
+        <v>2.8835562549173881</v>
       </c>
       <c r="J32" s="24"/>
     </row>
@@ -1696,130 +1696,130 @@
         <v>40</v>
       </c>
       <c r="B33" s="12">
-        <v>222.45</v>
+        <v>23</v>
       </c>
       <c r="C33" s="13">
-        <v>5898</v>
+        <v>3375</v>
       </c>
       <c r="D33" s="14">
-        <v>9262</v>
+        <v>7236</v>
       </c>
       <c r="E33" s="14">
-        <v>6251</v>
+        <v>5801</v>
       </c>
       <c r="F33" s="14">
-        <v>4632</v>
+        <v>2251</v>
       </c>
       <c r="G33" s="15">
         <f t="shared" si="0"/>
-        <v>9.2620000000000005</v>
+        <v>7.2359999999999998</v>
       </c>
       <c r="H33" s="15">
         <f t="shared" si="1"/>
-        <v>6.2510000000000003</v>
+        <v>5.8010000000000002</v>
       </c>
       <c r="I33" s="16">
         <f t="shared" si="2"/>
-        <v>1.9995682210708117</v>
+        <v>3.2145713016437139</v>
       </c>
       <c r="J33" s="17"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="B34" s="5">
-        <v>240.55</v>
-      </c>
-      <c r="C34" s="6">
-        <v>9293</v>
-      </c>
-      <c r="D34" s="7">
-        <v>8086</v>
-      </c>
-      <c r="E34" s="7">
-        <v>1210</v>
-      </c>
-      <c r="F34" s="7">
-        <v>1215</v>
-      </c>
-      <c r="G34" s="8">
-        <f t="shared" si="0"/>
-        <v>8.0860000000000003</v>
-      </c>
-      <c r="H34" s="8">
-        <f t="shared" si="1"/>
-        <v>1.21</v>
-      </c>
-      <c r="I34" s="9">
-        <f t="shared" si="2"/>
-        <v>6.655144032921811</v>
-      </c>
-      <c r="J34" s="10"/>
+      <c r="B34" s="19">
+        <v>180.97</v>
+      </c>
+      <c r="C34" s="20">
+        <v>5840</v>
+      </c>
+      <c r="D34" s="21">
+        <v>6924</v>
+      </c>
+      <c r="E34" s="21">
+        <v>4279</v>
+      </c>
+      <c r="F34" s="21">
+        <v>3349</v>
+      </c>
+      <c r="G34" s="22">
+        <f t="shared" si="0"/>
+        <v>6.9240000000000004</v>
+      </c>
+      <c r="H34" s="22">
+        <f t="shared" si="1"/>
+        <v>4.2789999999999999</v>
+      </c>
+      <c r="I34" s="23">
+        <f t="shared" si="2"/>
+        <v>2.06748283069573</v>
+      </c>
+      <c r="J34" s="24"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A35" s="11" t="s">
+      <c r="A35" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B35" s="12">
-        <v>128.41999999999999</v>
-      </c>
-      <c r="C35" s="13">
-        <v>6551</v>
-      </c>
-      <c r="D35" s="14">
-        <v>7330</v>
-      </c>
-      <c r="E35" s="14">
-        <v>3998</v>
-      </c>
-      <c r="F35" s="14">
-        <v>2542</v>
-      </c>
-      <c r="G35" s="15">
-        <f t="shared" si="0"/>
-        <v>7.33</v>
-      </c>
-      <c r="H35" s="15">
-        <f t="shared" si="1"/>
-        <v>3.9980000000000002</v>
-      </c>
-      <c r="I35" s="16">
-        <f t="shared" si="2"/>
-        <v>2.8835562549173881</v>
-      </c>
-      <c r="J35" s="17"/>
+      <c r="B35" s="5">
+        <v>189.27</v>
+      </c>
+      <c r="C35" s="6">
+        <v>5556</v>
+      </c>
+      <c r="D35" s="7">
+        <v>5887</v>
+      </c>
+      <c r="E35" s="7">
+        <v>3291</v>
+      </c>
+      <c r="F35" s="7">
+        <v>2759</v>
+      </c>
+      <c r="G35" s="8">
+        <f t="shared" si="0"/>
+        <v>5.8869999999999996</v>
+      </c>
+      <c r="H35" s="8">
+        <f t="shared" si="1"/>
+        <v>3.2909999999999999</v>
+      </c>
+      <c r="I35" s="9">
+        <f t="shared" si="2"/>
+        <v>2.1337441101848498</v>
+      </c>
+      <c r="J35" s="10"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="18" t="s">
         <v>43</v>
       </c>
       <c r="B36" s="19">
-        <v>180.97</v>
+        <v>207.35</v>
       </c>
       <c r="C36" s="20">
-        <v>5840</v>
+        <v>5781</v>
       </c>
       <c r="D36" s="21">
-        <v>6948</v>
+        <v>5832</v>
       </c>
       <c r="E36" s="21">
-        <v>4279</v>
+        <v>2635</v>
       </c>
       <c r="F36" s="21">
-        <v>3349</v>
+        <v>2643</v>
       </c>
       <c r="G36" s="22">
         <f t="shared" si="0"/>
-        <v>6.9480000000000004</v>
+        <v>5.8319999999999999</v>
       </c>
       <c r="H36" s="22">
         <f t="shared" si="1"/>
-        <v>4.2789999999999999</v>
+        <v>2.6349999999999998</v>
       </c>
       <c r="I36" s="23">
         <f t="shared" si="2"/>
-        <v>2.0746491489997014</v>
+        <v>2.2065834279228151</v>
       </c>
       <c r="J36" s="24"/>
     </row>
@@ -1828,264 +1828,264 @@
         <v>44</v>
       </c>
       <c r="B37" s="12">
-        <v>189.27</v>
+        <v>268.29000000000002</v>
       </c>
       <c r="C37" s="13">
-        <v>5556</v>
+        <v>6666</v>
       </c>
       <c r="D37" s="14">
-        <v>6198</v>
+        <v>5812</v>
       </c>
       <c r="E37" s="14">
-        <v>4279</v>
+        <v>2512</v>
       </c>
       <c r="F37" s="14">
-        <v>2759</v>
+        <v>954</v>
       </c>
       <c r="G37" s="15">
         <f t="shared" si="0"/>
-        <v>6.1980000000000004</v>
+        <v>5.8120000000000003</v>
       </c>
       <c r="H37" s="15">
         <f t="shared" si="1"/>
-        <v>4.2789999999999999</v>
+        <v>2.512</v>
       </c>
       <c r="I37" s="16">
         <f t="shared" si="2"/>
-        <v>2.2464661109097501</v>
+        <v>6.0922431865828095</v>
       </c>
       <c r="J37" s="17"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A38" s="18" t="s">
+      <c r="A38" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="B38" s="19">
-        <v>196.2</v>
-      </c>
-      <c r="C38" s="20">
-        <v>5516</v>
-      </c>
-      <c r="D38" s="21">
-        <v>6006</v>
-      </c>
-      <c r="E38" s="21">
-        <v>4262</v>
-      </c>
-      <c r="F38" s="21">
-        <v>3785</v>
-      </c>
-      <c r="G38" s="22">
-        <f t="shared" si="0"/>
-        <v>6.0060000000000002</v>
-      </c>
-      <c r="H38" s="22">
-        <f t="shared" si="1"/>
-        <v>4.2619999999999996</v>
-      </c>
-      <c r="I38" s="23">
-        <f t="shared" si="2"/>
-        <v>1.5867899603698812</v>
-      </c>
-      <c r="J38" s="24"/>
+      <c r="B38" s="12">
+        <v>249.78</v>
+      </c>
+      <c r="C38" s="13">
+        <v>6425</v>
+      </c>
+      <c r="D38" s="14">
+        <v>5731</v>
+      </c>
+      <c r="E38" s="14">
+        <v>2512</v>
+      </c>
+      <c r="F38" s="14">
+        <v>1605</v>
+      </c>
+      <c r="G38" s="15">
+        <f t="shared" si="0"/>
+        <v>5.7309999999999999</v>
+      </c>
+      <c r="H38" s="15">
+        <f t="shared" si="1"/>
+        <v>2.512</v>
+      </c>
+      <c r="I38" s="16">
+        <f t="shared" si="2"/>
+        <v>3.5707165109034267</v>
+      </c>
+      <c r="J38" s="17"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A39" s="11" t="s">
+      <c r="A39" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B39" s="12">
-        <v>207.35</v>
-      </c>
-      <c r="C39" s="13">
-        <v>5781</v>
-      </c>
-      <c r="D39" s="14">
-        <v>5956</v>
-      </c>
-      <c r="E39" s="14">
-        <v>2635</v>
-      </c>
-      <c r="F39" s="14">
-        <v>2643</v>
-      </c>
-      <c r="G39" s="15">
-        <f t="shared" si="0"/>
-        <v>5.9560000000000004</v>
-      </c>
-      <c r="H39" s="15">
-        <f t="shared" si="1"/>
-        <v>2.6349999999999998</v>
-      </c>
-      <c r="I39" s="16">
-        <f t="shared" si="2"/>
-        <v>2.2534998108210367</v>
-      </c>
-      <c r="J39" s="17"/>
+      <c r="B39" s="5">
+        <v>113.43</v>
+      </c>
+      <c r="C39" s="6">
+        <v>4317</v>
+      </c>
+      <c r="D39" s="7">
+        <v>4771</v>
+      </c>
+      <c r="E39" s="7">
+        <v>3095</v>
+      </c>
+      <c r="F39" s="7">
+        <v>2713</v>
+      </c>
+      <c r="G39" s="8">
+        <f t="shared" si="0"/>
+        <v>4.7709999999999999</v>
+      </c>
+      <c r="H39" s="8">
+        <f t="shared" si="1"/>
+        <v>3.0950000000000002</v>
+      </c>
+      <c r="I39" s="9">
+        <f t="shared" si="2"/>
+        <v>1.7585698488757833</v>
+      </c>
+      <c r="J39" s="10"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A40" s="18" t="s">
+      <c r="A40" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="B40" s="19">
-        <v>113.43</v>
-      </c>
-      <c r="C40" s="20">
-        <v>4317</v>
-      </c>
-      <c r="D40" s="21">
-        <v>5143</v>
-      </c>
-      <c r="E40" s="21">
-        <v>3094</v>
-      </c>
-      <c r="F40" s="21">
-        <v>2713</v>
-      </c>
-      <c r="G40" s="22">
-        <f t="shared" si="0"/>
-        <v>5.1429999999999998</v>
-      </c>
-      <c r="H40" s="22">
-        <f t="shared" si="1"/>
-        <v>3.0939999999999999</v>
-      </c>
-      <c r="I40" s="23">
-        <f t="shared" si="2"/>
-        <v>1.8956874308883156</v>
-      </c>
-      <c r="J40" s="24"/>
+      <c r="B40" s="12">
+        <v>265.83</v>
+      </c>
+      <c r="C40" s="13">
+        <v>6634</v>
+      </c>
+      <c r="D40" s="14">
+        <v>4547</v>
+      </c>
+      <c r="E40" s="14">
+        <v>1210</v>
+      </c>
+      <c r="F40" s="14">
+        <v>1241</v>
+      </c>
+      <c r="G40" s="15">
+        <f t="shared" si="0"/>
+        <v>4.5469999999999997</v>
+      </c>
+      <c r="H40" s="15">
+        <f t="shared" si="1"/>
+        <v>1.21</v>
+      </c>
+      <c r="I40" s="16">
+        <f t="shared" si="2"/>
+        <v>3.6639806607574537</v>
+      </c>
+      <c r="J40" s="17"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="B41" s="5">
-        <v>265.83</v>
-      </c>
-      <c r="C41" s="6">
-        <v>6634</v>
-      </c>
-      <c r="D41" s="7">
-        <v>5049</v>
-      </c>
-      <c r="E41" s="7">
+      <c r="B41" s="12">
+        <v>240.55</v>
+      </c>
+      <c r="C41" s="13">
+        <v>9293</v>
+      </c>
+      <c r="D41" s="14">
+        <v>4479</v>
+      </c>
+      <c r="E41" s="14">
         <v>1210</v>
       </c>
-      <c r="F41" s="7">
-        <v>1241</v>
-      </c>
-      <c r="G41" s="8">
-        <f t="shared" si="0"/>
-        <v>5.0490000000000004</v>
-      </c>
-      <c r="H41" s="8">
+      <c r="F41" s="14">
+        <v>1215</v>
+      </c>
+      <c r="G41" s="15">
+        <f t="shared" si="0"/>
+        <v>4.4790000000000001</v>
+      </c>
+      <c r="H41" s="15">
         <f t="shared" si="1"/>
         <v>1.21</v>
       </c>
-      <c r="I41" s="9">
-        <f t="shared" si="2"/>
-        <v>4.0684931506849313</v>
-      </c>
-      <c r="J41" s="10"/>
+      <c r="I41" s="16">
+        <f t="shared" si="2"/>
+        <v>3.6864197530864198</v>
+      </c>
+      <c r="J41" s="17"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A42" s="4" t="s">
+      <c r="A42" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="B42" s="5">
+      <c r="B42" s="12">
+        <v>135.82</v>
+      </c>
+      <c r="C42" s="13">
+        <v>5029</v>
+      </c>
+      <c r="D42" s="14">
+        <v>3959</v>
+      </c>
+      <c r="E42" s="14">
+        <v>182</v>
+      </c>
+      <c r="F42" s="14">
+        <v>218</v>
+      </c>
+      <c r="G42" s="15">
+        <f t="shared" si="0"/>
+        <v>3.9590000000000001</v>
+      </c>
+      <c r="H42" s="15">
+        <f t="shared" si="1"/>
+        <v>0.182</v>
+      </c>
+      <c r="I42" s="16">
+        <f t="shared" si="2"/>
+        <v>18.160550458715598</v>
+      </c>
+      <c r="J42" s="17"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A43" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B43" s="12">
         <v>356.7</v>
       </c>
-      <c r="C42" s="6">
+      <c r="C43" s="13">
         <v>10087</v>
       </c>
-      <c r="D42" s="7">
-        <v>4373</v>
-      </c>
-      <c r="E42" s="7">
+      <c r="D43" s="14">
+        <v>3822</v>
+      </c>
+      <c r="E43" s="14">
+        <v>28</v>
+      </c>
+      <c r="F43" s="14">
+        <v>44</v>
+      </c>
+      <c r="G43" s="15">
+        <f t="shared" si="0"/>
+        <v>3.8220000000000001</v>
+      </c>
+      <c r="H43" s="15">
+        <f t="shared" si="1"/>
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="I43" s="16">
+        <f t="shared" si="2"/>
+        <v>86.86363636363636</v>
+      </c>
+      <c r="J43" s="17"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A44" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="B44" s="12">
+        <v>27.2</v>
+      </c>
+      <c r="C44" s="13">
+        <v>2922</v>
+      </c>
+      <c r="D44" s="14">
+        <v>1351</v>
+      </c>
+      <c r="E44" s="14">
         <v>36</v>
       </c>
-      <c r="F42" s="7">
-        <v>44</v>
-      </c>
-      <c r="G42" s="8">
-        <f t="shared" si="0"/>
-        <v>4.3730000000000002</v>
-      </c>
-      <c r="H42" s="8">
+      <c r="F44" s="14">
+        <v>61</v>
+      </c>
+      <c r="G44" s="15">
+        <f t="shared" si="0"/>
+        <v>1.351</v>
+      </c>
+      <c r="H44" s="15">
         <f t="shared" si="1"/>
         <v>3.5999999999999997E-2</v>
       </c>
-      <c r="I42" s="9">
-        <f t="shared" si="2"/>
-        <v>99.38636363636364</v>
-      </c>
-      <c r="J42" s="10"/>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A43" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B43" s="5">
-        <v>135.82</v>
-      </c>
-      <c r="C43" s="6">
-        <v>5029</v>
-      </c>
-      <c r="D43" s="7">
-        <v>2564</v>
-      </c>
-      <c r="E43" s="7">
-        <v>182</v>
-      </c>
-      <c r="F43" s="7">
-        <v>218</v>
-      </c>
-      <c r="G43" s="8">
-        <f t="shared" si="0"/>
-        <v>2.5640000000000001</v>
-      </c>
-      <c r="H43" s="8">
-        <f t="shared" si="1"/>
-        <v>0.182</v>
-      </c>
-      <c r="I43" s="9">
-        <f t="shared" si="2"/>
-        <v>11.761467889908257</v>
-      </c>
-      <c r="J43" s="10"/>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A44" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B44" s="5">
-        <v>27.2</v>
-      </c>
-      <c r="C44" s="6">
-        <v>2922</v>
-      </c>
-      <c r="D44" s="7">
-        <v>1350</v>
-      </c>
-      <c r="E44" s="7">
-        <v>36</v>
-      </c>
-      <c r="F44" s="7">
-        <v>61</v>
-      </c>
-      <c r="G44" s="8">
-        <f t="shared" si="0"/>
-        <v>1.35</v>
-      </c>
-      <c r="H44" s="8">
-        <f t="shared" si="1"/>
-        <v>3.5999999999999997E-2</v>
-      </c>
-      <c r="I44" s="9">
-        <f t="shared" si="2"/>
-        <v>22.131147540983605</v>
-      </c>
-      <c r="J44" s="10"/>
+      <c r="I44" s="16">
+        <f t="shared" si="2"/>
+        <v>22.147540983606557</v>
+      </c>
+      <c r="J44" s="17"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="25" t="s">
@@ -2097,15 +2097,15 @@
       </c>
       <c r="D46" s="27">
         <f>MAX(D5:D44)</f>
-        <v>26947</v>
+        <v>12960</v>
       </c>
       <c r="G46" s="28">
         <f>IFERROR(MAX(G5:G44),"")</f>
-        <v>26.946999999999999</v>
+        <v>12.96</v>
       </c>
       <c r="I46" s="29">
         <f>IFERROR(AVERAGE(I5:I44),"")</f>
-        <v>7.9894998949830791</v>
+        <v>5.6650983878404153</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">

--- a/FAZENDA_PROMISSÃO_distancias.xlsx
+++ b/FAZENDA_PROMISSÃO_distancias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7815F4DF-98F1-49A6-8EB3-1A43519E6DFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AE00637-CE10-4EFA-A59C-67758CA16883}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -75,118 +75,118 @@
     <t>T-01</t>
   </si>
   <si>
+    <t>T-02</t>
+  </si>
+  <si>
+    <t>T-08</t>
+  </si>
+  <si>
+    <t>T-03</t>
+  </si>
+  <si>
+    <t>T-32A</t>
+  </si>
+  <si>
+    <t>T-07</t>
+  </si>
+  <si>
+    <t>T-28</t>
+  </si>
+  <si>
+    <t>T-27</t>
+  </si>
+  <si>
+    <t>T-31A</t>
+  </si>
+  <si>
+    <t>T-04</t>
+  </si>
+  <si>
+    <t>T-30A</t>
+  </si>
+  <si>
+    <t>T-32</t>
+  </si>
+  <si>
+    <t>T-09</t>
+  </si>
+  <si>
+    <t>T-06</t>
+  </si>
+  <si>
+    <t>T-13</t>
+  </si>
+  <si>
+    <t>T-29A</t>
+  </si>
+  <si>
+    <t>T-12</t>
+  </si>
+  <si>
+    <t>T-10</t>
+  </si>
+  <si>
+    <t>T-05</t>
+  </si>
+  <si>
+    <t>T-31B</t>
+  </si>
+  <si>
+    <t>T-24</t>
+  </si>
+  <si>
+    <t>T-25</t>
+  </si>
+  <si>
+    <t>T-14</t>
+  </si>
+  <si>
+    <t>T-11</t>
+  </si>
+  <si>
+    <t>T-26A</t>
+  </si>
+  <si>
+    <t>T-15</t>
+  </si>
+  <si>
+    <t>T-19</t>
+  </si>
+  <si>
+    <t>T-29B</t>
+  </si>
+  <si>
+    <t>T-23</t>
+  </si>
+  <si>
     <t>T-30B</t>
   </si>
   <si>
-    <t>T-32A</t>
-  </si>
-  <si>
-    <t>T-28</t>
-  </si>
-  <si>
-    <t>T-31A</t>
-  </si>
-  <si>
-    <t>T-02</t>
-  </si>
-  <si>
-    <t>T-27</t>
-  </si>
-  <si>
-    <t>T-30A</t>
-  </si>
-  <si>
-    <t>T-32</t>
-  </si>
-  <si>
-    <t>T-08</t>
-  </si>
-  <si>
-    <t>T-29A</t>
-  </si>
-  <si>
-    <t>T-03</t>
-  </si>
-  <si>
-    <t>T-31B</t>
-  </si>
-  <si>
-    <t>T-29B</t>
-  </si>
-  <si>
-    <t>T-10</t>
-  </si>
-  <si>
-    <t>T-11</t>
-  </si>
-  <si>
-    <t>T-07</t>
-  </si>
-  <si>
-    <t>T-26A</t>
-  </si>
-  <si>
-    <t>T-04</t>
-  </si>
-  <si>
-    <t>T-06</t>
-  </si>
-  <si>
-    <t>T-05</t>
-  </si>
-  <si>
-    <t>T-09</t>
-  </si>
-  <si>
     <t>T-30C</t>
   </si>
   <si>
     <t>T-26</t>
   </si>
   <si>
-    <t>T-13</t>
-  </si>
-  <si>
-    <t>T-12</t>
-  </si>
-  <si>
-    <t>T-24</t>
-  </si>
-  <si>
-    <t>T-25</t>
+    <t>T-16</t>
   </si>
   <si>
     <t>T-29 C</t>
   </si>
   <si>
-    <t>T-14</t>
-  </si>
-  <si>
-    <t>T-15</t>
-  </si>
-  <si>
-    <t>T-19</t>
+    <t>T-18</t>
+  </si>
+  <si>
+    <t>T-20</t>
   </si>
   <si>
     <t>T-22</t>
   </si>
   <si>
-    <t>T-23</t>
-  </si>
-  <si>
-    <t>T-16</t>
-  </si>
-  <si>
-    <t>T-18</t>
-  </si>
-  <si>
-    <t>T-20</t>
+    <t>T-17</t>
   </si>
   <si>
     <t>T-21</t>
-  </si>
-  <si>
-    <t>T-17</t>
   </si>
   <si>
     <t>T-29C</t>
@@ -339,12 +339,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
+        <fgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -778,25 +778,25 @@
         <v>6055</v>
       </c>
       <c r="D5" s="7">
-        <v>12960</v>
+        <v>12325</v>
       </c>
       <c r="E5" s="7">
-        <v>10338</v>
+        <v>9248</v>
       </c>
       <c r="F5" s="7">
         <v>7665</v>
       </c>
       <c r="G5" s="8">
         <f t="shared" ref="G5:G44" si="0">D5/1000</f>
-        <v>12.96</v>
+        <v>12.324999999999999</v>
       </c>
       <c r="H5" s="8">
         <f t="shared" ref="H5:H44" si="1">E5/1000</f>
-        <v>10.337999999999999</v>
+        <v>9.2479999999999993</v>
       </c>
       <c r="I5" s="9">
         <f t="shared" ref="I5:I44" si="2">IFERROR(D5/F5,"")</f>
-        <v>1.6908023483365948</v>
+        <v>1.6079582517938682</v>
       </c>
       <c r="J5" s="10"/>
     </row>
@@ -805,31 +805,31 @@
         <v>13</v>
       </c>
       <c r="B6" s="12">
-        <v>129.79</v>
+        <v>216.07</v>
       </c>
       <c r="C6" s="13">
-        <v>4831</v>
+        <v>5881</v>
       </c>
       <c r="D6" s="14">
-        <v>12959</v>
+        <v>10846</v>
       </c>
       <c r="E6" s="14">
-        <v>11538</v>
+        <v>7827</v>
       </c>
       <c r="F6" s="14">
-        <v>3323</v>
+        <v>6496</v>
       </c>
       <c r="G6" s="15">
         <f t="shared" si="0"/>
-        <v>12.959</v>
+        <v>10.846</v>
       </c>
       <c r="H6" s="15">
         <f t="shared" si="1"/>
-        <v>11.538</v>
+        <v>7.827</v>
       </c>
       <c r="I6" s="16">
         <f t="shared" si="2"/>
-        <v>3.8997893469756244</v>
+        <v>1.6696428571428572</v>
       </c>
       <c r="J6" s="17"/>
     </row>
@@ -838,361 +838,361 @@
         <v>14</v>
       </c>
       <c r="B7" s="5">
-        <v>83.99</v>
+        <v>128.52000000000001</v>
       </c>
       <c r="C7" s="6">
-        <v>4543</v>
+        <v>5847</v>
       </c>
       <c r="D7" s="7">
-        <v>12518</v>
+        <v>10695</v>
       </c>
       <c r="E7" s="7">
-        <v>10768</v>
+        <v>7756</v>
       </c>
       <c r="F7" s="7">
-        <v>6182</v>
+        <v>6977</v>
       </c>
       <c r="G7" s="8">
         <f t="shared" si="0"/>
-        <v>12.518000000000001</v>
+        <v>10.695</v>
       </c>
       <c r="H7" s="8">
         <f t="shared" si="1"/>
-        <v>10.768000000000001</v>
+        <v>7.7560000000000002</v>
       </c>
       <c r="I7" s="9">
         <f t="shared" si="2"/>
-        <v>2.0249110320284696</v>
+        <v>1.532893793894224</v>
       </c>
       <c r="J7" s="10"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="19">
-        <v>181.92</v>
-      </c>
-      <c r="C8" s="20">
-        <v>6154</v>
-      </c>
-      <c r="D8" s="21">
-        <v>12214</v>
-      </c>
-      <c r="E8" s="21">
-        <v>9304</v>
-      </c>
-      <c r="F8" s="21">
-        <v>5748</v>
-      </c>
-      <c r="G8" s="22">
-        <f t="shared" si="0"/>
-        <v>12.214</v>
-      </c>
-      <c r="H8" s="22">
-        <f t="shared" si="1"/>
-        <v>9.3040000000000003</v>
-      </c>
-      <c r="I8" s="23">
-        <f t="shared" si="2"/>
-        <v>2.1249130132219904</v>
-      </c>
-      <c r="J8" s="24"/>
+      <c r="B8" s="12">
+        <v>215.16</v>
+      </c>
+      <c r="C8" s="13">
+        <v>5870</v>
+      </c>
+      <c r="D8" s="14">
+        <v>9881</v>
+      </c>
+      <c r="E8" s="14">
+        <v>7458</v>
+      </c>
+      <c r="F8" s="14">
+        <v>5463</v>
+      </c>
+      <c r="G8" s="15">
+        <f t="shared" si="0"/>
+        <v>9.8810000000000002</v>
+      </c>
+      <c r="H8" s="15">
+        <f t="shared" si="1"/>
+        <v>7.4580000000000002</v>
+      </c>
+      <c r="I8" s="16">
+        <f t="shared" si="2"/>
+        <v>1.8087131612667033</v>
+      </c>
+      <c r="J8" s="17"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B9" s="5">
-        <v>132.85</v>
+        <v>83.99</v>
       </c>
       <c r="C9" s="6">
-        <v>5047</v>
+        <v>4543</v>
       </c>
       <c r="D9" s="7">
-        <v>12191</v>
+        <v>9620</v>
       </c>
       <c r="E9" s="7">
-        <v>10345</v>
+        <v>7871</v>
       </c>
       <c r="F9" s="7">
-        <v>4795</v>
+        <v>6182</v>
       </c>
       <c r="G9" s="8">
         <f t="shared" si="0"/>
-        <v>12.191000000000001</v>
+        <v>9.6199999999999992</v>
       </c>
       <c r="H9" s="8">
         <f t="shared" si="1"/>
-        <v>10.345000000000001</v>
+        <v>7.8710000000000004</v>
       </c>
       <c r="I9" s="9">
         <f t="shared" si="2"/>
-        <v>2.5424400417101145</v>
+        <v>1.5561307020381754</v>
       </c>
       <c r="J9" s="10"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="19">
-        <v>216.07</v>
-      </c>
-      <c r="C10" s="20">
-        <v>5881</v>
-      </c>
-      <c r="D10" s="21">
-        <v>11900</v>
-      </c>
-      <c r="E10" s="21">
-        <v>8902</v>
-      </c>
-      <c r="F10" s="21">
-        <v>6496</v>
-      </c>
-      <c r="G10" s="22">
-        <f t="shared" si="0"/>
-        <v>11.9</v>
-      </c>
-      <c r="H10" s="22">
-        <f t="shared" si="1"/>
-        <v>8.9019999999999992</v>
-      </c>
-      <c r="I10" s="23">
-        <f t="shared" si="2"/>
-        <v>1.8318965517241379</v>
-      </c>
-      <c r="J10" s="24"/>
+      <c r="B10" s="12">
+        <v>214</v>
+      </c>
+      <c r="C10" s="13">
+        <v>5853</v>
+      </c>
+      <c r="D10" s="14">
+        <v>9319</v>
+      </c>
+      <c r="E10" s="14">
+        <v>6331</v>
+      </c>
+      <c r="F10" s="14">
+        <v>5666</v>
+      </c>
+      <c r="G10" s="15">
+        <f t="shared" si="0"/>
+        <v>9.3190000000000008</v>
+      </c>
+      <c r="H10" s="15">
+        <f t="shared" si="1"/>
+        <v>6.3310000000000004</v>
+      </c>
+      <c r="I10" s="16">
+        <f t="shared" si="2"/>
+        <v>1.6447229085774797</v>
+      </c>
+      <c r="J10" s="17"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="5">
+        <v>181.92</v>
+      </c>
+      <c r="C11" s="6">
+        <v>6154</v>
+      </c>
+      <c r="D11" s="7">
+        <v>9316</v>
+      </c>
+      <c r="E11" s="7">
+        <v>6406</v>
+      </c>
+      <c r="F11" s="7">
+        <v>5748</v>
+      </c>
+      <c r="G11" s="8">
+        <f t="shared" si="0"/>
+        <v>9.3160000000000007</v>
+      </c>
+      <c r="H11" s="8">
+        <f t="shared" si="1"/>
+        <v>6.4059999999999997</v>
+      </c>
+      <c r="I11" s="9">
+        <f t="shared" si="2"/>
+        <v>1.6207376478775226</v>
+      </c>
+      <c r="J11" s="10"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="12">
         <v>248.35</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C12" s="13">
         <v>7351</v>
       </c>
-      <c r="D11" s="7">
-        <v>11757</v>
-      </c>
-      <c r="E11" s="7">
-        <v>8266</v>
-      </c>
-      <c r="F11" s="7">
+      <c r="D12" s="14">
+        <v>9305</v>
+      </c>
+      <c r="E12" s="14">
+        <v>5368</v>
+      </c>
+      <c r="F12" s="14">
         <v>4648</v>
       </c>
-      <c r="G11" s="8">
-        <f t="shared" si="0"/>
-        <v>11.757</v>
-      </c>
-      <c r="H11" s="8">
-        <f t="shared" si="1"/>
-        <v>8.266</v>
-      </c>
-      <c r="I11" s="9">
-        <f t="shared" si="2"/>
-        <v>2.5294750430292599</v>
-      </c>
-      <c r="J11" s="10"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="19">
-        <v>101.07</v>
-      </c>
-      <c r="C12" s="20">
-        <v>4286</v>
-      </c>
-      <c r="D12" s="21">
-        <v>11588</v>
-      </c>
-      <c r="E12" s="21">
-        <v>8542</v>
-      </c>
-      <c r="F12" s="21">
-        <v>4476</v>
-      </c>
-      <c r="G12" s="22">
-        <f t="shared" si="0"/>
-        <v>11.587999999999999</v>
-      </c>
-      <c r="H12" s="22">
-        <f t="shared" si="1"/>
-        <v>8.5419999999999998</v>
-      </c>
-      <c r="I12" s="23">
-        <f t="shared" si="2"/>
-        <v>2.5889186773905273</v>
-      </c>
-      <c r="J12" s="24"/>
+      <c r="G12" s="15">
+        <f t="shared" si="0"/>
+        <v>9.3049999999999997</v>
+      </c>
+      <c r="H12" s="15">
+        <f t="shared" si="1"/>
+        <v>5.3680000000000003</v>
+      </c>
+      <c r="I12" s="16">
+        <f t="shared" si="2"/>
+        <v>2.0019363166953528</v>
+      </c>
+      <c r="J12" s="17"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B13" s="5">
-        <v>138.68</v>
+        <v>132.85</v>
       </c>
       <c r="C13" s="6">
-        <v>5245</v>
+        <v>5047</v>
       </c>
       <c r="D13" s="7">
-        <v>11407</v>
+        <v>9293</v>
       </c>
       <c r="E13" s="7">
-        <v>9282</v>
+        <v>7447</v>
       </c>
       <c r="F13" s="7">
-        <v>4871</v>
+        <v>4795</v>
       </c>
       <c r="G13" s="8">
         <f t="shared" si="0"/>
-        <v>11.407</v>
+        <v>9.2929999999999993</v>
       </c>
       <c r="H13" s="8">
         <f t="shared" si="1"/>
-        <v>9.282</v>
+        <v>7.4470000000000001</v>
       </c>
       <c r="I13" s="9">
         <f t="shared" si="2"/>
-        <v>2.3418189283514677</v>
+        <v>1.938060479666319</v>
       </c>
       <c r="J13" s="10"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="19">
-        <v>128.52000000000001</v>
-      </c>
-      <c r="C14" s="20">
-        <v>5847</v>
-      </c>
-      <c r="D14" s="21">
-        <v>11236</v>
-      </c>
-      <c r="E14" s="21">
-        <v>7756</v>
-      </c>
-      <c r="F14" s="21">
-        <v>6977</v>
-      </c>
-      <c r="G14" s="22">
-        <f t="shared" si="0"/>
-        <v>11.236000000000001</v>
-      </c>
-      <c r="H14" s="22">
-        <f t="shared" si="1"/>
-        <v>7.7560000000000002</v>
-      </c>
-      <c r="I14" s="23">
-        <f t="shared" si="2"/>
-        <v>1.6104342840762504</v>
-      </c>
-      <c r="J14" s="24"/>
+      <c r="B14" s="12">
+        <v>222.45</v>
+      </c>
+      <c r="C14" s="13">
+        <v>5898</v>
+      </c>
+      <c r="D14" s="14">
+        <v>9106</v>
+      </c>
+      <c r="E14" s="14">
+        <v>6264</v>
+      </c>
+      <c r="F14" s="14">
+        <v>4632</v>
+      </c>
+      <c r="G14" s="15">
+        <f t="shared" si="0"/>
+        <v>9.1059999999999999</v>
+      </c>
+      <c r="H14" s="15">
+        <f t="shared" si="1"/>
+        <v>6.2640000000000002</v>
+      </c>
+      <c r="I14" s="16">
+        <f t="shared" si="2"/>
+        <v>1.9658894645941278</v>
+      </c>
+      <c r="J14" s="17"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>22</v>
       </c>
       <c r="B15" s="5">
-        <v>158.57</v>
+        <v>101.07</v>
       </c>
       <c r="C15" s="6">
-        <v>5634</v>
+        <v>4286</v>
       </c>
       <c r="D15" s="7">
-        <v>10904</v>
+        <v>8690</v>
       </c>
       <c r="E15" s="7">
-        <v>7276</v>
+        <v>5493</v>
       </c>
       <c r="F15" s="7">
-        <v>3705</v>
+        <v>4476</v>
       </c>
       <c r="G15" s="8">
         <f t="shared" si="0"/>
-        <v>10.904</v>
+        <v>8.69</v>
       </c>
       <c r="H15" s="8">
         <f t="shared" si="1"/>
-        <v>7.2759999999999998</v>
+        <v>5.4930000000000003</v>
       </c>
       <c r="I15" s="9">
         <f t="shared" si="2"/>
-        <v>2.9430499325236168</v>
+        <v>1.9414655942806076</v>
       </c>
       <c r="J15" s="10"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="18" t="s">
+      <c r="A16" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="19">
-        <v>215.16</v>
-      </c>
-      <c r="C16" s="20">
-        <v>5870</v>
-      </c>
-      <c r="D16" s="21">
-        <v>10437</v>
-      </c>
-      <c r="E16" s="21">
-        <v>7458</v>
-      </c>
-      <c r="F16" s="21">
-        <v>5463</v>
-      </c>
-      <c r="G16" s="22">
-        <f t="shared" si="0"/>
-        <v>10.436999999999999</v>
-      </c>
-      <c r="H16" s="22">
-        <f t="shared" si="1"/>
-        <v>7.4580000000000002</v>
-      </c>
-      <c r="I16" s="23">
-        <f t="shared" si="2"/>
-        <v>1.9104887424492036</v>
-      </c>
-      <c r="J16" s="24"/>
+      <c r="B16" s="12">
+        <v>138.68</v>
+      </c>
+      <c r="C16" s="13">
+        <v>5245</v>
+      </c>
+      <c r="D16" s="14">
+        <v>8509</v>
+      </c>
+      <c r="E16" s="14">
+        <v>6384</v>
+      </c>
+      <c r="F16" s="14">
+        <v>4871</v>
+      </c>
+      <c r="G16" s="15">
+        <f t="shared" si="0"/>
+        <v>8.5090000000000003</v>
+      </c>
+      <c r="H16" s="15">
+        <f t="shared" si="1"/>
+        <v>6.3840000000000003</v>
+      </c>
+      <c r="I16" s="16">
+        <f t="shared" si="2"/>
+        <v>1.7468692260316157</v>
+      </c>
+      <c r="J16" s="17"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>24</v>
       </c>
       <c r="B17" s="5">
-        <v>89.83</v>
+        <v>136.16</v>
       </c>
       <c r="C17" s="6">
-        <v>4143</v>
+        <v>5252</v>
       </c>
       <c r="D17" s="7">
-        <v>10403</v>
+        <v>8435</v>
       </c>
       <c r="E17" s="7">
-        <v>8249</v>
+        <v>5773</v>
       </c>
       <c r="F17" s="7">
-        <v>3986</v>
+        <v>5369</v>
       </c>
       <c r="G17" s="8">
         <f t="shared" si="0"/>
-        <v>10.403</v>
+        <v>8.4350000000000005</v>
       </c>
       <c r="H17" s="8">
         <f t="shared" si="1"/>
-        <v>8.2490000000000006</v>
+        <v>5.7729999999999997</v>
       </c>
       <c r="I17" s="9">
         <f t="shared" si="2"/>
-        <v>2.6098845960863022</v>
+        <v>1.5710560625814862</v>
       </c>
       <c r="J17" s="10"/>
     </row>
@@ -1201,31 +1201,31 @@
         <v>25</v>
       </c>
       <c r="B18" s="12">
-        <v>115.08</v>
+        <v>211.14</v>
       </c>
       <c r="C18" s="13">
-        <v>5656</v>
+        <v>5814</v>
       </c>
       <c r="D18" s="14">
-        <v>9988</v>
+        <v>8372</v>
       </c>
       <c r="E18" s="14">
-        <v>5844</v>
+        <v>5988</v>
       </c>
       <c r="F18" s="14">
-        <v>2262</v>
+        <v>4461</v>
       </c>
       <c r="G18" s="15">
         <f t="shared" si="0"/>
-        <v>9.9879999999999995</v>
+        <v>8.3719999999999999</v>
       </c>
       <c r="H18" s="15">
         <f t="shared" si="1"/>
-        <v>5.8440000000000003</v>
+        <v>5.9880000000000004</v>
       </c>
       <c r="I18" s="16">
         <f t="shared" si="2"/>
-        <v>4.4155614500442084</v>
+        <v>1.8767092580138982</v>
       </c>
       <c r="J18" s="17"/>
     </row>
@@ -1234,31 +1234,31 @@
         <v>26</v>
       </c>
       <c r="B19" s="5">
-        <v>225.86</v>
+        <v>198.71</v>
       </c>
       <c r="C19" s="6">
-        <v>6836</v>
+        <v>5502</v>
       </c>
       <c r="D19" s="7">
-        <v>9444</v>
+        <v>8022</v>
       </c>
       <c r="E19" s="7">
-        <v>4349</v>
+        <v>5249</v>
       </c>
       <c r="F19" s="7">
-        <v>3960</v>
+        <v>4181</v>
       </c>
       <c r="G19" s="8">
         <f t="shared" si="0"/>
-        <v>9.4440000000000008</v>
+        <v>8.0220000000000002</v>
       </c>
       <c r="H19" s="8">
         <f t="shared" si="1"/>
-        <v>4.3490000000000002</v>
+        <v>5.2489999999999997</v>
       </c>
       <c r="I19" s="9">
         <f t="shared" si="2"/>
-        <v>2.3848484848484848</v>
+        <v>1.9186797416885912</v>
       </c>
       <c r="J19" s="10"/>
     </row>
@@ -1267,31 +1267,31 @@
         <v>27</v>
       </c>
       <c r="B20" s="12">
-        <v>303.27</v>
+        <v>158.57</v>
       </c>
       <c r="C20" s="13">
-        <v>7420</v>
+        <v>5634</v>
       </c>
       <c r="D20" s="14">
-        <v>9444</v>
+        <v>8006</v>
       </c>
       <c r="E20" s="14">
-        <v>3158</v>
+        <v>4354</v>
       </c>
       <c r="F20" s="14">
-        <v>2827</v>
+        <v>3705</v>
       </c>
       <c r="G20" s="15">
         <f t="shared" si="0"/>
-        <v>9.4440000000000008</v>
+        <v>8.0060000000000002</v>
       </c>
       <c r="H20" s="15">
         <f t="shared" si="1"/>
-        <v>3.1579999999999999</v>
+        <v>4.3540000000000001</v>
       </c>
       <c r="I20" s="16">
         <f t="shared" si="2"/>
-        <v>3.3406437920056598</v>
+        <v>2.1608636977058029</v>
       </c>
       <c r="J20" s="17"/>
     </row>
@@ -1300,31 +1300,31 @@
         <v>28</v>
       </c>
       <c r="B21" s="5">
-        <v>214</v>
+        <v>196.2</v>
       </c>
       <c r="C21" s="6">
-        <v>5853</v>
+        <v>5516</v>
       </c>
       <c r="D21" s="7">
-        <v>9307</v>
+        <v>7932</v>
       </c>
       <c r="E21" s="7">
-        <v>7403</v>
+        <v>4263</v>
       </c>
       <c r="F21" s="7">
-        <v>5666</v>
+        <v>3785</v>
       </c>
       <c r="G21" s="8">
         <f t="shared" si="0"/>
-        <v>9.3070000000000004</v>
+        <v>7.9320000000000004</v>
       </c>
       <c r="H21" s="8">
         <f t="shared" si="1"/>
-        <v>7.4029999999999996</v>
+        <v>4.2629999999999999</v>
       </c>
       <c r="I21" s="9">
         <f t="shared" si="2"/>
-        <v>1.6426050123543947</v>
+        <v>2.095640686922061</v>
       </c>
       <c r="J21" s="10"/>
     </row>
@@ -1333,31 +1333,31 @@
         <v>29</v>
       </c>
       <c r="B22" s="12">
-        <v>127.51</v>
+        <v>225.86</v>
       </c>
       <c r="C22" s="13">
-        <v>5515</v>
+        <v>6836</v>
       </c>
       <c r="D22" s="14">
-        <v>9225</v>
+        <v>7814</v>
       </c>
       <c r="E22" s="14">
-        <v>7276</v>
+        <v>4339</v>
       </c>
       <c r="F22" s="14">
-        <v>2671</v>
+        <v>3960</v>
       </c>
       <c r="G22" s="15">
         <f t="shared" si="0"/>
-        <v>9.2249999999999996</v>
+        <v>7.8140000000000001</v>
       </c>
       <c r="H22" s="15">
         <f t="shared" si="1"/>
-        <v>7.2759999999999998</v>
+        <v>4.3390000000000004</v>
       </c>
       <c r="I22" s="16">
         <f t="shared" si="2"/>
-        <v>3.4537626357169597</v>
+        <v>1.9732323232323232</v>
       </c>
       <c r="J22" s="17"/>
     </row>
@@ -1366,163 +1366,163 @@
         <v>30</v>
       </c>
       <c r="B23" s="5">
-        <v>222.45</v>
+        <v>176.55</v>
       </c>
       <c r="C23" s="6">
-        <v>5898</v>
+        <v>7594</v>
       </c>
       <c r="D23" s="7">
-        <v>9106</v>
+        <v>7622</v>
       </c>
       <c r="E23" s="7">
-        <v>6252</v>
+        <v>4746</v>
       </c>
       <c r="F23" s="7">
-        <v>4632</v>
+        <v>3538</v>
       </c>
       <c r="G23" s="8">
         <f t="shared" si="0"/>
-        <v>9.1059999999999999</v>
+        <v>7.6219999999999999</v>
       </c>
       <c r="H23" s="8">
         <f t="shared" si="1"/>
-        <v>6.2519999999999998</v>
+        <v>4.7460000000000004</v>
       </c>
       <c r="I23" s="9">
         <f t="shared" si="2"/>
-        <v>1.9658894645941278</v>
+        <v>2.1543244771057095</v>
       </c>
       <c r="J23" s="10"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" s="18" t="s">
+      <c r="A24" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="B24" s="19">
-        <v>211.14</v>
-      </c>
-      <c r="C24" s="20">
-        <v>5814</v>
-      </c>
-      <c r="D24" s="21">
-        <v>8958</v>
-      </c>
-      <c r="E24" s="21">
-        <v>5988</v>
-      </c>
-      <c r="F24" s="21">
-        <v>4461</v>
-      </c>
-      <c r="G24" s="22">
-        <f t="shared" si="0"/>
-        <v>8.9580000000000002</v>
-      </c>
-      <c r="H24" s="22">
-        <f t="shared" si="1"/>
-        <v>5.9880000000000004</v>
-      </c>
-      <c r="I24" s="23">
-        <f t="shared" si="2"/>
-        <v>2.0080699394754538</v>
-      </c>
-      <c r="J24" s="24"/>
+      <c r="B24" s="12">
+        <v>89.83</v>
+      </c>
+      <c r="C24" s="13">
+        <v>4143</v>
+      </c>
+      <c r="D24" s="14">
+        <v>7505</v>
+      </c>
+      <c r="E24" s="14">
+        <v>5351</v>
+      </c>
+      <c r="F24" s="14">
+        <v>3986</v>
+      </c>
+      <c r="G24" s="15">
+        <f t="shared" si="0"/>
+        <v>7.5049999999999999</v>
+      </c>
+      <c r="H24" s="15">
+        <f t="shared" si="1"/>
+        <v>5.351</v>
+      </c>
+      <c r="I24" s="16">
+        <f t="shared" si="2"/>
+        <v>1.8828399397892623</v>
+      </c>
+      <c r="J24" s="17"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>32</v>
       </c>
       <c r="B25" s="5">
-        <v>176.55</v>
+        <v>313.18</v>
       </c>
       <c r="C25" s="6">
-        <v>7594</v>
+        <v>7098</v>
       </c>
       <c r="D25" s="7">
-        <v>8953</v>
+        <v>7316</v>
       </c>
       <c r="E25" s="7">
-        <v>4746</v>
+        <v>3852</v>
       </c>
       <c r="F25" s="7">
-        <v>3538</v>
+        <v>2810</v>
       </c>
       <c r="G25" s="8">
         <f t="shared" si="0"/>
-        <v>8.9529999999999994</v>
+        <v>7.3159999999999998</v>
       </c>
       <c r="H25" s="8">
         <f t="shared" si="1"/>
-        <v>4.7460000000000004</v>
+        <v>3.8519999999999999</v>
       </c>
       <c r="I25" s="9">
         <f t="shared" si="2"/>
-        <v>2.5305257207461844</v>
+        <v>2.6035587188612102</v>
       </c>
       <c r="J25" s="10"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A26" s="18" t="s">
+      <c r="A26" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="B26" s="19">
-        <v>136.16</v>
-      </c>
-      <c r="C26" s="20">
-        <v>5252</v>
-      </c>
-      <c r="D26" s="21">
-        <v>8435</v>
-      </c>
-      <c r="E26" s="21">
-        <v>5773</v>
-      </c>
-      <c r="F26" s="21">
-        <v>5369</v>
-      </c>
-      <c r="G26" s="22">
-        <f t="shared" si="0"/>
-        <v>8.4350000000000005</v>
-      </c>
-      <c r="H26" s="22">
-        <f t="shared" si="1"/>
-        <v>5.7729999999999997</v>
-      </c>
-      <c r="I26" s="23">
-        <f t="shared" si="2"/>
-        <v>1.5710560625814862</v>
-      </c>
-      <c r="J26" s="24"/>
+      <c r="B26" s="12">
+        <v>128.41999999999999</v>
+      </c>
+      <c r="C26" s="13">
+        <v>6551</v>
+      </c>
+      <c r="D26" s="14">
+        <v>7184</v>
+      </c>
+      <c r="E26" s="14">
+        <v>3078</v>
+      </c>
+      <c r="F26" s="14">
+        <v>2542</v>
+      </c>
+      <c r="G26" s="15">
+        <f t="shared" si="0"/>
+        <v>7.1840000000000002</v>
+      </c>
+      <c r="H26" s="15">
+        <f t="shared" si="1"/>
+        <v>3.0779999999999998</v>
+      </c>
+      <c r="I26" s="16">
+        <f t="shared" si="2"/>
+        <v>2.8261211644374509</v>
+      </c>
+      <c r="J26" s="17"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>34</v>
       </c>
       <c r="B27" s="5">
-        <v>53.2</v>
+        <v>180.97</v>
       </c>
       <c r="C27" s="6">
-        <v>3095</v>
+        <v>5840</v>
       </c>
       <c r="D27" s="7">
-        <v>8289</v>
+        <v>6920</v>
       </c>
       <c r="E27" s="7">
-        <v>7205</v>
+        <v>4279</v>
       </c>
       <c r="F27" s="7">
-        <v>3321</v>
+        <v>3349</v>
       </c>
       <c r="G27" s="8">
         <f t="shared" si="0"/>
-        <v>8.2889999999999997</v>
+        <v>6.92</v>
       </c>
       <c r="H27" s="8">
         <f t="shared" si="1"/>
-        <v>7.2050000000000001</v>
+        <v>4.2789999999999999</v>
       </c>
       <c r="I27" s="9">
         <f t="shared" si="2"/>
-        <v>2.4959349593495936</v>
+        <v>2.0662884443117346</v>
       </c>
       <c r="J27" s="10"/>
     </row>
@@ -1531,31 +1531,31 @@
         <v>35</v>
       </c>
       <c r="B28" s="12">
-        <v>147.1</v>
+        <v>303.27</v>
       </c>
       <c r="C28" s="13">
-        <v>5457</v>
+        <v>7420</v>
       </c>
       <c r="D28" s="14">
-        <v>8224</v>
+        <v>6887</v>
       </c>
       <c r="E28" s="14">
-        <v>5488</v>
+        <v>3158</v>
       </c>
       <c r="F28" s="14">
-        <v>1631</v>
+        <v>2827</v>
       </c>
       <c r="G28" s="15">
         <f t="shared" si="0"/>
-        <v>8.2240000000000002</v>
+        <v>6.8869999999999996</v>
       </c>
       <c r="H28" s="15">
         <f t="shared" si="1"/>
-        <v>5.4880000000000004</v>
+        <v>3.1579999999999999</v>
       </c>
       <c r="I28" s="16">
         <f t="shared" si="2"/>
-        <v>5.0423053341508277</v>
+        <v>2.4361513972408915</v>
       </c>
       <c r="J28" s="17"/>
     </row>
@@ -1564,229 +1564,229 @@
         <v>36</v>
       </c>
       <c r="B29" s="5">
-        <v>198.71</v>
+        <v>127.51</v>
       </c>
       <c r="C29" s="6">
-        <v>5502</v>
+        <v>5515</v>
       </c>
       <c r="D29" s="7">
-        <v>8048</v>
+        <v>6533</v>
       </c>
       <c r="E29" s="7">
-        <v>5261</v>
+        <v>4378</v>
       </c>
       <c r="F29" s="7">
-        <v>4181</v>
+        <v>2671</v>
       </c>
       <c r="G29" s="8">
         <f t="shared" si="0"/>
-        <v>8.048</v>
+        <v>6.5330000000000004</v>
       </c>
       <c r="H29" s="8">
         <f t="shared" si="1"/>
-        <v>5.2610000000000001</v>
+        <v>4.3780000000000001</v>
       </c>
       <c r="I29" s="9">
         <f t="shared" si="2"/>
-        <v>1.9248983496771108</v>
+        <v>2.4459004118307748</v>
       </c>
       <c r="J29" s="10"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A30" s="18" t="s">
+      <c r="A30" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="B30" s="19">
-        <v>196.2</v>
-      </c>
-      <c r="C30" s="20">
-        <v>5516</v>
-      </c>
-      <c r="D30" s="21">
-        <v>7944</v>
-      </c>
-      <c r="E30" s="21">
-        <v>4263</v>
-      </c>
-      <c r="F30" s="21">
-        <v>3785</v>
-      </c>
-      <c r="G30" s="22">
-        <f t="shared" si="0"/>
-        <v>7.944</v>
-      </c>
-      <c r="H30" s="22">
-        <f t="shared" si="1"/>
-        <v>4.2629999999999999</v>
-      </c>
-      <c r="I30" s="23">
-        <f t="shared" si="2"/>
-        <v>2.0988110964332893</v>
-      </c>
-      <c r="J30" s="24"/>
+      <c r="B30" s="12">
+        <v>189.27</v>
+      </c>
+      <c r="C30" s="13">
+        <v>5556</v>
+      </c>
+      <c r="D30" s="14">
+        <v>5875</v>
+      </c>
+      <c r="E30" s="14">
+        <v>3291</v>
+      </c>
+      <c r="F30" s="14">
+        <v>2759</v>
+      </c>
+      <c r="G30" s="15">
+        <f t="shared" si="0"/>
+        <v>5.875</v>
+      </c>
+      <c r="H30" s="15">
+        <f t="shared" si="1"/>
+        <v>3.2909999999999999</v>
+      </c>
+      <c r="I30" s="16">
+        <f t="shared" si="2"/>
+        <v>2.1293947082276188</v>
+      </c>
+      <c r="J30" s="17"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>38</v>
       </c>
       <c r="B31" s="5">
-        <v>313.18</v>
+        <v>207.35</v>
       </c>
       <c r="C31" s="6">
-        <v>7098</v>
+        <v>5781</v>
       </c>
       <c r="D31" s="7">
-        <v>7392</v>
+        <v>5832</v>
       </c>
       <c r="E31" s="7">
-        <v>3998</v>
+        <v>2635</v>
       </c>
       <c r="F31" s="7">
-        <v>2810</v>
+        <v>2643</v>
       </c>
       <c r="G31" s="8">
         <f t="shared" si="0"/>
-        <v>7.3920000000000003</v>
+        <v>5.8319999999999999</v>
       </c>
       <c r="H31" s="8">
         <f t="shared" si="1"/>
-        <v>3.9980000000000002</v>
+        <v>2.6349999999999998</v>
       </c>
       <c r="I31" s="9">
         <f t="shared" si="2"/>
-        <v>2.6306049822064055</v>
+        <v>2.2065834279228151</v>
       </c>
       <c r="J31" s="10"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A32" s="18" t="s">
+      <c r="A32" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B32" s="19">
-        <v>128.41999999999999</v>
-      </c>
-      <c r="C32" s="20">
-        <v>6551</v>
-      </c>
-      <c r="D32" s="21">
-        <v>7330</v>
-      </c>
-      <c r="E32" s="21">
-        <v>3998</v>
-      </c>
-      <c r="F32" s="21">
-        <v>2542</v>
-      </c>
-      <c r="G32" s="22">
-        <f t="shared" si="0"/>
-        <v>7.33</v>
-      </c>
-      <c r="H32" s="22">
-        <f t="shared" si="1"/>
-        <v>3.9980000000000002</v>
-      </c>
-      <c r="I32" s="23">
-        <f t="shared" si="2"/>
-        <v>2.8835562549173881</v>
-      </c>
-      <c r="J32" s="24"/>
+      <c r="B32" s="12">
+        <v>115.08</v>
+      </c>
+      <c r="C32" s="13">
+        <v>5656</v>
+      </c>
+      <c r="D32" s="14">
+        <v>5704</v>
+      </c>
+      <c r="E32" s="14">
+        <v>2929</v>
+      </c>
+      <c r="F32" s="14">
+        <v>2262</v>
+      </c>
+      <c r="G32" s="15">
+        <f t="shared" si="0"/>
+        <v>5.7039999999999997</v>
+      </c>
+      <c r="H32" s="15">
+        <f t="shared" si="1"/>
+        <v>2.9289999999999998</v>
+      </c>
+      <c r="I32" s="16">
+        <f t="shared" si="2"/>
+        <v>2.5216622458001767</v>
+      </c>
+      <c r="J32" s="17"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A33" s="11" t="s">
+      <c r="A33" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="B33" s="12">
-        <v>23</v>
-      </c>
-      <c r="C33" s="13">
-        <v>3375</v>
-      </c>
-      <c r="D33" s="14">
-        <v>7236</v>
-      </c>
-      <c r="E33" s="14">
-        <v>5801</v>
-      </c>
-      <c r="F33" s="14">
-        <v>2251</v>
-      </c>
-      <c r="G33" s="15">
-        <f t="shared" si="0"/>
-        <v>7.2359999999999998</v>
-      </c>
-      <c r="H33" s="15">
-        <f t="shared" si="1"/>
-        <v>5.8010000000000002</v>
-      </c>
-      <c r="I33" s="16">
-        <f t="shared" si="2"/>
-        <v>3.2145713016437139</v>
-      </c>
-      <c r="J33" s="17"/>
+      <c r="B33" s="19">
+        <v>249.78</v>
+      </c>
+      <c r="C33" s="20">
+        <v>6425</v>
+      </c>
+      <c r="D33" s="21">
+        <v>5585</v>
+      </c>
+      <c r="E33" s="21">
+        <v>2372</v>
+      </c>
+      <c r="F33" s="21">
+        <v>1605</v>
+      </c>
+      <c r="G33" s="22">
+        <f t="shared" si="0"/>
+        <v>5.585</v>
+      </c>
+      <c r="H33" s="22">
+        <f t="shared" si="1"/>
+        <v>2.3719999999999999</v>
+      </c>
+      <c r="I33" s="23">
+        <f t="shared" si="2"/>
+        <v>3.4797507788161992</v>
+      </c>
+      <c r="J33" s="24"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A34" s="18" t="s">
+      <c r="A34" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B34" s="19">
-        <v>180.97</v>
-      </c>
-      <c r="C34" s="20">
-        <v>5840</v>
-      </c>
-      <c r="D34" s="21">
-        <v>6924</v>
-      </c>
-      <c r="E34" s="21">
-        <v>4279</v>
-      </c>
-      <c r="F34" s="21">
-        <v>3349</v>
-      </c>
-      <c r="G34" s="22">
-        <f t="shared" si="0"/>
-        <v>6.9240000000000004</v>
-      </c>
-      <c r="H34" s="22">
-        <f t="shared" si="1"/>
-        <v>4.2789999999999999</v>
-      </c>
-      <c r="I34" s="23">
-        <f t="shared" si="2"/>
-        <v>2.06748283069573</v>
-      </c>
-      <c r="J34" s="24"/>
+      <c r="B34" s="12">
+        <v>129.79</v>
+      </c>
+      <c r="C34" s="13">
+        <v>4831</v>
+      </c>
+      <c r="D34" s="14">
+        <v>5572</v>
+      </c>
+      <c r="E34" s="14">
+        <v>4327</v>
+      </c>
+      <c r="F34" s="14">
+        <v>3323</v>
+      </c>
+      <c r="G34" s="15">
+        <f t="shared" si="0"/>
+        <v>5.5720000000000001</v>
+      </c>
+      <c r="H34" s="15">
+        <f t="shared" si="1"/>
+        <v>4.327</v>
+      </c>
+      <c r="I34" s="16">
+        <f t="shared" si="2"/>
+        <v>1.6767980740294914</v>
+      </c>
+      <c r="J34" s="17"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>42</v>
       </c>
       <c r="B35" s="5">
-        <v>189.27</v>
+        <v>53.2</v>
       </c>
       <c r="C35" s="6">
-        <v>5556</v>
+        <v>3095</v>
       </c>
       <c r="D35" s="7">
-        <v>5887</v>
+        <v>5391</v>
       </c>
       <c r="E35" s="7">
-        <v>3291</v>
+        <v>4327</v>
       </c>
       <c r="F35" s="7">
-        <v>2759</v>
+        <v>3321</v>
       </c>
       <c r="G35" s="8">
         <f t="shared" si="0"/>
-        <v>5.8869999999999996</v>
+        <v>5.391</v>
       </c>
       <c r="H35" s="8">
         <f t="shared" si="1"/>
-        <v>3.2909999999999999</v>
+        <v>4.327</v>
       </c>
       <c r="I35" s="9">
         <f t="shared" si="2"/>
-        <v>2.1337441101848498</v>
+        <v>1.6233062330623307</v>
       </c>
       <c r="J35" s="10"/>
     </row>
@@ -1795,297 +1795,297 @@
         <v>43</v>
       </c>
       <c r="B36" s="19">
-        <v>207.35</v>
+        <v>147.1</v>
       </c>
       <c r="C36" s="20">
-        <v>5781</v>
+        <v>5457</v>
       </c>
       <c r="D36" s="21">
-        <v>5832</v>
+        <v>5326</v>
       </c>
       <c r="E36" s="21">
-        <v>2635</v>
+        <v>2590</v>
       </c>
       <c r="F36" s="21">
-        <v>2643</v>
+        <v>1631</v>
       </c>
       <c r="G36" s="22">
         <f t="shared" si="0"/>
-        <v>5.8319999999999999</v>
+        <v>5.3259999999999996</v>
       </c>
       <c r="H36" s="22">
         <f t="shared" si="1"/>
-        <v>2.6349999999999998</v>
+        <v>2.59</v>
       </c>
       <c r="I36" s="23">
         <f t="shared" si="2"/>
-        <v>2.2065834279228151</v>
+        <v>3.2654812998160638</v>
       </c>
       <c r="J36" s="24"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A37" s="11" t="s">
+      <c r="A37" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B37" s="12">
-        <v>268.29000000000002</v>
-      </c>
-      <c r="C37" s="13">
-        <v>6666</v>
-      </c>
-      <c r="D37" s="14">
-        <v>5812</v>
-      </c>
-      <c r="E37" s="14">
-        <v>2512</v>
-      </c>
-      <c r="F37" s="14">
-        <v>954</v>
-      </c>
-      <c r="G37" s="15">
-        <f t="shared" si="0"/>
-        <v>5.8120000000000003</v>
-      </c>
-      <c r="H37" s="15">
-        <f t="shared" si="1"/>
-        <v>2.512</v>
-      </c>
-      <c r="I37" s="16">
-        <f t="shared" si="2"/>
-        <v>6.0922431865828095</v>
-      </c>
-      <c r="J37" s="17"/>
+      <c r="B37" s="5">
+        <v>113.43</v>
+      </c>
+      <c r="C37" s="6">
+        <v>4317</v>
+      </c>
+      <c r="D37" s="7">
+        <v>4771</v>
+      </c>
+      <c r="E37" s="7">
+        <v>3095</v>
+      </c>
+      <c r="F37" s="7">
+        <v>2713</v>
+      </c>
+      <c r="G37" s="8">
+        <f t="shared" si="0"/>
+        <v>4.7709999999999999</v>
+      </c>
+      <c r="H37" s="8">
+        <f t="shared" si="1"/>
+        <v>3.0950000000000002</v>
+      </c>
+      <c r="I37" s="9">
+        <f t="shared" si="2"/>
+        <v>1.7585698488757833</v>
+      </c>
+      <c r="J37" s="10"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="11" t="s">
         <v>45</v>
       </c>
       <c r="B38" s="12">
-        <v>249.78</v>
+        <v>23</v>
       </c>
       <c r="C38" s="13">
-        <v>6425</v>
+        <v>3375</v>
       </c>
       <c r="D38" s="14">
-        <v>5731</v>
+        <v>4639</v>
       </c>
       <c r="E38" s="14">
-        <v>2512</v>
+        <v>2903</v>
       </c>
       <c r="F38" s="14">
-        <v>1605</v>
+        <v>2251</v>
       </c>
       <c r="G38" s="15">
         <f t="shared" si="0"/>
-        <v>5.7309999999999999</v>
+        <v>4.6390000000000002</v>
       </c>
       <c r="H38" s="15">
         <f t="shared" si="1"/>
-        <v>2.512</v>
+        <v>2.903</v>
       </c>
       <c r="I38" s="16">
         <f t="shared" si="2"/>
-        <v>3.5707165109034267</v>
+        <v>2.0608618391825857</v>
       </c>
       <c r="J38" s="17"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="B39" s="5">
-        <v>113.43</v>
-      </c>
-      <c r="C39" s="6">
-        <v>4317</v>
-      </c>
-      <c r="D39" s="7">
-        <v>4771</v>
-      </c>
-      <c r="E39" s="7">
-        <v>3095</v>
-      </c>
-      <c r="F39" s="7">
-        <v>2713</v>
-      </c>
-      <c r="G39" s="8">
-        <f t="shared" si="0"/>
-        <v>4.7709999999999999</v>
-      </c>
-      <c r="H39" s="8">
-        <f t="shared" si="1"/>
-        <v>3.0950000000000002</v>
-      </c>
-      <c r="I39" s="9">
-        <f t="shared" si="2"/>
-        <v>1.7585698488757833</v>
-      </c>
-      <c r="J39" s="10"/>
+      <c r="B39" s="19">
+        <v>265.83</v>
+      </c>
+      <c r="C39" s="20">
+        <v>6634</v>
+      </c>
+      <c r="D39" s="21">
+        <v>4541</v>
+      </c>
+      <c r="E39" s="21">
+        <v>1210</v>
+      </c>
+      <c r="F39" s="21">
+        <v>1241</v>
+      </c>
+      <c r="G39" s="22">
+        <f t="shared" si="0"/>
+        <v>4.5410000000000004</v>
+      </c>
+      <c r="H39" s="22">
+        <f t="shared" si="1"/>
+        <v>1.21</v>
+      </c>
+      <c r="I39" s="23">
+        <f t="shared" si="2"/>
+        <v>3.6591458501208702</v>
+      </c>
+      <c r="J39" s="24"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A40" s="11" t="s">
+      <c r="A40" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="B40" s="12">
-        <v>265.83</v>
-      </c>
-      <c r="C40" s="13">
-        <v>6634</v>
-      </c>
-      <c r="D40" s="14">
-        <v>4547</v>
-      </c>
-      <c r="E40" s="14">
+      <c r="B40" s="19">
+        <v>240.55</v>
+      </c>
+      <c r="C40" s="20">
+        <v>9293</v>
+      </c>
+      <c r="D40" s="21">
+        <v>4467</v>
+      </c>
+      <c r="E40" s="21">
         <v>1210</v>
       </c>
-      <c r="F40" s="14">
-        <v>1241</v>
-      </c>
-      <c r="G40" s="15">
-        <f t="shared" si="0"/>
-        <v>4.5469999999999997</v>
-      </c>
-      <c r="H40" s="15">
+      <c r="F40" s="21">
+        <v>1215</v>
+      </c>
+      <c r="G40" s="22">
+        <f t="shared" si="0"/>
+        <v>4.4669999999999996</v>
+      </c>
+      <c r="H40" s="22">
         <f t="shared" si="1"/>
         <v>1.21</v>
       </c>
-      <c r="I40" s="16">
-        <f t="shared" si="2"/>
-        <v>3.6639806607574537</v>
-      </c>
-      <c r="J40" s="17"/>
+      <c r="I40" s="23">
+        <f t="shared" si="2"/>
+        <v>3.6765432098765434</v>
+      </c>
+      <c r="J40" s="24"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A41" s="11" t="s">
+      <c r="A41" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="B41" s="12">
-        <v>240.55</v>
-      </c>
-      <c r="C41" s="13">
-        <v>9293</v>
-      </c>
-      <c r="D41" s="14">
-        <v>4479</v>
-      </c>
-      <c r="E41" s="14">
-        <v>1210</v>
-      </c>
-      <c r="F41" s="14">
-        <v>1215</v>
-      </c>
-      <c r="G41" s="15">
-        <f t="shared" si="0"/>
-        <v>4.4790000000000001</v>
-      </c>
-      <c r="H41" s="15">
-        <f t="shared" si="1"/>
-        <v>1.21</v>
-      </c>
-      <c r="I41" s="16">
-        <f t="shared" si="2"/>
-        <v>3.6864197530864198</v>
-      </c>
-      <c r="J41" s="17"/>
+      <c r="B41" s="19">
+        <v>268.29000000000002</v>
+      </c>
+      <c r="C41" s="20">
+        <v>6666</v>
+      </c>
+      <c r="D41" s="21">
+        <v>4290</v>
+      </c>
+      <c r="E41" s="21">
+        <v>997</v>
+      </c>
+      <c r="F41" s="21">
+        <v>954</v>
+      </c>
+      <c r="G41" s="22">
+        <f t="shared" si="0"/>
+        <v>4.29</v>
+      </c>
+      <c r="H41" s="22">
+        <f t="shared" si="1"/>
+        <v>0.997</v>
+      </c>
+      <c r="I41" s="23">
+        <f t="shared" si="2"/>
+        <v>4.4968553459119498</v>
+      </c>
+      <c r="J41" s="24"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A42" s="11" t="s">
+      <c r="A42" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="B42" s="12">
+      <c r="B42" s="19">
+        <v>356.7</v>
+      </c>
+      <c r="C42" s="20">
+        <v>10087</v>
+      </c>
+      <c r="D42" s="21">
+        <v>3825</v>
+      </c>
+      <c r="E42" s="21">
+        <v>28</v>
+      </c>
+      <c r="F42" s="21">
+        <v>44</v>
+      </c>
+      <c r="G42" s="22">
+        <f t="shared" si="0"/>
+        <v>3.8250000000000002</v>
+      </c>
+      <c r="H42" s="22">
+        <f t="shared" si="1"/>
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="I42" s="23">
+        <f t="shared" si="2"/>
+        <v>86.931818181818187</v>
+      </c>
+      <c r="J42" s="24"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A43" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="B43" s="19">
         <v>135.82</v>
       </c>
-      <c r="C42" s="13">
+      <c r="C43" s="20">
         <v>5029</v>
       </c>
-      <c r="D42" s="14">
-        <v>3959</v>
-      </c>
-      <c r="E42" s="14">
+      <c r="D43" s="21">
+        <v>2460</v>
+      </c>
+      <c r="E43" s="21">
         <v>182</v>
       </c>
-      <c r="F42" s="14">
+      <c r="F43" s="21">
         <v>218</v>
       </c>
-      <c r="G42" s="15">
-        <f t="shared" si="0"/>
-        <v>3.9590000000000001</v>
-      </c>
-      <c r="H42" s="15">
+      <c r="G43" s="22">
+        <f t="shared" si="0"/>
+        <v>2.46</v>
+      </c>
+      <c r="H43" s="22">
         <f t="shared" si="1"/>
         <v>0.182</v>
       </c>
-      <c r="I42" s="16">
-        <f t="shared" si="2"/>
-        <v>18.160550458715598</v>
-      </c>
-      <c r="J42" s="17"/>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A43" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="B43" s="12">
-        <v>356.7</v>
-      </c>
-      <c r="C43" s="13">
-        <v>10087</v>
-      </c>
-      <c r="D43" s="14">
-        <v>3822</v>
-      </c>
-      <c r="E43" s="14">
-        <v>28</v>
-      </c>
-      <c r="F43" s="14">
-        <v>44</v>
-      </c>
-      <c r="G43" s="15">
-        <f t="shared" si="0"/>
-        <v>3.8220000000000001</v>
-      </c>
-      <c r="H43" s="15">
-        <f t="shared" si="1"/>
-        <v>2.8000000000000001E-2</v>
-      </c>
-      <c r="I43" s="16">
-        <f t="shared" si="2"/>
-        <v>86.86363636363636</v>
-      </c>
-      <c r="J43" s="17"/>
+      <c r="I43" s="23">
+        <f t="shared" si="2"/>
+        <v>11.284403669724771</v>
+      </c>
+      <c r="J43" s="24"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A44" s="11" t="s">
+      <c r="A44" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="B44" s="12">
+      <c r="B44" s="19">
         <v>27.2</v>
       </c>
-      <c r="C44" s="13">
+      <c r="C44" s="20">
         <v>2922</v>
       </c>
-      <c r="D44" s="14">
+      <c r="D44" s="21">
         <v>1351</v>
       </c>
-      <c r="E44" s="14">
+      <c r="E44" s="21">
         <v>36</v>
       </c>
-      <c r="F44" s="14">
+      <c r="F44" s="21">
         <v>61</v>
       </c>
-      <c r="G44" s="15">
+      <c r="G44" s="22">
         <f t="shared" si="0"/>
         <v>1.351</v>
       </c>
-      <c r="H44" s="15">
+      <c r="H44" s="22">
         <f t="shared" si="1"/>
         <v>3.5999999999999997E-2</v>
       </c>
-      <c r="I44" s="16">
+      <c r="I44" s="23">
         <f t="shared" si="2"/>
         <v>22.147540983606557</v>
       </c>
-      <c r="J44" s="17"/>
+      <c r="J44" s="24"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="25" t="s">
@@ -2093,19 +2093,19 @@
       </c>
       <c r="B46" s="26">
         <f>SUM(B5:B44)</f>
-        <v>7068.9400000000005</v>
+        <v>7068.94</v>
       </c>
       <c r="D46" s="27">
         <f>MAX(D5:D44)</f>
-        <v>12960</v>
+        <v>12325</v>
       </c>
       <c r="G46" s="28">
         <f>IFERROR(MAX(G5:G44),"")</f>
-        <v>12.96</v>
+        <v>12.324999999999999</v>
       </c>
       <c r="I46" s="29">
         <f>IFERROR(AVERAGE(I5:I44),"")</f>
-        <v>5.6650983878404153</v>
+        <v>5.0491275606093007</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">

--- a/FAZENDA_PROMISSÃO_distancias.xlsx
+++ b/FAZENDA_PROMISSÃO_distancias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AE00637-CE10-4EFA-A59C-67758CA16883}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A69F8098-CF87-4222-8A0A-DD8D63355805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/FAZENDA_PROMISSÃO_distancias.xlsx
+++ b/FAZENDA_PROMISSÃO_distancias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A69F8098-CF87-4222-8A0A-DD8D63355805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1FAFE11-0E9D-4E76-A51D-69E2486EC45E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -90,63 +90,69 @@
     <t>T-07</t>
   </si>
   <si>
+    <t>T-27</t>
+  </si>
+  <si>
+    <t>T-04</t>
+  </si>
+  <si>
     <t>T-28</t>
   </si>
   <si>
-    <t>T-27</t>
-  </si>
-  <si>
     <t>T-31A</t>
   </si>
   <si>
-    <t>T-04</t>
+    <t>T-32</t>
+  </si>
+  <si>
+    <t>T-09</t>
+  </si>
+  <si>
+    <t>T-06</t>
+  </si>
+  <si>
+    <t>T-13</t>
+  </si>
+  <si>
+    <t>T-10</t>
   </si>
   <si>
     <t>T-30A</t>
   </si>
   <si>
-    <t>T-32</t>
-  </si>
-  <si>
-    <t>T-09</t>
-  </si>
-  <si>
-    <t>T-06</t>
-  </si>
-  <si>
-    <t>T-13</t>
+    <t>T-05</t>
+  </si>
+  <si>
+    <t>T-31B</t>
+  </si>
+  <si>
+    <t>T-24</t>
   </si>
   <si>
     <t>T-29A</t>
   </si>
   <si>
+    <t>T-25</t>
+  </si>
+  <si>
+    <t>T-14</t>
+  </si>
+  <si>
+    <t>T-30B</t>
+  </si>
+  <si>
+    <t>T-11</t>
+  </si>
+  <si>
     <t>T-12</t>
   </si>
   <si>
-    <t>T-10</t>
-  </si>
-  <si>
-    <t>T-05</t>
-  </si>
-  <si>
-    <t>T-31B</t>
-  </si>
-  <si>
-    <t>T-24</t>
-  </si>
-  <si>
-    <t>T-25</t>
-  </si>
-  <si>
-    <t>T-14</t>
-  </si>
-  <si>
-    <t>T-11</t>
-  </si>
-  <si>
     <t>T-26A</t>
   </si>
   <si>
+    <t>T-30C</t>
+  </si>
+  <si>
     <t>T-15</t>
   </si>
   <si>
@@ -157,12 +163,6 @@
   </si>
   <si>
     <t>T-23</t>
-  </si>
-  <si>
-    <t>T-30B</t>
-  </si>
-  <si>
-    <t>T-30C</t>
   </si>
   <si>
     <t>T-26</t>
@@ -778,25 +778,25 @@
         <v>6055</v>
       </c>
       <c r="D5" s="7">
-        <v>12325</v>
+        <v>12306</v>
       </c>
       <c r="E5" s="7">
-        <v>9248</v>
+        <v>9243</v>
       </c>
       <c r="F5" s="7">
         <v>7665</v>
       </c>
       <c r="G5" s="8">
         <f t="shared" ref="G5:G44" si="0">D5/1000</f>
-        <v>12.324999999999999</v>
+        <v>12.305999999999999</v>
       </c>
       <c r="H5" s="8">
         <f t="shared" ref="H5:H44" si="1">E5/1000</f>
-        <v>9.2479999999999993</v>
+        <v>9.2430000000000003</v>
       </c>
       <c r="I5" s="9">
         <f t="shared" ref="I5:I44" si="2">IFERROR(D5/F5,"")</f>
-        <v>1.6079582517938682</v>
+        <v>1.6054794520547946</v>
       </c>
       <c r="J5" s="10"/>
     </row>
@@ -811,25 +811,25 @@
         <v>5881</v>
       </c>
       <c r="D6" s="14">
-        <v>10846</v>
+        <v>10805</v>
       </c>
       <c r="E6" s="14">
-        <v>7827</v>
+        <v>7821</v>
       </c>
       <c r="F6" s="14">
         <v>6496</v>
       </c>
       <c r="G6" s="15">
         <f t="shared" si="0"/>
-        <v>10.846</v>
+        <v>10.805</v>
       </c>
       <c r="H6" s="15">
         <f t="shared" si="1"/>
-        <v>7.827</v>
+        <v>7.8209999999999997</v>
       </c>
       <c r="I6" s="16">
         <f t="shared" si="2"/>
-        <v>1.6696428571428572</v>
+        <v>1.6633312807881773</v>
       </c>
       <c r="J6" s="17"/>
     </row>
@@ -844,25 +844,25 @@
         <v>5847</v>
       </c>
       <c r="D7" s="7">
-        <v>10695</v>
+        <v>10689</v>
       </c>
       <c r="E7" s="7">
-        <v>7756</v>
+        <v>7750</v>
       </c>
       <c r="F7" s="7">
         <v>6977</v>
       </c>
       <c r="G7" s="8">
         <f t="shared" si="0"/>
-        <v>10.695</v>
+        <v>10.689</v>
       </c>
       <c r="H7" s="8">
         <f t="shared" si="1"/>
-        <v>7.7560000000000002</v>
+        <v>7.75</v>
       </c>
       <c r="I7" s="9">
         <f t="shared" si="2"/>
-        <v>1.532893793894224</v>
+        <v>1.532033825426401</v>
       </c>
       <c r="J7" s="10"/>
     </row>
@@ -877,7 +877,7 @@
         <v>5870</v>
       </c>
       <c r="D8" s="14">
-        <v>9881</v>
+        <v>9883</v>
       </c>
       <c r="E8" s="14">
         <v>7458</v>
@@ -887,7 +887,7 @@
       </c>
       <c r="G8" s="15">
         <f t="shared" si="0"/>
-        <v>9.8810000000000002</v>
+        <v>9.8829999999999991</v>
       </c>
       <c r="H8" s="15">
         <f t="shared" si="1"/>
@@ -895,7 +895,7 @@
       </c>
       <c r="I8" s="16">
         <f t="shared" si="2"/>
-        <v>1.8087131612667033</v>
+        <v>1.80907926047959</v>
       </c>
       <c r="J8" s="17"/>
     </row>
@@ -910,25 +910,25 @@
         <v>4543</v>
       </c>
       <c r="D9" s="7">
-        <v>9620</v>
+        <v>9617</v>
       </c>
       <c r="E9" s="7">
-        <v>7871</v>
+        <v>7867</v>
       </c>
       <c r="F9" s="7">
         <v>6182</v>
       </c>
       <c r="G9" s="8">
         <f t="shared" si="0"/>
-        <v>9.6199999999999992</v>
+        <v>9.6170000000000009</v>
       </c>
       <c r="H9" s="8">
         <f t="shared" si="1"/>
-        <v>7.8710000000000004</v>
+        <v>7.867</v>
       </c>
       <c r="I9" s="9">
         <f t="shared" si="2"/>
-        <v>1.5561307020381754</v>
+        <v>1.5556454221934648</v>
       </c>
       <c r="J9" s="10"/>
     </row>
@@ -943,25 +943,25 @@
         <v>5853</v>
       </c>
       <c r="D10" s="14">
-        <v>9319</v>
+        <v>9313</v>
       </c>
       <c r="E10" s="14">
-        <v>6331</v>
+        <v>6325</v>
       </c>
       <c r="F10" s="14">
         <v>5666</v>
       </c>
       <c r="G10" s="15">
         <f t="shared" si="0"/>
-        <v>9.3190000000000008</v>
+        <v>9.3130000000000006</v>
       </c>
       <c r="H10" s="15">
         <f t="shared" si="1"/>
-        <v>6.3310000000000004</v>
+        <v>6.3250000000000002</v>
       </c>
       <c r="I10" s="16">
         <f t="shared" si="2"/>
-        <v>1.6447229085774797</v>
+        <v>1.6436639604659371</v>
       </c>
       <c r="J10" s="17"/>
     </row>
@@ -970,31 +970,31 @@
         <v>18</v>
       </c>
       <c r="B11" s="5">
-        <v>181.92</v>
+        <v>248.35</v>
       </c>
       <c r="C11" s="6">
-        <v>6154</v>
+        <v>7351</v>
       </c>
       <c r="D11" s="7">
-        <v>9316</v>
+        <v>9305</v>
       </c>
       <c r="E11" s="7">
-        <v>6406</v>
+        <v>5368</v>
       </c>
       <c r="F11" s="7">
-        <v>5748</v>
+        <v>4648</v>
       </c>
       <c r="G11" s="8">
         <f t="shared" si="0"/>
-        <v>9.3160000000000007</v>
+        <v>9.3049999999999997</v>
       </c>
       <c r="H11" s="8">
         <f t="shared" si="1"/>
-        <v>6.4059999999999997</v>
+        <v>5.3680000000000003</v>
       </c>
       <c r="I11" s="9">
         <f t="shared" si="2"/>
-        <v>1.6207376478775226</v>
+        <v>2.0019363166953528</v>
       </c>
       <c r="J11" s="10"/>
     </row>
@@ -1003,31 +1003,31 @@
         <v>19</v>
       </c>
       <c r="B12" s="12">
-        <v>248.35</v>
+        <v>222.45</v>
       </c>
       <c r="C12" s="13">
-        <v>7351</v>
+        <v>5898</v>
       </c>
       <c r="D12" s="14">
-        <v>9305</v>
+        <v>9106</v>
       </c>
       <c r="E12" s="14">
-        <v>5368</v>
+        <v>6264</v>
       </c>
       <c r="F12" s="14">
-        <v>4648</v>
+        <v>4632</v>
       </c>
       <c r="G12" s="15">
         <f t="shared" si="0"/>
-        <v>9.3049999999999997</v>
+        <v>9.1059999999999999</v>
       </c>
       <c r="H12" s="15">
         <f t="shared" si="1"/>
-        <v>5.3680000000000003</v>
+        <v>6.2640000000000002</v>
       </c>
       <c r="I12" s="16">
         <f t="shared" si="2"/>
-        <v>2.0019363166953528</v>
+        <v>1.9658894645941278</v>
       </c>
       <c r="J12" s="17"/>
     </row>
@@ -1036,31 +1036,31 @@
         <v>20</v>
       </c>
       <c r="B13" s="5">
-        <v>132.85</v>
+        <v>181.92</v>
       </c>
       <c r="C13" s="6">
-        <v>5047</v>
+        <v>6154</v>
       </c>
       <c r="D13" s="7">
-        <v>9293</v>
+        <v>9062</v>
       </c>
       <c r="E13" s="7">
-        <v>7447</v>
+        <v>6416</v>
       </c>
       <c r="F13" s="7">
-        <v>4795</v>
+        <v>5748</v>
       </c>
       <c r="G13" s="8">
         <f t="shared" si="0"/>
-        <v>9.2929999999999993</v>
+        <v>9.0619999999999994</v>
       </c>
       <c r="H13" s="8">
         <f t="shared" si="1"/>
-        <v>7.4470000000000001</v>
+        <v>6.4160000000000004</v>
       </c>
       <c r="I13" s="9">
         <f t="shared" si="2"/>
-        <v>1.938060479666319</v>
+        <v>1.5765483646485734</v>
       </c>
       <c r="J13" s="10"/>
     </row>
@@ -1069,31 +1069,31 @@
         <v>21</v>
       </c>
       <c r="B14" s="12">
-        <v>222.45</v>
+        <v>132.85</v>
       </c>
       <c r="C14" s="13">
-        <v>5898</v>
+        <v>5047</v>
       </c>
       <c r="D14" s="14">
-        <v>9106</v>
+        <v>8819</v>
       </c>
       <c r="E14" s="14">
-        <v>6264</v>
+        <v>6230</v>
       </c>
       <c r="F14" s="14">
-        <v>4632</v>
+        <v>4795</v>
       </c>
       <c r="G14" s="15">
         <f t="shared" si="0"/>
-        <v>9.1059999999999999</v>
+        <v>8.8190000000000008</v>
       </c>
       <c r="H14" s="15">
         <f t="shared" si="1"/>
-        <v>6.2640000000000002</v>
+        <v>6.23</v>
       </c>
       <c r="I14" s="16">
         <f t="shared" si="2"/>
-        <v>1.9658894645941278</v>
+        <v>1.8392075078206465</v>
       </c>
       <c r="J14" s="17"/>
     </row>
@@ -1102,31 +1102,31 @@
         <v>22</v>
       </c>
       <c r="B15" s="5">
-        <v>101.07</v>
+        <v>138.68</v>
       </c>
       <c r="C15" s="6">
-        <v>4286</v>
+        <v>5245</v>
       </c>
       <c r="D15" s="7">
-        <v>8690</v>
+        <v>8509</v>
       </c>
       <c r="E15" s="7">
-        <v>5493</v>
+        <v>6385</v>
       </c>
       <c r="F15" s="7">
-        <v>4476</v>
+        <v>4871</v>
       </c>
       <c r="G15" s="8">
         <f t="shared" si="0"/>
-        <v>8.69</v>
+        <v>8.5090000000000003</v>
       </c>
       <c r="H15" s="8">
         <f t="shared" si="1"/>
-        <v>5.4930000000000003</v>
+        <v>6.3849999999999998</v>
       </c>
       <c r="I15" s="9">
         <f t="shared" si="2"/>
-        <v>1.9414655942806076</v>
+        <v>1.7468692260316157</v>
       </c>
       <c r="J15" s="10"/>
     </row>
@@ -1135,31 +1135,31 @@
         <v>23</v>
       </c>
       <c r="B16" s="12">
-        <v>138.68</v>
+        <v>136.16</v>
       </c>
       <c r="C16" s="13">
-        <v>5245</v>
+        <v>5252</v>
       </c>
       <c r="D16" s="14">
-        <v>8509</v>
+        <v>8429</v>
       </c>
       <c r="E16" s="14">
-        <v>6384</v>
+        <v>5767</v>
       </c>
       <c r="F16" s="14">
-        <v>4871</v>
+        <v>5369</v>
       </c>
       <c r="G16" s="15">
         <f t="shared" si="0"/>
-        <v>8.5090000000000003</v>
+        <v>8.4290000000000003</v>
       </c>
       <c r="H16" s="15">
         <f t="shared" si="1"/>
-        <v>6.3840000000000003</v>
+        <v>5.7670000000000003</v>
       </c>
       <c r="I16" s="16">
         <f t="shared" si="2"/>
-        <v>1.7468692260316157</v>
+        <v>1.5699385360402309</v>
       </c>
       <c r="J16" s="17"/>
     </row>
@@ -1168,31 +1168,31 @@
         <v>24</v>
       </c>
       <c r="B17" s="5">
-        <v>136.16</v>
+        <v>211.14</v>
       </c>
       <c r="C17" s="6">
-        <v>5252</v>
+        <v>5814</v>
       </c>
       <c r="D17" s="7">
-        <v>8435</v>
+        <v>8372</v>
       </c>
       <c r="E17" s="7">
-        <v>5773</v>
+        <v>5994</v>
       </c>
       <c r="F17" s="7">
-        <v>5369</v>
+        <v>4461</v>
       </c>
       <c r="G17" s="8">
         <f t="shared" si="0"/>
-        <v>8.4350000000000005</v>
+        <v>8.3719999999999999</v>
       </c>
       <c r="H17" s="8">
         <f t="shared" si="1"/>
-        <v>5.7729999999999997</v>
+        <v>5.9939999999999998</v>
       </c>
       <c r="I17" s="9">
         <f t="shared" si="2"/>
-        <v>1.5710560625814862</v>
+        <v>1.8767092580138982</v>
       </c>
       <c r="J17" s="10"/>
     </row>
@@ -1201,31 +1201,31 @@
         <v>25</v>
       </c>
       <c r="B18" s="12">
-        <v>211.14</v>
+        <v>198.71</v>
       </c>
       <c r="C18" s="13">
-        <v>5814</v>
+        <v>5502</v>
       </c>
       <c r="D18" s="14">
-        <v>8372</v>
+        <v>7961</v>
       </c>
       <c r="E18" s="14">
-        <v>5988</v>
+        <v>5244</v>
       </c>
       <c r="F18" s="14">
-        <v>4461</v>
+        <v>4181</v>
       </c>
       <c r="G18" s="15">
         <f t="shared" si="0"/>
-        <v>8.3719999999999999</v>
+        <v>7.9610000000000003</v>
       </c>
       <c r="H18" s="15">
         <f t="shared" si="1"/>
-        <v>5.9880000000000004</v>
+        <v>5.2439999999999998</v>
       </c>
       <c r="I18" s="16">
         <f t="shared" si="2"/>
-        <v>1.8767092580138982</v>
+        <v>1.9040899306386032</v>
       </c>
       <c r="J18" s="17"/>
     </row>
@@ -1234,31 +1234,31 @@
         <v>26</v>
       </c>
       <c r="B19" s="5">
-        <v>198.71</v>
+        <v>225.86</v>
       </c>
       <c r="C19" s="6">
-        <v>5502</v>
+        <v>6836</v>
       </c>
       <c r="D19" s="7">
-        <v>8022</v>
+        <v>7808</v>
       </c>
       <c r="E19" s="7">
-        <v>5249</v>
+        <v>4333</v>
       </c>
       <c r="F19" s="7">
-        <v>4181</v>
+        <v>3960</v>
       </c>
       <c r="G19" s="8">
         <f t="shared" si="0"/>
-        <v>8.0220000000000002</v>
+        <v>7.8079999999999998</v>
       </c>
       <c r="H19" s="8">
         <f t="shared" si="1"/>
-        <v>5.2489999999999997</v>
+        <v>4.3330000000000002</v>
       </c>
       <c r="I19" s="9">
         <f t="shared" si="2"/>
-        <v>1.9186797416885912</v>
+        <v>1.9717171717171718</v>
       </c>
       <c r="J19" s="10"/>
     </row>
@@ -1267,31 +1267,31 @@
         <v>27</v>
       </c>
       <c r="B20" s="12">
-        <v>158.57</v>
+        <v>101.07</v>
       </c>
       <c r="C20" s="13">
-        <v>5634</v>
+        <v>4286</v>
       </c>
       <c r="D20" s="14">
-        <v>8006</v>
+        <v>7761</v>
       </c>
       <c r="E20" s="14">
-        <v>4354</v>
+        <v>5493</v>
       </c>
       <c r="F20" s="14">
-        <v>3705</v>
+        <v>4476</v>
       </c>
       <c r="G20" s="15">
         <f t="shared" si="0"/>
-        <v>8.0060000000000002</v>
+        <v>7.7610000000000001</v>
       </c>
       <c r="H20" s="15">
         <f t="shared" si="1"/>
-        <v>4.3540000000000001</v>
+        <v>5.4930000000000003</v>
       </c>
       <c r="I20" s="16">
         <f t="shared" si="2"/>
-        <v>2.1608636977058029</v>
+        <v>1.7339142091152815</v>
       </c>
       <c r="J20" s="17"/>
     </row>
@@ -1300,31 +1300,31 @@
         <v>28</v>
       </c>
       <c r="B21" s="5">
-        <v>196.2</v>
+        <v>176.55</v>
       </c>
       <c r="C21" s="6">
-        <v>5516</v>
+        <v>7594</v>
       </c>
       <c r="D21" s="7">
-        <v>7932</v>
+        <v>7621</v>
       </c>
       <c r="E21" s="7">
-        <v>4263</v>
+        <v>4750</v>
       </c>
       <c r="F21" s="7">
-        <v>3785</v>
+        <v>3538</v>
       </c>
       <c r="G21" s="8">
         <f t="shared" si="0"/>
-        <v>7.9320000000000004</v>
+        <v>7.6210000000000004</v>
       </c>
       <c r="H21" s="8">
         <f t="shared" si="1"/>
-        <v>4.2629999999999999</v>
+        <v>4.75</v>
       </c>
       <c r="I21" s="9">
         <f t="shared" si="2"/>
-        <v>2.095640686922061</v>
+        <v>2.1540418315432448</v>
       </c>
       <c r="J21" s="10"/>
     </row>
@@ -1333,31 +1333,31 @@
         <v>29</v>
       </c>
       <c r="B22" s="12">
-        <v>225.86</v>
+        <v>89.83</v>
       </c>
       <c r="C22" s="13">
-        <v>6836</v>
+        <v>4143</v>
       </c>
       <c r="D22" s="14">
-        <v>7814</v>
+        <v>7502</v>
       </c>
       <c r="E22" s="14">
-        <v>4339</v>
+        <v>5345</v>
       </c>
       <c r="F22" s="14">
-        <v>3960</v>
+        <v>3986</v>
       </c>
       <c r="G22" s="15">
         <f t="shared" si="0"/>
-        <v>7.8140000000000001</v>
+        <v>7.5019999999999998</v>
       </c>
       <c r="H22" s="15">
         <f t="shared" si="1"/>
-        <v>4.3390000000000004</v>
+        <v>5.3449999999999998</v>
       </c>
       <c r="I22" s="16">
         <f t="shared" si="2"/>
-        <v>1.9732323232323232</v>
+        <v>1.8820873055694933</v>
       </c>
       <c r="J22" s="17"/>
     </row>
@@ -1366,31 +1366,31 @@
         <v>30</v>
       </c>
       <c r="B23" s="5">
-        <v>176.55</v>
+        <v>313.18</v>
       </c>
       <c r="C23" s="6">
-        <v>7594</v>
+        <v>7098</v>
       </c>
       <c r="D23" s="7">
-        <v>7622</v>
+        <v>7316</v>
       </c>
       <c r="E23" s="7">
-        <v>4746</v>
+        <v>3852</v>
       </c>
       <c r="F23" s="7">
-        <v>3538</v>
+        <v>2810</v>
       </c>
       <c r="G23" s="8">
         <f t="shared" si="0"/>
-        <v>7.6219999999999999</v>
+        <v>7.3159999999999998</v>
       </c>
       <c r="H23" s="8">
         <f t="shared" si="1"/>
-        <v>4.7460000000000004</v>
+        <v>3.8519999999999999</v>
       </c>
       <c r="I23" s="9">
         <f t="shared" si="2"/>
-        <v>2.1543244771057095</v>
+        <v>2.6035587188612102</v>
       </c>
       <c r="J23" s="10"/>
     </row>
@@ -1399,31 +1399,31 @@
         <v>31</v>
       </c>
       <c r="B24" s="12">
-        <v>89.83</v>
+        <v>158.57</v>
       </c>
       <c r="C24" s="13">
-        <v>4143</v>
+        <v>5634</v>
       </c>
       <c r="D24" s="14">
-        <v>7505</v>
+        <v>7225</v>
       </c>
       <c r="E24" s="14">
-        <v>5351</v>
+        <v>4354</v>
       </c>
       <c r="F24" s="14">
-        <v>3986</v>
+        <v>3705</v>
       </c>
       <c r="G24" s="15">
         <f t="shared" si="0"/>
-        <v>7.5049999999999999</v>
+        <v>7.2249999999999996</v>
       </c>
       <c r="H24" s="15">
         <f t="shared" si="1"/>
-        <v>5.351</v>
+        <v>4.3540000000000001</v>
       </c>
       <c r="I24" s="16">
         <f t="shared" si="2"/>
-        <v>1.8828399397892623</v>
+        <v>1.9500674763832659</v>
       </c>
       <c r="J24" s="17"/>
     </row>
@@ -1432,31 +1432,31 @@
         <v>32</v>
       </c>
       <c r="B25" s="5">
-        <v>313.18</v>
+        <v>128.41999999999999</v>
       </c>
       <c r="C25" s="6">
-        <v>7098</v>
+        <v>6551</v>
       </c>
       <c r="D25" s="7">
-        <v>7316</v>
+        <v>7184</v>
       </c>
       <c r="E25" s="7">
-        <v>3852</v>
+        <v>3078</v>
       </c>
       <c r="F25" s="7">
-        <v>2810</v>
+        <v>2542</v>
       </c>
       <c r="G25" s="8">
         <f t="shared" si="0"/>
-        <v>7.3159999999999998</v>
+        <v>7.1840000000000002</v>
       </c>
       <c r="H25" s="8">
         <f t="shared" si="1"/>
-        <v>3.8519999999999999</v>
+        <v>3.0779999999999998</v>
       </c>
       <c r="I25" s="9">
         <f t="shared" si="2"/>
-        <v>2.6035587188612102</v>
+        <v>2.8261211644374509</v>
       </c>
       <c r="J25" s="10"/>
     </row>
@@ -1465,31 +1465,31 @@
         <v>33</v>
       </c>
       <c r="B26" s="12">
-        <v>128.41999999999999</v>
+        <v>180.97</v>
       </c>
       <c r="C26" s="13">
-        <v>6551</v>
+        <v>5840</v>
       </c>
       <c r="D26" s="14">
-        <v>7184</v>
+        <v>6920</v>
       </c>
       <c r="E26" s="14">
-        <v>3078</v>
+        <v>4279</v>
       </c>
       <c r="F26" s="14">
-        <v>2542</v>
+        <v>3349</v>
       </c>
       <c r="G26" s="15">
         <f t="shared" si="0"/>
-        <v>7.1840000000000002</v>
+        <v>6.92</v>
       </c>
       <c r="H26" s="15">
         <f t="shared" si="1"/>
-        <v>3.0779999999999998</v>
+        <v>4.2789999999999999</v>
       </c>
       <c r="I26" s="16">
         <f t="shared" si="2"/>
-        <v>2.8261211644374509</v>
+        <v>2.0662884443117346</v>
       </c>
       <c r="J26" s="17"/>
     </row>
@@ -1498,31 +1498,31 @@
         <v>34</v>
       </c>
       <c r="B27" s="5">
-        <v>180.97</v>
+        <v>129.79</v>
       </c>
       <c r="C27" s="6">
-        <v>5840</v>
+        <v>4831</v>
       </c>
       <c r="D27" s="7">
-        <v>6920</v>
+        <v>6883</v>
       </c>
       <c r="E27" s="7">
-        <v>4279</v>
+        <v>4327</v>
       </c>
       <c r="F27" s="7">
-        <v>3349</v>
+        <v>3323</v>
       </c>
       <c r="G27" s="8">
         <f t="shared" si="0"/>
-        <v>6.92</v>
+        <v>6.883</v>
       </c>
       <c r="H27" s="8">
         <f t="shared" si="1"/>
-        <v>4.2789999999999999</v>
+        <v>4.327</v>
       </c>
       <c r="I27" s="9">
         <f t="shared" si="2"/>
-        <v>2.0662884443117346</v>
+        <v>2.0713210953957266</v>
       </c>
       <c r="J27" s="10"/>
     </row>
@@ -1537,25 +1537,25 @@
         <v>7420</v>
       </c>
       <c r="D28" s="14">
-        <v>6887</v>
+        <v>6881</v>
       </c>
       <c r="E28" s="14">
-        <v>3158</v>
+        <v>3156</v>
       </c>
       <c r="F28" s="14">
         <v>2827</v>
       </c>
       <c r="G28" s="15">
         <f t="shared" si="0"/>
-        <v>6.8869999999999996</v>
+        <v>6.8810000000000002</v>
       </c>
       <c r="H28" s="15">
         <f t="shared" si="1"/>
-        <v>3.1579999999999999</v>
+        <v>3.1560000000000001</v>
       </c>
       <c r="I28" s="16">
         <f t="shared" si="2"/>
-        <v>2.4361513972408915</v>
+        <v>2.434029006013442</v>
       </c>
       <c r="J28" s="17"/>
     </row>
@@ -1564,31 +1564,31 @@
         <v>36</v>
       </c>
       <c r="B29" s="5">
-        <v>127.51</v>
+        <v>196.2</v>
       </c>
       <c r="C29" s="6">
-        <v>5515</v>
+        <v>5516</v>
       </c>
       <c r="D29" s="7">
-        <v>6533</v>
+        <v>6732</v>
       </c>
       <c r="E29" s="7">
-        <v>4378</v>
+        <v>4263</v>
       </c>
       <c r="F29" s="7">
-        <v>2671</v>
+        <v>3785</v>
       </c>
       <c r="G29" s="8">
         <f t="shared" si="0"/>
-        <v>6.5330000000000004</v>
+        <v>6.7320000000000002</v>
       </c>
       <c r="H29" s="8">
         <f t="shared" si="1"/>
-        <v>4.3780000000000001</v>
+        <v>4.2629999999999999</v>
       </c>
       <c r="I29" s="9">
         <f t="shared" si="2"/>
-        <v>2.4459004118307748</v>
+        <v>1.7785997357992074</v>
       </c>
       <c r="J29" s="10"/>
     </row>
@@ -1597,31 +1597,31 @@
         <v>37</v>
       </c>
       <c r="B30" s="12">
-        <v>189.27</v>
+        <v>127.51</v>
       </c>
       <c r="C30" s="13">
-        <v>5556</v>
+        <v>5515</v>
       </c>
       <c r="D30" s="14">
-        <v>5875</v>
+        <v>6531</v>
       </c>
       <c r="E30" s="14">
-        <v>3291</v>
+        <v>4378</v>
       </c>
       <c r="F30" s="14">
-        <v>2759</v>
+        <v>2671</v>
       </c>
       <c r="G30" s="15">
         <f t="shared" si="0"/>
-        <v>5.875</v>
+        <v>6.5309999999999997</v>
       </c>
       <c r="H30" s="15">
         <f t="shared" si="1"/>
-        <v>3.2909999999999999</v>
+        <v>4.3780000000000001</v>
       </c>
       <c r="I30" s="16">
         <f t="shared" si="2"/>
-        <v>2.1293947082276188</v>
+        <v>2.4451516286035191</v>
       </c>
       <c r="J30" s="17"/>
     </row>
@@ -1630,31 +1630,31 @@
         <v>38</v>
       </c>
       <c r="B31" s="5">
-        <v>207.35</v>
+        <v>53.2</v>
       </c>
       <c r="C31" s="6">
-        <v>5781</v>
+        <v>3095</v>
       </c>
       <c r="D31" s="7">
-        <v>5832</v>
+        <v>5977</v>
       </c>
       <c r="E31" s="7">
-        <v>2635</v>
+        <v>4327</v>
       </c>
       <c r="F31" s="7">
-        <v>2643</v>
+        <v>3321</v>
       </c>
       <c r="G31" s="8">
         <f t="shared" si="0"/>
-        <v>5.8319999999999999</v>
+        <v>5.9770000000000003</v>
       </c>
       <c r="H31" s="8">
         <f t="shared" si="1"/>
-        <v>2.6349999999999998</v>
+        <v>4.327</v>
       </c>
       <c r="I31" s="9">
         <f t="shared" si="2"/>
-        <v>2.2065834279228151</v>
+        <v>1.7997591087021982</v>
       </c>
       <c r="J31" s="10"/>
     </row>
@@ -1663,132 +1663,132 @@
         <v>39</v>
       </c>
       <c r="B32" s="12">
-        <v>115.08</v>
+        <v>189.27</v>
       </c>
       <c r="C32" s="13">
-        <v>5656</v>
+        <v>5556</v>
       </c>
       <c r="D32" s="14">
-        <v>5704</v>
+        <v>5875</v>
       </c>
       <c r="E32" s="14">
-        <v>2929</v>
+        <v>3291</v>
       </c>
       <c r="F32" s="14">
-        <v>2262</v>
+        <v>2759</v>
       </c>
       <c r="G32" s="15">
         <f t="shared" si="0"/>
-        <v>5.7039999999999997</v>
+        <v>5.875</v>
       </c>
       <c r="H32" s="15">
         <f t="shared" si="1"/>
-        <v>2.9289999999999998</v>
+        <v>3.2909999999999999</v>
       </c>
       <c r="I32" s="16">
         <f t="shared" si="2"/>
-        <v>2.5216622458001767</v>
+        <v>2.1293947082276188</v>
       </c>
       <c r="J32" s="17"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A33" s="18" t="s">
+      <c r="A33" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B33" s="19">
-        <v>249.78</v>
-      </c>
-      <c r="C33" s="20">
-        <v>6425</v>
-      </c>
-      <c r="D33" s="21">
-        <v>5585</v>
-      </c>
-      <c r="E33" s="21">
-        <v>2372</v>
-      </c>
-      <c r="F33" s="21">
-        <v>1605</v>
-      </c>
-      <c r="G33" s="22">
-        <f t="shared" si="0"/>
-        <v>5.585</v>
-      </c>
-      <c r="H33" s="22">
-        <f t="shared" si="1"/>
-        <v>2.3719999999999999</v>
-      </c>
-      <c r="I33" s="23">
-        <f t="shared" si="2"/>
-        <v>3.4797507788161992</v>
-      </c>
-      <c r="J33" s="24"/>
+      <c r="B33" s="5">
+        <v>207.35</v>
+      </c>
+      <c r="C33" s="6">
+        <v>5781</v>
+      </c>
+      <c r="D33" s="7">
+        <v>5832</v>
+      </c>
+      <c r="E33" s="7">
+        <v>2635</v>
+      </c>
+      <c r="F33" s="7">
+        <v>2643</v>
+      </c>
+      <c r="G33" s="8">
+        <f t="shared" si="0"/>
+        <v>5.8319999999999999</v>
+      </c>
+      <c r="H33" s="8">
+        <f t="shared" si="1"/>
+        <v>2.6349999999999998</v>
+      </c>
+      <c r="I33" s="9">
+        <f t="shared" si="2"/>
+        <v>2.2065834279228151</v>
+      </c>
+      <c r="J33" s="10"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="11" t="s">
         <v>41</v>
       </c>
       <c r="B34" s="12">
-        <v>129.79</v>
+        <v>115.08</v>
       </c>
       <c r="C34" s="13">
-        <v>4831</v>
+        <v>5656</v>
       </c>
       <c r="D34" s="14">
-        <v>5572</v>
+        <v>5698</v>
       </c>
       <c r="E34" s="14">
-        <v>4327</v>
+        <v>2929</v>
       </c>
       <c r="F34" s="14">
-        <v>3323</v>
+        <v>2262</v>
       </c>
       <c r="G34" s="15">
         <f t="shared" si="0"/>
-        <v>5.5720000000000001</v>
+        <v>5.6980000000000004</v>
       </c>
       <c r="H34" s="15">
         <f t="shared" si="1"/>
-        <v>4.327</v>
+        <v>2.9289999999999998</v>
       </c>
       <c r="I34" s="16">
         <f t="shared" si="2"/>
-        <v>1.6767980740294914</v>
+        <v>2.5190097259062778</v>
       </c>
       <c r="J34" s="17"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="B35" s="5">
-        <v>53.2</v>
-      </c>
-      <c r="C35" s="6">
-        <v>3095</v>
-      </c>
-      <c r="D35" s="7">
-        <v>5391</v>
-      </c>
-      <c r="E35" s="7">
-        <v>4327</v>
-      </c>
-      <c r="F35" s="7">
-        <v>3321</v>
-      </c>
-      <c r="G35" s="8">
-        <f t="shared" si="0"/>
-        <v>5.391</v>
-      </c>
-      <c r="H35" s="8">
-        <f t="shared" si="1"/>
-        <v>4.327</v>
-      </c>
-      <c r="I35" s="9">
-        <f t="shared" si="2"/>
-        <v>1.6233062330623307</v>
-      </c>
-      <c r="J35" s="10"/>
+      <c r="B35" s="19">
+        <v>249.78</v>
+      </c>
+      <c r="C35" s="20">
+        <v>6425</v>
+      </c>
+      <c r="D35" s="21">
+        <v>5585</v>
+      </c>
+      <c r="E35" s="21">
+        <v>2372</v>
+      </c>
+      <c r="F35" s="21">
+        <v>1605</v>
+      </c>
+      <c r="G35" s="22">
+        <f t="shared" si="0"/>
+        <v>5.585</v>
+      </c>
+      <c r="H35" s="22">
+        <f t="shared" si="1"/>
+        <v>2.3719999999999999</v>
+      </c>
+      <c r="I35" s="23">
+        <f t="shared" si="2"/>
+        <v>3.4797507788161992</v>
+      </c>
+      <c r="J35" s="24"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="18" t="s">
@@ -1837,7 +1837,7 @@
         <v>4771</v>
       </c>
       <c r="E37" s="7">
-        <v>3095</v>
+        <v>3091</v>
       </c>
       <c r="F37" s="7">
         <v>2713</v>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="H37" s="8">
         <f t="shared" si="1"/>
-        <v>3.0950000000000002</v>
+        <v>3.0910000000000002</v>
       </c>
       <c r="I37" s="9">
         <f t="shared" si="2"/>
@@ -2093,19 +2093,19 @@
       </c>
       <c r="B46" s="26">
         <f>SUM(B5:B44)</f>
-        <v>7068.94</v>
+        <v>7068.9400000000005</v>
       </c>
       <c r="D46" s="27">
         <f>MAX(D5:D44)</f>
-        <v>12325</v>
+        <v>12306</v>
       </c>
       <c r="G46" s="28">
         <f>IFERROR(MAX(G5:G44),"")</f>
-        <v>12.324999999999999</v>
+        <v>12.305999999999999</v>
       </c>
       <c r="I46" s="29">
         <f>IFERROR(AVERAGE(I5:I44),"")</f>
-        <v>5.0491275606093007</v>
+        <v>5.040575939303765</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">

--- a/FAZENDA_PROMISSÃO_distancias.xlsx
+++ b/FAZENDA_PROMISSÃO_distancias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1FAFE11-0E9D-4E76-A51D-69E2486EC45E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4019091E-416B-4386-9DBD-98367E19BAA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2232" yWindow="2232" windowWidth="14100" windowHeight="9792" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Distâncias" sheetId="1" r:id="rId1"/>
@@ -156,13 +156,13 @@
     <t>T-15</t>
   </si>
   <si>
+    <t>T-29B</t>
+  </si>
+  <si>
+    <t>T-23</t>
+  </si>
+  <si>
     <t>T-19</t>
-  </si>
-  <si>
-    <t>T-29B</t>
-  </si>
-  <si>
-    <t>T-23</t>
   </si>
   <si>
     <t>T-26</t>
@@ -1696,99 +1696,99 @@
         <v>40</v>
       </c>
       <c r="B33" s="5">
+        <v>115.08</v>
+      </c>
+      <c r="C33" s="6">
+        <v>5656</v>
+      </c>
+      <c r="D33" s="7">
+        <v>5698</v>
+      </c>
+      <c r="E33" s="7">
+        <v>2929</v>
+      </c>
+      <c r="F33" s="7">
+        <v>2262</v>
+      </c>
+      <c r="G33" s="8">
+        <f t="shared" si="0"/>
+        <v>5.6980000000000004</v>
+      </c>
+      <c r="H33" s="8">
+        <f t="shared" si="1"/>
+        <v>2.9289999999999998</v>
+      </c>
+      <c r="I33" s="9">
+        <f t="shared" si="2"/>
+        <v>2.5190097259062778</v>
+      </c>
+      <c r="J33" s="10"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A34" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="19">
+        <v>249.78</v>
+      </c>
+      <c r="C34" s="20">
+        <v>6425</v>
+      </c>
+      <c r="D34" s="21">
+        <v>5585</v>
+      </c>
+      <c r="E34" s="21">
+        <v>2372</v>
+      </c>
+      <c r="F34" s="21">
+        <v>1605</v>
+      </c>
+      <c r="G34" s="22">
+        <f t="shared" si="0"/>
+        <v>5.585</v>
+      </c>
+      <c r="H34" s="22">
+        <f t="shared" si="1"/>
+        <v>2.3719999999999999</v>
+      </c>
+      <c r="I34" s="23">
+        <f t="shared" si="2"/>
+        <v>3.4797507788161992</v>
+      </c>
+      <c r="J34" s="24"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A35" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="5">
         <v>207.35</v>
       </c>
-      <c r="C33" s="6">
+      <c r="C35" s="6">
         <v>5781</v>
       </c>
-      <c r="D33" s="7">
-        <v>5832</v>
-      </c>
-      <c r="E33" s="7">
+      <c r="D35" s="7">
+        <v>5560</v>
+      </c>
+      <c r="E35" s="7">
         <v>2635</v>
       </c>
-      <c r="F33" s="7">
+      <c r="F35" s="7">
         <v>2643</v>
       </c>
-      <c r="G33" s="8">
-        <f t="shared" si="0"/>
-        <v>5.8319999999999999</v>
-      </c>
-      <c r="H33" s="8">
+      <c r="G35" s="8">
+        <f t="shared" si="0"/>
+        <v>5.56</v>
+      </c>
+      <c r="H35" s="8">
         <f t="shared" si="1"/>
         <v>2.6349999999999998</v>
       </c>
-      <c r="I33" s="9">
-        <f t="shared" si="2"/>
-        <v>2.2065834279228151</v>
-      </c>
-      <c r="J33" s="10"/>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A34" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="B34" s="12">
-        <v>115.08</v>
-      </c>
-      <c r="C34" s="13">
-        <v>5656</v>
-      </c>
-      <c r="D34" s="14">
-        <v>5698</v>
-      </c>
-      <c r="E34" s="14">
-        <v>2929</v>
-      </c>
-      <c r="F34" s="14">
-        <v>2262</v>
-      </c>
-      <c r="G34" s="15">
-        <f t="shared" si="0"/>
-        <v>5.6980000000000004</v>
-      </c>
-      <c r="H34" s="15">
-        <f t="shared" si="1"/>
-        <v>2.9289999999999998</v>
-      </c>
-      <c r="I34" s="16">
-        <f t="shared" si="2"/>
-        <v>2.5190097259062778</v>
-      </c>
-      <c r="J34" s="17"/>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A35" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" s="19">
-        <v>249.78</v>
-      </c>
-      <c r="C35" s="20">
-        <v>6425</v>
-      </c>
-      <c r="D35" s="21">
-        <v>5585</v>
-      </c>
-      <c r="E35" s="21">
-        <v>2372</v>
-      </c>
-      <c r="F35" s="21">
-        <v>1605</v>
-      </c>
-      <c r="G35" s="22">
-        <f t="shared" si="0"/>
-        <v>5.585</v>
-      </c>
-      <c r="H35" s="22">
-        <f t="shared" si="1"/>
-        <v>2.3719999999999999</v>
-      </c>
-      <c r="I35" s="23">
-        <f t="shared" si="2"/>
-        <v>3.4797507788161992</v>
-      </c>
-      <c r="J35" s="24"/>
+      <c r="I35" s="9">
+        <f t="shared" si="2"/>
+        <v>2.1036700718880059</v>
+      </c>
+      <c r="J35" s="10"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="18" t="s">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="I46" s="29">
         <f>IFERROR(AVERAGE(I5:I44),"")</f>
-        <v>5.040575939303765</v>
+        <v>5.0380031054028942</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">

--- a/FAZENDA_PROMISSÃO_distancias.xlsx
+++ b/FAZENDA_PROMISSÃO_distancias.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhao\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4019091E-416B-4386-9DBD-98367E19BAA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70B4E1D7-9BA7-410E-82FA-C845EE1410C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2232" yWindow="2232" windowWidth="14100" windowHeight="9792" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Distâncias" sheetId="1" r:id="rId1"/>

--- a/FAZENDA_PROMISSÃO_distancias.xlsx
+++ b/FAZENDA_PROMISSÃO_distancias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70B4E1D7-9BA7-410E-82FA-C845EE1410C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC7BCFA5-4DA0-4CB0-BA7B-97DCD74194D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/FAZENDA_PROMISSÃO_distancias.xlsx
+++ b/FAZENDA_PROMISSÃO_distancias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC7BCFA5-4DA0-4CB0-BA7B-97DCD74194D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E65B532F-BA2B-46C4-9BC2-8267F986EF3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -280,49 +280,58 @@
       <b/>
       <sz val="14"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">

--- a/FAZENDA_PROMISSÃO_distancias.xlsx
+++ b/FAZENDA_PROMISSÃO_distancias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E65B532F-BA2B-46C4-9BC2-8267F986EF3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED16C8DE-BC2F-4C23-8061-F3ECC9F0B4E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="40875" yWindow="3930" windowWidth="14100" windowHeight="9795" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Distâncias" sheetId="1" r:id="rId1"/>
@@ -280,58 +280,49 @@
       <b/>
       <sz val="14"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">

--- a/FAZENDA_PROMISSÃO_distancias.xlsx
+++ b/FAZENDA_PROMISSÃO_distancias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED16C8DE-BC2F-4C23-8061-F3ECC9F0B4E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BB4FB45-E086-47EB-90B0-1B8A3C3E2D41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40875" yWindow="3930" windowWidth="14100" windowHeight="9795" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="11280" windowHeight="7836" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Distâncias" sheetId="1" r:id="rId1"/>
@@ -280,49 +280,58 @@
       <b/>
       <sz val="14"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">

--- a/FAZENDA_PROMISSÃO_distancias.xlsx
+++ b/FAZENDA_PROMISSÃO_distancias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BB4FB45-E086-47EB-90B0-1B8A3C3E2D41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A970569-9F86-402E-A2B2-99882E27A72A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="11280" windowHeight="7836" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Distâncias" sheetId="1" r:id="rId1"/>

--- a/FAZENDA_PROMISSÃO_distancias.xlsx
+++ b/FAZENDA_PROMISSÃO_distancias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A970569-9F86-402E-A2B2-99882E27A72A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F32FA6AF-7842-48F9-8A74-0306808BE17E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Distâncias" sheetId="1" r:id="rId1"/>
@@ -280,58 +280,49 @@
       <b/>
       <sz val="14"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
